--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>นายธีรพัส แก้วงาม</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D2" s="30" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>นางสาวนภัสสร นูมหันต์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>นางสาวนรภร เจริญสลุง</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>นายบุนยามีน มะสง</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D5" s="30" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>นายปัญญานันท์ ทองแก้วเกิด</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D6" s="30" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>นางสาวภิญยดา ศรีแนน</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D7" s="30" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>นายภูริณ มานหมัด</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>นายรัชชานนท์ สาคะเรศ</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D9" s="30" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>นายวรพล พลอยชัด</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>นายศุภณัฐ จันทรังษี</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D11" s="30" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>นางสาวเศรษฐกมล วังออมทรัพย์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>นางสาวอริศรา เล่งกูล</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D13" s="30" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>นายภัทรพล ดิษฐาพร</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>นายภาคิน แซ่โง้ว</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>นายกนล แสงเดช</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>นางสาวกมลนิตย์ โตอยู่</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D17" s="30" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>นายกฤษกร ศรีสัจจัง</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D18" s="30" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>นายกันติวัสส์ ตันตระการย์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D19" s="30" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>นายเกษมโชค นชะพงษ์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D20" s="30" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>นายจักรินทร์ อินทร์น้อย</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D21" s="30" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>นางสาวจันทร์เจ้า เทพจิตต์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D22" s="30" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>นางสาวฑิฆัมพร ตรีบุสยะรัตน์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D23" s="30" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>นางสาวณปภัช บุญมายศ</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D24" s="30" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>นายธนทัต มุทธากาญจน์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D25" s="30" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C26" s="31" t="inlineStr">
         <is>
-          <t>นายธนภูมิ เหลืองชัยพัฒนา</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D26" s="30" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>นายธนากร เรืองพูน</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D27" s="30" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="C28" s="31" t="inlineStr">
         <is>
-          <t>นายธรรมกร เจริญพร</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D28" s="30" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>นางสาวธัชตะวัน ยกโต</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D29" s="30" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>นายนนทกร จวนทองรักษ์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>นายนภัสรพี อร่ามฉิม</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C32" s="31" t="inlineStr">
         <is>
-          <t>นายพิชญุตม์ ลอยมา</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D32" s="30" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>นายภควัฒน์ พรมประโคน</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D33" s="30" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="C34" s="31" t="inlineStr">
         <is>
-          <t>นายภัคพล ลาวชัย</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D34" s="30" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>นายภัคพล อินทะรังษี</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D35" s="30" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="C36" s="31" t="inlineStr">
         <is>
-          <t>นายยุทธนา สุขกำเนิด</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D36" s="30" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>นายรพีภัทร มอยนา</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D37" s="30" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>นายวีรภัทร ดีมาก</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D38" s="30" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>นางสาวศวิตา ไชยสุนทร</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D39" s="30" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C40" s="31" t="inlineStr">
         <is>
-          <t>นายสรศักดิ์ โคตรนาม</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D40" s="30" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>นายสราวุฒิ ยะโส</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D41" s="30" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>นายสิทชัยเลิศ ศรนรายณ์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D42" s="30" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>นายสุทธิโชติ ใบเตย</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D43" s="30" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>นายสุเมธ อบอารีย์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D44" s="30" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>นายอัสนี คงดีจันทร์</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D45" s="30" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>นางสาวอาทิตยา ไทยเจริญ</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D46" s="30" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>นางสาวอารยา แสนสุข</t>
+          <t>----</t>
         </is>
       </c>
       <c r="D47" s="30" t="inlineStr">

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="41210" yWindow="-5830" windowWidth="21700" windowHeight="19230" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10746" yWindow="0" windowWidth="11154" windowHeight="12192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -63,8 +63,15 @@
     <font>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +92,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,18 +204,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -212,13 +215,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,10 +243,13 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -350,6 +366,36 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4419600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -570,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="120.9" customHeight="1">
+    <row r="6" ht="156.9" customHeight="1">
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>รายชื่อนิสิต</t>
@@ -596,7 +642,11 @@
           <t>Ex.4 EFG for Sphere</t>
         </is>
       </c>
-      <c r="O6" s="10" t="n"/>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>Ex.5 Guassian vs Mercator</t>
+        </is>
+      </c>
       <c r="P6" s="10" t="n"/>
       <c r="Q6" s="10" t="n"/>
       <c r="R6" s="10" t="n"/>
@@ -657,11 +707,15 @@
       <c r="L7" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="12" t="n"/>
+      <c r="M7" s="12" t="n">
+        <v>10</v>
+      </c>
       <c r="N7" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="O7" s="12" t="n"/>
+      <c r="O7" s="12" t="n">
+        <v>10</v>
+      </c>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="12" t="n"/>
       <c r="R7" s="12" t="n"/>
@@ -783,9 +837,13 @@
         </is>
       </c>
       <c r="L9" s="17" t="n"/>
-      <c r="M9" s="9" t="n"/>
+      <c r="M9" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="N9" s="11" t="n"/>
-      <c r="O9" s="9" t="n"/>
+      <c r="O9" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
@@ -844,9 +902,13 @@
         </is>
       </c>
       <c r="L10" s="17" t="n"/>
-      <c r="M10" s="9" t="n"/>
+      <c r="M10" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="N10" s="11" t="n"/>
-      <c r="O10" s="9" t="n"/>
+      <c r="O10" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P10" s="9" t="n"/>
       <c r="Q10" s="9" t="n"/>
       <c r="R10" s="9" t="n"/>
@@ -907,11 +969,15 @@
       <c r="L11" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M11" s="9" t="n"/>
+      <c r="M11" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="N11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" s="9" t="n"/>
+      <c r="O11" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
@@ -1094,9 +1160,13 @@
         </is>
       </c>
       <c r="L14" s="17" t="n"/>
-      <c r="M14" s="9" t="n"/>
+      <c r="M14" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="N14" s="11" t="n"/>
-      <c r="O14" s="9" t="n"/>
+      <c r="O14" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P14" s="9" t="n"/>
       <c r="Q14" s="9" t="n"/>
       <c r="R14" s="9" t="n"/>
@@ -1157,11 +1227,15 @@
       <c r="L15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="9" t="n"/>
+      <c r="M15" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="N15" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O15" s="9" t="n"/>
+      <c r="O15" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
@@ -1220,11 +1294,15 @@
         </is>
       </c>
       <c r="L16" s="17" t="n"/>
-      <c r="M16" s="9" t="n"/>
+      <c r="M16" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="N16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O16" s="9" t="n"/>
+      <c r="O16" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P16" s="9" t="n"/>
       <c r="Q16" s="9" t="n"/>
       <c r="R16" s="9" t="n"/>
@@ -1285,11 +1363,15 @@
       <c r="L17" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M17" s="9" t="n"/>
+      <c r="M17" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="N17" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="9" t="n"/>
+      <c r="O17" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -1348,9 +1430,13 @@
         </is>
       </c>
       <c r="L18" s="17" t="n"/>
-      <c r="M18" s="9" t="n"/>
+      <c r="M18" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="N18" s="11" t="n"/>
-      <c r="O18" s="9" t="n"/>
+      <c r="O18" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P18" s="9" t="n"/>
       <c r="Q18" s="9" t="n"/>
       <c r="R18" s="9" t="n"/>
@@ -1472,11 +1558,15 @@
       <c r="L20" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="9" t="n"/>
+      <c r="M20" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="N20" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="O20" s="9" t="n"/>
+      <c r="O20" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P20" s="9" t="n"/>
       <c r="Q20" s="9" t="n"/>
       <c r="R20" s="9" t="n"/>
@@ -1537,9 +1627,13 @@
       <c r="L21" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M21" s="9" t="n"/>
+      <c r="M21" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="N21" s="11" t="n"/>
-      <c r="O21" s="9" t="n"/>
+      <c r="O21" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
@@ -1600,11 +1694,15 @@
       <c r="L22" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M22" s="9" t="n"/>
+      <c r="M22" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="N22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O22" s="9" t="n"/>
+      <c r="O22" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P22" s="9" t="n"/>
       <c r="Q22" s="9" t="n"/>
       <c r="R22" s="9" t="n"/>
@@ -1665,11 +1763,15 @@
       <c r="L23" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M23" s="9" t="n"/>
+      <c r="M23" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="N23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O23" s="9" t="n"/>
+      <c r="O23" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
@@ -1730,11 +1832,15 @@
       <c r="L24" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M24" s="9" t="n"/>
+      <c r="M24" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N24" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O24" s="9" t="n"/>
+      <c r="O24" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P24" s="9" t="n"/>
       <c r="Q24" s="9" t="n"/>
       <c r="R24" s="9" t="n"/>
@@ -1795,11 +1901,15 @@
       <c r="L25" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="9" t="n"/>
+      <c r="M25" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="N25" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="9" t="n"/>
+      <c r="O25" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
@@ -1860,11 +1970,15 @@
       <c r="L26" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M26" s="9" t="n"/>
+      <c r="M26" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="N26" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O26" s="9" t="n"/>
+      <c r="O26" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P26" s="9" t="n"/>
       <c r="Q26" s="9" t="n"/>
       <c r="R26" s="9" t="n"/>
@@ -1925,9 +2039,13 @@
       <c r="L27" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="M27" s="9" t="n"/>
+      <c r="M27" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="N27" s="11" t="n"/>
-      <c r="O27" s="9" t="n"/>
+      <c r="O27" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
@@ -1992,7 +2110,9 @@
       <c r="N28" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O28" s="9" t="n"/>
+      <c r="O28" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="P28" s="9" t="n"/>
       <c r="Q28" s="9" t="n"/>
       <c r="R28" s="9" t="n"/>
@@ -2053,11 +2173,15 @@
       <c r="L29" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="M29" s="9" t="n"/>
+      <c r="M29" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="N29" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O29" s="9" t="n"/>
+      <c r="O29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
@@ -2118,11 +2242,15 @@
       <c r="L30" s="17" t="n">
         <v>11.5</v>
       </c>
-      <c r="M30" s="9" t="n"/>
+      <c r="M30" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O30" s="9" t="n"/>
+      <c r="O30" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P30" s="9" t="n"/>
       <c r="Q30" s="9" t="n"/>
       <c r="R30" s="9" t="n"/>
@@ -2244,11 +2372,15 @@
       <c r="L32" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M32" s="9" t="n"/>
+      <c r="M32" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N32" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O32" s="9" t="n"/>
+      <c r="O32" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P32" s="9" t="n"/>
       <c r="Q32" s="9" t="n"/>
       <c r="R32" s="9" t="n"/>
@@ -2309,9 +2441,13 @@
       <c r="L33" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="M33" s="9" t="n"/>
+      <c r="M33" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N33" s="11" t="n"/>
-      <c r="O33" s="9" t="n"/>
+      <c r="O33" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
@@ -2372,9 +2508,13 @@
       <c r="L34" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M34" s="9" t="n"/>
+      <c r="M34" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="N34" s="11" t="n"/>
-      <c r="O34" s="9" t="n"/>
+      <c r="O34" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P34" s="9" t="n"/>
       <c r="Q34" s="9" t="n"/>
       <c r="R34" s="9" t="n"/>
@@ -2435,11 +2575,15 @@
       <c r="L35" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M35" s="9" t="n"/>
+      <c r="M35" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O35" s="9" t="n"/>
+      <c r="O35" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
@@ -2500,11 +2644,15 @@
       <c r="L36" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M36" s="9" t="n"/>
+      <c r="M36" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="N36" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O36" s="9" t="n"/>
+      <c r="O36" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P36" s="9" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="9" t="n"/>
@@ -2565,11 +2713,15 @@
       <c r="L37" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M37" s="9" t="n"/>
+      <c r="M37" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="N37" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O37" s="9" t="n"/>
+      <c r="O37" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
@@ -2628,11 +2780,15 @@
         </is>
       </c>
       <c r="L38" s="17" t="n"/>
-      <c r="M38" s="9" t="n"/>
+      <c r="M38" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="N38" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O38" s="9" t="n"/>
+      <c r="O38" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P38" s="9" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="9" t="n"/>
@@ -2693,11 +2849,15 @@
       <c r="L39" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M39" s="9" t="n"/>
+      <c r="M39" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N39" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O39" s="9" t="n"/>
+      <c r="O39" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
@@ -2758,11 +2918,15 @@
       <c r="L40" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M40" s="9" t="n"/>
+      <c r="M40" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N40" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="O40" s="9" t="n"/>
+      <c r="O40" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P40" s="9" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="9" t="n"/>
@@ -2823,11 +2987,15 @@
       <c r="L41" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M41" s="9" t="n"/>
+      <c r="M41" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N41" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O41" s="9" t="n"/>
+      <c r="O41" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
@@ -2888,11 +3056,15 @@
       <c r="L42" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M42" s="9" t="n"/>
+      <c r="M42" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="N42" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O42" s="9" t="n"/>
+      <c r="O42" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P42" s="9" t="n"/>
       <c r="Q42" s="9" t="n"/>
       <c r="R42" s="9" t="n"/>
@@ -2953,11 +3125,15 @@
       <c r="L43" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M43" s="9" t="n"/>
+      <c r="M43" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="N43" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O43" s="9" t="n"/>
+      <c r="O43" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
@@ -3018,11 +3194,15 @@
       <c r="L44" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="M44" s="9" t="n"/>
+      <c r="M44" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N44" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O44" s="9" t="n"/>
+      <c r="O44" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P44" s="9" t="n"/>
       <c r="Q44" s="9" t="n"/>
       <c r="R44" s="9" t="n"/>
@@ -3083,11 +3263,15 @@
       <c r="L45" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M45" s="9" t="n"/>
+      <c r="M45" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N45" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O45" s="9" t="n"/>
+      <c r="O45" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
@@ -3148,9 +3332,13 @@
       <c r="L46" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M46" s="9" t="n"/>
+      <c r="M46" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N46" s="11" t="n"/>
-      <c r="O46" s="9" t="n"/>
+      <c r="O46" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="P46" s="9" t="n"/>
       <c r="Q46" s="9" t="n"/>
       <c r="R46" s="9" t="n"/>
@@ -3211,11 +3399,15 @@
       <c r="L47" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M47" s="9" t="n"/>
+      <c r="M47" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N47" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O47" s="9" t="n"/>
+      <c r="O47" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
@@ -3276,11 +3468,15 @@
       <c r="L48" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M48" s="9" t="n"/>
+      <c r="M48" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="N48" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O48" s="9" t="n"/>
+      <c r="O48" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P48" s="9" t="n"/>
       <c r="Q48" s="9" t="n"/>
       <c r="R48" s="9" t="n"/>
@@ -3341,11 +3537,15 @@
       <c r="L49" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M49" s="9" t="n"/>
+      <c r="M49" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N49" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O49" s="9" t="n"/>
+      <c r="O49" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
@@ -3406,11 +3606,15 @@
       <c r="L50" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M50" s="9" t="n"/>
+      <c r="M50" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N50" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O50" s="9" t="n"/>
+      <c r="O50" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P50" s="9" t="n"/>
       <c r="Q50" s="9" t="n"/>
       <c r="R50" s="9" t="n"/>
@@ -3471,11 +3675,15 @@
       <c r="L51" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="M51" s="9" t="n"/>
+      <c r="M51" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="N51" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O51" s="9" t="n"/>
+      <c r="O51" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
@@ -3536,18 +3744,22 @@
       <c r="L52" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="M52" s="9" t="n"/>
+      <c r="M52" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="N52" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O52" s="9" t="n"/>
+      <c r="O52" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P52" s="9" t="n"/>
       <c r="Q52" s="9" t="n"/>
       <c r="R52" s="9" t="n"/>
       <c r="S52" s="9" t="n"/>
       <c r="T52" s="9" t="n"/>
     </row>
-    <row r="53" ht="20.4" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
         <is>
           <t>46</t>
@@ -3601,11 +3813,15 @@
       <c r="L53" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="M53" s="9" t="n"/>
+      <c r="M53" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N53" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O53" s="9" t="n"/>
+      <c r="O53" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
@@ -3645,14 +3861,16 @@
     <col width="6.94921875" customWidth="1" min="1" max="1"/>
     <col width="16.19921875" customWidth="1" min="2" max="2"/>
     <col width="31.046875" customWidth="1" min="3" max="3"/>
-    <col width="3.796875" customWidth="1" style="21" min="4" max="4"/>
-    <col width="3.796875" customWidth="1" style="20" min="5" max="5"/>
-    <col width="3.796875" customWidth="1" min="6" max="14"/>
+    <col width="3.796875" customWidth="1" style="19" min="4" max="4"/>
+    <col width="3.796875" customWidth="1" min="5" max="5"/>
+    <col width="3.796875" customWidth="1" style="18" min="6" max="6"/>
+    <col width="3.796875" customWidth="1" min="7" max="14"/>
     <col width="8.796875" customWidth="1" min="15" max="15"/>
     <col width="4.6484375" customWidth="1" min="16" max="26"/>
   </cols>
   <sheetData>
-    <row r="6" ht="73.5" customHeight="1">
+    <row r="5" ht="19.2" customHeight="1"/>
+    <row r="6" ht="69.59999999999999" customHeight="1">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="10" t="inlineStr">
@@ -3660,25 +3878,25 @@
           <t>การเข้าเรียน</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>04-14JUL69</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="19" t="n"/>
-      <c r="L6" s="19" t="n"/>
-      <c r="M6" s="19" t="n"/>
-      <c r="N6" s="19" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="25" t="n"/>
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -3694,16 +3912,16 @@
         <v/>
       </c>
       <c r="D7" s="23" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -3718,11 +3936,11 @@
         <f>Exercise!D8</f>
         <v/>
       </c>
-      <c r="D8" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="D8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="17" t="n"/>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
@@ -3745,11 +3963,11 @@
         <f>Exercise!D9</f>
         <v/>
       </c>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="17" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
@@ -3772,11 +3990,11 @@
         <f>Exercise!D10</f>
         <v/>
       </c>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="n"/>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
@@ -3799,13 +4017,13 @@
         <f>Exercise!D11</f>
         <v/>
       </c>
-      <c r="D11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="n"/>
+      <c r="D11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
@@ -3828,13 +4046,13 @@
         <f>Exercise!D12</f>
         <v/>
       </c>
-      <c r="D12" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9" t="n"/>
+      <c r="D12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="n"/>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
@@ -3857,11 +4075,11 @@
         <f>Exercise!D13</f>
         <v/>
       </c>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="n"/>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
@@ -3884,11 +4102,11 @@
         <f>Exercise!D14</f>
         <v/>
       </c>
-      <c r="D14" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="D14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="17" t="n"/>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
@@ -3911,13 +4129,13 @@
         <f>Exercise!D15</f>
         <v/>
       </c>
-      <c r="D15" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="D15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -3940,13 +4158,13 @@
         <f>Exercise!D16</f>
         <v/>
       </c>
-      <c r="D16" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="n"/>
+      <c r="D16" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17" t="n"/>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
@@ -3969,13 +4187,13 @@
         <f>Exercise!D17</f>
         <v/>
       </c>
-      <c r="D17" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9" t="n"/>
+      <c r="D17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="17" t="n"/>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -3998,11 +4216,11 @@
         <f>Exercise!D18</f>
         <v/>
       </c>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="17" t="n"/>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -4025,9 +4243,9 @@
         <f>Exercise!D19</f>
         <v/>
       </c>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="9" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="17" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
@@ -4050,9 +4268,9 @@
         <f>Exercise!D20</f>
         <v/>
       </c>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="17" t="n"/>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
@@ -4075,13 +4293,13 @@
         <f>Exercise!D21</f>
         <v/>
       </c>
-      <c r="D21" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9" t="n"/>
+      <c r="D21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
@@ -4104,13 +4322,13 @@
         <f>Exercise!D22</f>
         <v/>
       </c>
-      <c r="D22" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="n"/>
+      <c r="D22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
@@ -4133,13 +4351,13 @@
         <f>Exercise!D23</f>
         <v/>
       </c>
-      <c r="D23" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="n"/>
+      <c r="D23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
@@ -4162,13 +4380,13 @@
         <f>Exercise!D24</f>
         <v/>
       </c>
-      <c r="D24" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="n"/>
+      <c r="D24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
@@ -4191,13 +4409,13 @@
         <f>Exercise!D25</f>
         <v/>
       </c>
-      <c r="D25" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9" t="n"/>
+      <c r="D25" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
@@ -4220,13 +4438,13 @@
         <f>Exercise!D26</f>
         <v/>
       </c>
-      <c r="D26" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9" t="n"/>
+      <c r="D26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17" t="n"/>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
@@ -4249,11 +4467,11 @@
         <f>Exercise!D27</f>
         <v/>
       </c>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
@@ -4276,11 +4494,11 @@
         <f>Exercise!D28</f>
         <v/>
       </c>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17" t="n"/>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
@@ -4303,13 +4521,13 @@
         <f>Exercise!D29</f>
         <v/>
       </c>
-      <c r="D29" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="9" t="n"/>
+      <c r="D29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="17" t="n"/>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
@@ -4332,13 +4550,13 @@
         <f>Exercise!D30</f>
         <v/>
       </c>
-      <c r="D30" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="9" t="n"/>
+      <c r="D30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="17" t="n"/>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
@@ -4361,9 +4579,9 @@
         <f>Exercise!D31</f>
         <v/>
       </c>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="9" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="17" t="n"/>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
@@ -4386,13 +4604,13 @@
         <f>Exercise!D32</f>
         <v/>
       </c>
-      <c r="D32" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="9" t="n"/>
+      <c r="D32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="n"/>
       <c r="G32" s="9" t="n"/>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
@@ -4415,11 +4633,11 @@
         <f>Exercise!D33</f>
         <v/>
       </c>
-      <c r="D33" s="24" t="n"/>
-      <c r="E33" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="9" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="17" t="n"/>
       <c r="G33" s="9" t="n"/>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
@@ -4442,11 +4660,11 @@
         <f>Exercise!D34</f>
         <v/>
       </c>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="9" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="17" t="n"/>
       <c r="G34" s="9" t="n"/>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
@@ -4469,13 +4687,13 @@
         <f>Exercise!D35</f>
         <v/>
       </c>
-      <c r="D35" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="9" t="n"/>
+      <c r="D35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="17" t="n"/>
       <c r="G35" s="9" t="n"/>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
@@ -4498,13 +4716,13 @@
         <f>Exercise!D36</f>
         <v/>
       </c>
-      <c r="D36" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="9" t="n"/>
+      <c r="D36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="n"/>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
@@ -4527,13 +4745,13 @@
         <f>Exercise!D37</f>
         <v/>
       </c>
-      <c r="D37" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="9" t="n"/>
+      <c r="D37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="17" t="n"/>
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
@@ -4556,11 +4774,11 @@
         <f>Exercise!D38</f>
         <v/>
       </c>
-      <c r="D38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="9" t="n"/>
+      <c r="D38" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="17" t="n"/>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
@@ -4583,13 +4801,13 @@
         <f>Exercise!D39</f>
         <v/>
       </c>
-      <c r="D39" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9" t="n"/>
+      <c r="D39" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="17" t="n"/>
       <c r="G39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
@@ -4612,13 +4830,13 @@
         <f>Exercise!D40</f>
         <v/>
       </c>
-      <c r="D40" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="9" t="n"/>
+      <c r="D40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="17" t="n"/>
       <c r="G40" s="9" t="n"/>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
@@ -4641,13 +4859,13 @@
         <f>Exercise!D41</f>
         <v/>
       </c>
-      <c r="D41" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="9" t="n"/>
+      <c r="D41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="17" t="n"/>
       <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
@@ -4670,13 +4888,13 @@
         <f>Exercise!D42</f>
         <v/>
       </c>
-      <c r="D42" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="9" t="n"/>
+      <c r="D42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="17" t="n"/>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
@@ -4699,13 +4917,13 @@
         <f>Exercise!D43</f>
         <v/>
       </c>
-      <c r="D43" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="9" t="n"/>
+      <c r="D43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="17" t="n"/>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
@@ -4728,13 +4946,13 @@
         <f>Exercise!D44</f>
         <v/>
       </c>
-      <c r="D44" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="9" t="n"/>
+      <c r="D44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17" t="n"/>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
@@ -4757,13 +4975,13 @@
         <f>Exercise!D45</f>
         <v/>
       </c>
-      <c r="D45" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="9" t="n"/>
+      <c r="D45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="17" t="n"/>
       <c r="G45" s="9" t="n"/>
       <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n"/>
@@ -4786,13 +5004,13 @@
         <f>Exercise!D46</f>
         <v/>
       </c>
-      <c r="D46" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="9" t="n"/>
+      <c r="D46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="17" t="n"/>
       <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
@@ -4815,13 +5033,13 @@
         <f>Exercise!D47</f>
         <v/>
       </c>
-      <c r="D47" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="9" t="n"/>
+      <c r="D47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="17" t="n"/>
       <c r="G47" s="9" t="n"/>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
@@ -4844,13 +5062,13 @@
         <f>Exercise!D48</f>
         <v/>
       </c>
-      <c r="D48" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="9" t="n"/>
+      <c r="D48" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="17" t="n"/>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
@@ -4873,13 +5091,13 @@
         <f>Exercise!D49</f>
         <v/>
       </c>
-      <c r="D49" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="9" t="n"/>
+      <c r="D49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="17" t="n"/>
       <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
@@ -4902,13 +5120,13 @@
         <f>Exercise!D50</f>
         <v/>
       </c>
-      <c r="D50" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="9" t="n"/>
+      <c r="D50" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="17" t="n"/>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
@@ -4931,13 +5149,13 @@
         <f>Exercise!D51</f>
         <v/>
       </c>
-      <c r="D51" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="9" t="n"/>
+      <c r="D51" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="17" t="n"/>
       <c r="G51" s="9" t="n"/>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
@@ -4960,13 +5178,13 @@
         <f>Exercise!D52</f>
         <v/>
       </c>
-      <c r="D52" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="9" t="n"/>
+      <c r="D52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="17" t="n"/>
       <c r="G52" s="9" t="n"/>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
@@ -4989,13 +5207,13 @@
         <f>Exercise!D53</f>
         <v/>
       </c>
-      <c r="D53" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="9" t="n"/>
+      <c r="D53" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="17" t="n"/>
       <c r="G53" s="9" t="n"/>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
@@ -5016,7 +5234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5105,14 +5323,14 @@
       </c>
       <c r="D2" s="30" t="inlineStr">
         <is>
-          <t>8.00/22.00</t>
+          <t>8.00/42.00</t>
         </is>
       </c>
       <c r="E2" s="32" t="n">
-        <v>36.36363636363637</v>
+        <v>19.04761904761905</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>25.45454545454546</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G2" s="30" t="inlineStr">
         <is>
@@ -5126,7 +5344,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="32" t="n">
-        <v>40.45454545454545</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="K2" s="30" t="inlineStr">
         <is>
@@ -5150,14 +5368,14 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>13.00/42.00</t>
         </is>
       </c>
       <c r="E3" s="32" t="n">
-        <v>0</v>
+        <v>30.95238095238095</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>0</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="G3" s="30" t="inlineStr">
         <is>
@@ -5171,7 +5389,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="32" t="n">
-        <v>15</v>
+        <v>36.66666666666667</v>
       </c>
       <c r="K3" s="30" t="inlineStr">
         <is>
@@ -5195,14 +5413,14 @@
       </c>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>8.00/42.00</t>
         </is>
       </c>
       <c r="E4" s="32" t="n">
-        <v>0</v>
+        <v>19.04761904761905</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G4" s="30" t="inlineStr">
         <is>
@@ -5216,7 +5434,7 @@
         <v>15</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>15</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="K4" s="30" t="inlineStr">
         <is>
@@ -5240,14 +5458,14 @@
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>26.00/42.00</t>
         </is>
       </c>
       <c r="E5" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="G5" s="30" t="inlineStr">
         <is>
@@ -5261,11 +5479,11 @@
         <v>30</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="K5" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
     </row>
@@ -5285,14 +5503,14 @@
       </c>
       <c r="D6" s="30" t="inlineStr">
         <is>
-          <t>7.00/22.00</t>
+          <t>7.00/42.00</t>
         </is>
       </c>
       <c r="E6" s="32" t="n">
-        <v>31.81818181818182</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>22.27272727272727</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G6" s="30" t="inlineStr">
         <is>
@@ -5306,7 +5524,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>52.27272727272727</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="K6" s="30" t="inlineStr">
         <is>
@@ -5330,7 +5548,7 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>0.00/42.00</t>
         </is>
       </c>
       <c r="E7" s="32" t="n">
@@ -5375,14 +5593,14 @@
       </c>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>9.00/42.00</t>
         </is>
       </c>
       <c r="E8" s="32" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G8" s="30" t="inlineStr">
         <is>
@@ -5396,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K8" s="30" t="inlineStr">
         <is>
@@ -5420,14 +5638,14 @@
       </c>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t>20.00/22.00</t>
+          <t>27.00/42.00</t>
         </is>
       </c>
       <c r="E9" s="32" t="n">
-        <v>90.90909090909091</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>45</v>
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
@@ -5441,11 +5659,11 @@
         <v>30</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>93.63636363636363</v>
+        <v>75</v>
       </c>
       <c r="K9" s="30" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
     </row>
@@ -5465,14 +5683,14 @@
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>10.00/22.00</t>
+          <t>22.00/42.00</t>
         </is>
       </c>
       <c r="E10" s="32" t="n">
-        <v>45.45454545454545</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>31.81818181818182</v>
+        <v>36.66666666666667</v>
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
@@ -5486,7 +5704,7 @@
         <v>30</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>61.81818181818181</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="K10" s="30" t="inlineStr">
         <is>
@@ -5510,14 +5728,14 @@
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>20.00/22.00</t>
+          <t>28.00/42.00</t>
         </is>
       </c>
       <c r="E11" s="32" t="n">
-        <v>90.90909090909091</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="G11" s="30" t="inlineStr">
         <is>
@@ -5531,11 +5749,11 @@
         <v>30</v>
       </c>
       <c r="J11" s="32" t="n">
-        <v>93.63636363636363</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="K11" s="30" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
     </row>
@@ -5555,14 +5773,14 @@
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>10.00/42.00</t>
         </is>
       </c>
       <c r="E12" s="32" t="n">
-        <v>0</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
@@ -5576,7 +5794,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>15</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="K12" s="30" t="inlineStr">
         <is>
@@ -5600,7 +5818,7 @@
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>0.00/42.00</t>
         </is>
       </c>
       <c r="E13" s="32" t="n">
@@ -5645,14 +5863,14 @@
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>21.00/22.00</t>
+          <t>30.00/42.00</t>
         </is>
       </c>
       <c r="E14" s="32" t="n">
-        <v>95.45454545454545</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>66.81818181818183</v>
+        <v>50</v>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
@@ -5666,11 +5884,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="32" t="n">
-        <v>66.81818181818183</v>
+        <v>50</v>
       </c>
       <c r="K14" s="30" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
@@ -5690,14 +5908,14 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>12.00/22.00</t>
+          <t>22.00/42.00</t>
         </is>
       </c>
       <c r="E15" s="32" t="n">
-        <v>54.54545454545454</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>38.18181818181818</v>
+        <v>36.66666666666667</v>
       </c>
       <c r="G15" s="30" t="inlineStr">
         <is>
@@ -5711,7 +5929,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="32" t="n">
-        <v>68.18181818181819</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="K15" s="30" t="inlineStr">
         <is>
@@ -5735,14 +5953,14 @@
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>17.00/22.00</t>
+          <t>34.00/42.00</t>
         </is>
       </c>
       <c r="E16" s="32" t="n">
-        <v>77.27272727272727</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>54.09090909090909</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="G16" s="30" t="inlineStr">
         <is>
@@ -5756,7 +5974,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>84.09090909090909</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="K16" s="30" t="inlineStr">
         <is>
@@ -5780,14 +5998,14 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>35.00/42.00</t>
         </is>
       </c>
       <c r="E17" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="G17" s="30" t="inlineStr">
         <is>
@@ -5801,7 +6019,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>88.33333333333334</v>
       </c>
       <c r="K17" s="30" t="inlineStr">
         <is>
@@ -5825,14 +6043,14 @@
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>38.00/42.00</t>
         </is>
       </c>
       <c r="E18" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
@@ -5846,11 +6064,11 @@
         <v>30</v>
       </c>
       <c r="J18" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>93.33333333333334</v>
       </c>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
     </row>
@@ -5870,14 +6088,14 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>13.00/22.00</t>
+          <t>25.00/42.00</t>
         </is>
       </c>
       <c r="E19" s="32" t="n">
-        <v>59.09090909090909</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>41.36363636363637</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="G19" s="30" t="inlineStr">
         <is>
@@ -5891,7 +6109,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>71.36363636363637</v>
+        <v>71.66666666666666</v>
       </c>
       <c r="K19" s="30" t="inlineStr">
         <is>
@@ -5915,14 +6133,14 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>22.00/22.00</t>
+          <t>37.00/42.00</t>
         </is>
       </c>
       <c r="E20" s="32" t="n">
-        <v>100</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>70</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
@@ -5936,7 +6154,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="32" t="n">
-        <v>100</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="K20" s="30" t="inlineStr">
         <is>
@@ -5960,14 +6178,14 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>7.00/22.00</t>
+          <t>22.00/42.00</t>
         </is>
       </c>
       <c r="E21" s="32" t="n">
-        <v>31.81818181818182</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>22.27272727272727</v>
+        <v>36.66666666666667</v>
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
@@ -5981,7 +6199,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>37.27272727272727</v>
+        <v>51.66666666666667</v>
       </c>
       <c r="K21" s="30" t="inlineStr">
         <is>
@@ -6005,14 +6223,14 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>14.00/22.00</t>
+          <t>18.00/42.00</t>
         </is>
       </c>
       <c r="E22" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>44.54545454545455</v>
+        <v>30</v>
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
@@ -6026,7 +6244,7 @@
         <v>15</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>59.54545454545455</v>
+        <v>45</v>
       </c>
       <c r="K22" s="30" t="inlineStr">
         <is>
@@ -6050,14 +6268,14 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>16.00/22.00</t>
+          <t>34.00/42.00</t>
         </is>
       </c>
       <c r="E23" s="32" t="n">
-        <v>72.72727272727273</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>50.90909090909091</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
@@ -6071,7 +6289,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="32" t="n">
-        <v>80.90909090909091</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="K23" s="30" t="inlineStr">
         <is>
@@ -6095,14 +6313,14 @@
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
-          <t>21.50/22.00</t>
+          <t>41.50/42.00</t>
         </is>
       </c>
       <c r="E24" s="32" t="n">
-        <v>97.72727272727273</v>
+        <v>98.80952380952381</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>68.40909090909091</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
@@ -6116,7 +6334,7 @@
         <v>30</v>
       </c>
       <c r="J24" s="32" t="n">
-        <v>98.40909090909091</v>
+        <v>99.16666666666667</v>
       </c>
       <c r="K24" s="30" t="inlineStr">
         <is>
@@ -6140,7 +6358,7 @@
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
-          <t>0.00/22.00</t>
+          <t>0.00/42.00</t>
         </is>
       </c>
       <c r="E25" s="32" t="n">
@@ -6185,14 +6403,14 @@
       </c>
       <c r="D26" s="30" t="inlineStr">
         <is>
-          <t>22.00/22.00</t>
+          <t>41.00/42.00</t>
         </is>
       </c>
       <c r="E26" s="32" t="n">
-        <v>100</v>
+        <v>97.61904761904762</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>70</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="G26" s="30" t="inlineStr">
         <is>
@@ -6206,7 +6424,7 @@
         <v>30</v>
       </c>
       <c r="J26" s="32" t="n">
-        <v>100</v>
+        <v>98.33333333333333</v>
       </c>
       <c r="K26" s="30" t="inlineStr">
         <is>
@@ -6230,14 +6448,14 @@
       </c>
       <c r="D27" s="30" t="inlineStr">
         <is>
-          <t>5.00/22.00</t>
+          <t>25.00/42.00</t>
         </is>
       </c>
       <c r="E27" s="32" t="n">
-        <v>22.72727272727273</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>15.90909090909091</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
@@ -6251,7 +6469,7 @@
         <v>15</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>30.90909090909091</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="K27" s="30" t="inlineStr">
         <is>
@@ -6275,14 +6493,14 @@
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
-          <t>12.00/22.00</t>
+          <t>26.00/42.00</t>
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>54.54545454545454</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>38.18181818181818</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
@@ -6296,7 +6514,7 @@
         <v>15</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>53.18181818181818</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="K28" s="30" t="inlineStr">
         <is>
@@ -6320,14 +6538,14 @@
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>38.00/42.00</t>
         </is>
       </c>
       <c r="E29" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="G29" s="30" t="inlineStr">
         <is>
@@ -6341,11 +6559,11 @@
         <v>30</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>93.33333333333334</v>
       </c>
       <c r="K29" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
     </row>
@@ -6365,14 +6583,14 @@
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
-          <t>19.00/22.00</t>
+          <t>37.00/42.00</t>
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>86.36363636363636</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>60.45454545454545</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
@@ -6386,7 +6604,7 @@
         <v>30</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>90.45454545454545</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="K30" s="30" t="inlineStr">
         <is>
@@ -6410,14 +6628,14 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>21.00/22.00</t>
+          <t>39.00/42.00</t>
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>95.45454545454545</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>66.81818181818183</v>
+        <v>65</v>
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
@@ -6431,7 +6649,7 @@
         <v>30</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>96.81818181818183</v>
+        <v>95</v>
       </c>
       <c r="K31" s="30" t="inlineStr">
         <is>
@@ -6455,14 +6673,14 @@
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
-          <t>10.00/22.00</t>
+          <t>20.00/42.00</t>
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>45.45454545454545</v>
+        <v>47.61904761904761</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
@@ -6476,7 +6694,7 @@
         <v>15</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>46.81818181818181</v>
+        <v>48.33333333333333</v>
       </c>
       <c r="K32" s="30" t="inlineStr">
         <is>
@@ -6500,7 +6718,7 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>22.00/22.00</t>
+          <t>42.00/42.00</t>
         </is>
       </c>
       <c r="E33" s="32" t="n">
@@ -6545,14 +6763,14 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>20.00/22.00</t>
+          <t>39.00/42.00</t>
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>90.90909090909091</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="F34" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>65</v>
       </c>
       <c r="G34" s="30" t="inlineStr">
         <is>
@@ -6566,7 +6784,7 @@
         <v>30</v>
       </c>
       <c r="J34" s="32" t="n">
-        <v>93.63636363636363</v>
+        <v>95</v>
       </c>
       <c r="K34" s="30" t="inlineStr">
         <is>
@@ -6590,14 +6808,14 @@
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
-          <t>20.00/22.00</t>
+          <t>39.00/42.00</t>
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>90.90909090909091</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="F35" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>65</v>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
@@ -6611,7 +6829,7 @@
         <v>30</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>93.63636363636363</v>
+        <v>95</v>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
@@ -6635,14 +6853,14 @@
       </c>
       <c r="D36" s="30" t="inlineStr">
         <is>
-          <t>17.00/22.00</t>
+          <t>34.00/42.00</t>
         </is>
       </c>
       <c r="E36" s="32" t="n">
-        <v>77.27272727272727</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>54.09090909090909</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
@@ -6656,7 +6874,7 @@
         <v>30</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>84.09090909090909</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="K36" s="30" t="inlineStr">
         <is>
@@ -6680,14 +6898,14 @@
       </c>
       <c r="D37" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>29.00/42.00</t>
         </is>
       </c>
       <c r="E37" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="F37" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
@@ -6701,11 +6919,11 @@
         <v>30</v>
       </c>
       <c r="J37" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>78.33333333333334</v>
       </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
     </row>
@@ -6725,14 +6943,14 @@
       </c>
       <c r="D38" s="30" t="inlineStr">
         <is>
-          <t>12.00/22.00</t>
+          <t>32.00/42.00</t>
         </is>
       </c>
       <c r="E38" s="32" t="n">
-        <v>54.54545454545454</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>38.18181818181818</v>
+        <v>53.33333333333333</v>
       </c>
       <c r="G38" s="30" t="inlineStr">
         <is>
@@ -6746,11 +6964,11 @@
         <v>30</v>
       </c>
       <c r="J38" s="32" t="n">
-        <v>68.18181818181819</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="K38" s="30" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
     </row>
@@ -6770,14 +6988,14 @@
       </c>
       <c r="D39" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>38.00/42.00</t>
         </is>
       </c>
       <c r="E39" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="G39" s="30" t="inlineStr">
         <is>
@@ -6791,11 +7009,11 @@
         <v>30</v>
       </c>
       <c r="J39" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>93.33333333333334</v>
       </c>
       <c r="K39" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
     </row>
@@ -6815,14 +7033,14 @@
       </c>
       <c r="D40" s="30" t="inlineStr">
         <is>
-          <t>8.00/22.00</t>
+          <t>26.00/42.00</t>
         </is>
       </c>
       <c r="E40" s="32" t="n">
-        <v>36.36363636363637</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>25.45454545454546</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
@@ -6836,11 +7054,11 @@
         <v>30</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>55.45454545454545</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="K40" s="30" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
     </row>
@@ -6860,14 +7078,14 @@
       </c>
       <c r="D41" s="30" t="inlineStr">
         <is>
-          <t>17.00/22.00</t>
+          <t>37.00/42.00</t>
         </is>
       </c>
       <c r="E41" s="32" t="n">
-        <v>77.27272727272727</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>54.09090909090909</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
@@ -6881,11 +7099,11 @@
         <v>30</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>84.09090909090909</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="K41" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
     </row>
@@ -6905,14 +7123,14 @@
       </c>
       <c r="D42" s="30" t="inlineStr">
         <is>
-          <t>17.00/22.00</t>
+          <t>35.00/42.00</t>
         </is>
       </c>
       <c r="E42" s="32" t="n">
-        <v>77.27272727272727</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>54.09090909090909</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
@@ -6926,7 +7144,7 @@
         <v>30</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>84.09090909090909</v>
+        <v>88.33333333333334</v>
       </c>
       <c r="K42" s="30" t="inlineStr">
         <is>
@@ -6950,14 +7168,14 @@
       </c>
       <c r="D43" s="30" t="inlineStr">
         <is>
-          <t>21.00/22.00</t>
+          <t>40.00/42.00</t>
         </is>
       </c>
       <c r="E43" s="32" t="n">
-        <v>95.45454545454545</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>66.81818181818183</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
@@ -6971,7 +7189,7 @@
         <v>30</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>96.81818181818183</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="K43" s="30" t="inlineStr">
         <is>
@@ -6995,14 +7213,14 @@
       </c>
       <c r="D44" s="30" t="inlineStr">
         <is>
-          <t>21.00/22.00</t>
+          <t>36.00/42.00</t>
         </is>
       </c>
       <c r="E44" s="32" t="n">
-        <v>95.45454545454545</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>66.81818181818183</v>
+        <v>60</v>
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
@@ -7016,7 +7234,7 @@
         <v>30</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>96.81818181818183</v>
+        <v>90</v>
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
@@ -7040,14 +7258,14 @@
       </c>
       <c r="D45" s="30" t="inlineStr">
         <is>
-          <t>14.00/22.00</t>
+          <t>34.00/42.00</t>
         </is>
       </c>
       <c r="E45" s="32" t="n">
-        <v>63.63636363636363</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>44.54545454545455</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
@@ -7061,11 +7279,11 @@
         <v>30</v>
       </c>
       <c r="J45" s="32" t="n">
-        <v>74.54545454545455</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="K45" s="30" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
     </row>
@@ -7085,14 +7303,14 @@
       </c>
       <c r="D46" s="30" t="inlineStr">
         <is>
-          <t>22.00/22.00</t>
+          <t>40.00/42.00</t>
         </is>
       </c>
       <c r="E46" s="32" t="n">
-        <v>100</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>70</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
@@ -7106,7 +7324,7 @@
         <v>30</v>
       </c>
       <c r="J46" s="32" t="n">
-        <v>100</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="K46" s="30" t="inlineStr">
         <is>
@@ -7130,14 +7348,14 @@
       </c>
       <c r="D47" s="30" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>37.00/42.00</t>
         </is>
       </c>
       <c r="E47" s="32" t="n">
-        <v>81.81818181818183</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>57.27272727272727</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
@@ -7151,56 +7369,91 @@
         <v>30</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>87.27272727272728</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="K47" s="30" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>Exercise maximum score</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>22</v>
+      <c r="B50" s="34" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>Exercise weight</t>
         </is>
       </c>
-      <c r="B51" s="33" t="n">
+      <c r="B51" s="35" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>Attendance sessions</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="34" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>Attendance weight</t>
         </is>
       </c>
-      <c r="B53" s="33" t="n">
+      <c r="B53" s="35" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="n"/>
+      <c r="B54" s="34" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>Mean Grand Total</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n">
+        <v>70.05434782608695</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>SD Grand Total (population)</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n">
+        <v>27.71512375871958</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10746" yWindow="0" windowWidth="11154" windowHeight="12192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="B1d\-mmm\-yy"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -54,6 +56,12 @@
       <name val="Carlito"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1" tint="0.0499893185216834"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -161,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,7 +212,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -215,15 +222,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,22 +247,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -336,7 +355,7 @@
       <col>3</col>
       <colOff>1313180</colOff>
       <row>5</row>
-      <rowOff>1422060</rowOff>
+      <rowOff>1420790</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -569,14 +588,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -593,7 +612,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="28" t="inlineStr">
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -647,8 +666,12 @@
           <t>Ex.5 Guassian vs Mercator</t>
         </is>
       </c>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t>Ex.6 Tissot Indicator</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="n"/>
       <c r="R6" s="10" t="n"/>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
@@ -2240,7 +2263,7 @@
         </is>
       </c>
       <c r="L30" s="17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M30" s="9" t="n">
         <v>10</v>
@@ -3335,7 +3358,9 @@
       <c r="M46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="N46" s="11" t="n"/>
+      <c r="N46" s="11" t="n">
+        <v>7</v>
+      </c>
       <c r="O46" s="9" t="n">
         <v>8</v>
       </c>
@@ -3745,7 +3770,7 @@
         <v>12</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N52" s="11" t="n">
         <v>10</v>
@@ -3861,9 +3886,9 @@
     <col width="6.94921875" customWidth="1" min="1" max="1"/>
     <col width="16.19921875" customWidth="1" min="2" max="2"/>
     <col width="31.046875" customWidth="1" min="3" max="3"/>
-    <col width="3.796875" customWidth="1" style="19" min="4" max="4"/>
+    <col width="3.796875" customWidth="1" style="18" min="4" max="4"/>
     <col width="3.796875" customWidth="1" min="5" max="5"/>
-    <col width="3.796875" customWidth="1" style="18" min="6" max="6"/>
+    <col width="3.796875" customWidth="1" style="26" min="6" max="6"/>
     <col width="3.796875" customWidth="1" min="7" max="14"/>
     <col width="8.796875" customWidth="1" min="15" max="15"/>
     <col width="4.6484375" customWidth="1" min="16" max="26"/>
@@ -3878,25 +3903,29 @@
           <t>การเข้าเรียน</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>04-14JUL69</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="25" t="n"/>
-      <c r="L6" s="25" t="n"/>
-      <c r="M6" s="25" t="n"/>
-      <c r="N6" s="25" t="n"/>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>06-10/8/1969</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="23" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -3911,17 +3940,17 @@
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="23" t="n"/>
-      <c r="I7" s="23" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -3936,11 +3965,13 @@
         <f>Exercise!D8</f>
         <v/>
       </c>
-      <c r="D8" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="17" t="n"/>
+      <c r="D8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
@@ -3963,11 +3994,11 @@
         <f>Exercise!D9</f>
         <v/>
       </c>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="28" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
@@ -3990,11 +4021,11 @@
         <f>Exercise!D10</f>
         <v/>
       </c>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="28" t="n"/>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
@@ -4017,13 +4048,15 @@
         <f>Exercise!D11</f>
         <v/>
       </c>
-      <c r="D11" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17" t="n"/>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
@@ -4046,13 +4079,15 @@
         <f>Exercise!D12</f>
         <v/>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17" t="n"/>
+      <c r="D12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
@@ -4075,11 +4110,11 @@
         <f>Exercise!D13</f>
         <v/>
       </c>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="28" t="n"/>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
@@ -4102,11 +4137,13 @@
         <f>Exercise!D14</f>
         <v/>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="17" t="n"/>
+      <c r="D14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
@@ -4129,13 +4166,15 @@
         <f>Exercise!D15</f>
         <v/>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17" t="n"/>
+      <c r="D15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4158,13 +4197,15 @@
         <f>Exercise!D16</f>
         <v/>
       </c>
-      <c r="D16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17" t="n"/>
+      <c r="D16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
@@ -4187,13 +4228,15 @@
         <f>Exercise!D17</f>
         <v/>
       </c>
-      <c r="D17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17" t="n"/>
+      <c r="D17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4216,11 +4259,13 @@
         <f>Exercise!D18</f>
         <v/>
       </c>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="17" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -4243,9 +4288,9 @@
         <f>Exercise!D19</f>
         <v/>
       </c>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="17" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="28" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
@@ -4268,9 +4313,11 @@
         <f>Exercise!D20</f>
         <v/>
       </c>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="17" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
@@ -4293,13 +4340,13 @@
         <f>Exercise!D21</f>
         <v/>
       </c>
-      <c r="D21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17" t="n"/>
+      <c r="D21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="28" t="n"/>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
@@ -4322,13 +4369,15 @@
         <f>Exercise!D22</f>
         <v/>
       </c>
-      <c r="D22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="17" t="n"/>
+      <c r="D22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
@@ -4351,13 +4400,15 @@
         <f>Exercise!D23</f>
         <v/>
       </c>
-      <c r="D23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17" t="n"/>
+      <c r="D23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
@@ -4380,13 +4431,15 @@
         <f>Exercise!D24</f>
         <v/>
       </c>
-      <c r="D24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17" t="n"/>
+      <c r="D24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
@@ -4409,13 +4462,15 @@
         <f>Exercise!D25</f>
         <v/>
       </c>
-      <c r="D25" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17" t="n"/>
+      <c r="D25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
@@ -4438,13 +4493,15 @@
         <f>Exercise!D26</f>
         <v/>
       </c>
-      <c r="D26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17" t="n"/>
+      <c r="D26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
@@ -4467,11 +4524,13 @@
         <f>Exercise!D27</f>
         <v/>
       </c>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="17" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
@@ -4494,11 +4553,13 @@
         <f>Exercise!D28</f>
         <v/>
       </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="17" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
@@ -4521,13 +4582,15 @@
         <f>Exercise!D29</f>
         <v/>
       </c>
-      <c r="D29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="17" t="n"/>
+      <c r="D29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
@@ -4550,13 +4613,15 @@
         <f>Exercise!D30</f>
         <v/>
       </c>
-      <c r="D30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="17" t="n"/>
+      <c r="D30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
@@ -4579,9 +4644,9 @@
         <f>Exercise!D31</f>
         <v/>
       </c>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="17" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
@@ -4604,13 +4669,15 @@
         <f>Exercise!D32</f>
         <v/>
       </c>
-      <c r="D32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="17" t="n"/>
+      <c r="D32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G32" s="9" t="n"/>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
@@ -4633,11 +4700,13 @@
         <f>Exercise!D33</f>
         <v/>
       </c>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="17" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G33" s="9" t="n"/>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
@@ -4660,11 +4729,15 @@
         <f>Exercise!D34</f>
         <v/>
       </c>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="17" t="n"/>
+      <c r="D34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G34" s="9" t="n"/>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
@@ -4687,13 +4760,15 @@
         <f>Exercise!D35</f>
         <v/>
       </c>
-      <c r="D35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="17" t="n"/>
+      <c r="D35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G35" s="9" t="n"/>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
@@ -4716,13 +4791,15 @@
         <f>Exercise!D36</f>
         <v/>
       </c>
-      <c r="D36" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17" t="n"/>
+      <c r="D36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
@@ -4745,13 +4822,15 @@
         <f>Exercise!D37</f>
         <v/>
       </c>
-      <c r="D37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="17" t="n"/>
+      <c r="D37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
@@ -4774,11 +4853,13 @@
         <f>Exercise!D38</f>
         <v/>
       </c>
-      <c r="D38" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="17" t="n"/>
+      <c r="D38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
@@ -4801,13 +4882,15 @@
         <f>Exercise!D39</f>
         <v/>
       </c>
-      <c r="D39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="17" t="n"/>
+      <c r="D39" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
@@ -4830,13 +4913,15 @@
         <f>Exercise!D40</f>
         <v/>
       </c>
-      <c r="D40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="17" t="n"/>
+      <c r="D40" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G40" s="9" t="n"/>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
@@ -4859,13 +4944,15 @@
         <f>Exercise!D41</f>
         <v/>
       </c>
-      <c r="D41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="17" t="n"/>
+      <c r="D41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
@@ -4888,13 +4975,15 @@
         <f>Exercise!D42</f>
         <v/>
       </c>
-      <c r="D42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="17" t="n"/>
+      <c r="D42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
@@ -4917,13 +5006,15 @@
         <f>Exercise!D43</f>
         <v/>
       </c>
-      <c r="D43" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="17" t="n"/>
+      <c r="D43" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
@@ -4946,13 +5037,15 @@
         <f>Exercise!D44</f>
         <v/>
       </c>
-      <c r="D44" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17" t="n"/>
+      <c r="D44" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
@@ -4975,13 +5068,15 @@
         <f>Exercise!D45</f>
         <v/>
       </c>
-      <c r="D45" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="17" t="n"/>
+      <c r="D45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G45" s="9" t="n"/>
       <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n"/>
@@ -5004,13 +5099,15 @@
         <f>Exercise!D46</f>
         <v/>
       </c>
-      <c r="D46" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="17" t="n"/>
+      <c r="D46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
@@ -5033,13 +5130,15 @@
         <f>Exercise!D47</f>
         <v/>
       </c>
-      <c r="D47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="17" t="n"/>
+      <c r="D47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G47" s="9" t="n"/>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
@@ -5062,13 +5161,15 @@
         <f>Exercise!D48</f>
         <v/>
       </c>
-      <c r="D48" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="17" t="n"/>
+      <c r="D48" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
@@ -5091,13 +5192,15 @@
         <f>Exercise!D49</f>
         <v/>
       </c>
-      <c r="D49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="17" t="n"/>
+      <c r="D49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
@@ -5120,13 +5223,15 @@
         <f>Exercise!D50</f>
         <v/>
       </c>
-      <c r="D50" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="17" t="n"/>
+      <c r="D50" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
@@ -5149,13 +5254,15 @@
         <f>Exercise!D51</f>
         <v/>
       </c>
-      <c r="D51" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="17" t="n"/>
+      <c r="D51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G51" s="9" t="n"/>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
@@ -5178,13 +5285,15 @@
         <f>Exercise!D52</f>
         <v/>
       </c>
-      <c r="D52" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="17" t="n"/>
+      <c r="D52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G52" s="9" t="n"/>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
@@ -5207,13 +5316,15 @@
         <f>Exercise!D53</f>
         <v/>
       </c>
-      <c r="D53" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="17" t="n"/>
+      <c r="D53" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="G53" s="9" t="n"/>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
@@ -5251,2204 +5362,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="A2" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>8.00/42.00</t>
         </is>
       </c>
-      <c r="E2" s="32" t="n">
+      <c r="E2" s="35" t="n">
         <v>19.04761904761905</v>
       </c>
-      <c r="F2" s="32" t="n">
+      <c r="F2" s="35" t="n">
         <v>13.33333333333333</v>
       </c>
-      <c r="G2" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H2" s="32" t="n">
+      <c r="G2" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H2" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I2" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>6610553165</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>13.00/42.00</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>30.95238095238095</v>
+      </c>
+      <c r="F3" s="35" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="G3" s="33" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="35" t="n">
+        <v>31.66666666666667</v>
+      </c>
+      <c r="K3" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>6610553173</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>8.00/42.00</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="F4" s="35" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="35" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>6610553181</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>26.00/42.00</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>61.90476190476191</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>7.00/42.00</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>0.00/42.00</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>9.00/42.00</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="K8" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>27.00/42.00</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>22.00/42.00</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>36.66666666666667</v>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>28.00/42.00</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>76.66666666666666</v>
+      </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>10.00/42.00</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>0.00/42.00</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>30.00/42.00</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="F14" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="I2" s="32" t="n">
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>22.00/42.00</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>36.66666666666667</v>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>56.66666666666667</v>
+      </c>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="32" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="K2" s="30" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>34.00/42.00</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>86.66666666666666</v>
+      </c>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>35.00/42.00</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>38.00/42.00</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>93.33333333333334</v>
+      </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>25.00/42.00</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>59.52380952380953</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>71.66666666666666</v>
+      </c>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>37.00/42.00</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>22.00/42.00</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>36.66666666666667</v>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>56.66666666666667</v>
+      </c>
+      <c r="K21" s="33" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>6610553165</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>13.00/42.00</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="n">
-        <v>30.95238095238095</v>
-      </c>
-      <c r="F3" s="32" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H3" s="32" t="n">
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>18.00/42.00</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="I3" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="32" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K22" s="33" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="n">
+    <row r="23">
+      <c r="A23" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>34.00/42.00</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>86.66666666666666</v>
+      </c>
+      <c r="K23" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>42.00/42.00</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>0.00/42.00</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="33" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>41.00/42.00</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="n">
+        <v>97.61904761904762</v>
+      </c>
+      <c r="F26" s="35" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>98.33333333333333</v>
+      </c>
+      <c r="K26" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>25.00/42.00</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="n">
+        <v>59.52380952380953</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="K27" s="33" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>26.00/42.00</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="n">
+        <v>61.90476190476191</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>38.00/42.00</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="n">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>93.33333333333334</v>
+      </c>
+      <c r="K29" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>37.00/42.00</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="n">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="F30" s="35" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="G30" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="35" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="K30" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>39.00/42.00</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="n">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="F31" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G31" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>95</v>
+      </c>
+      <c r="K31" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>20.00/42.00</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="n">
+        <v>47.61904761904761</v>
+      </c>
+      <c r="F32" s="35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G32" s="33" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="I32" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="35" t="n">
+        <v>53.33333333333333</v>
+      </c>
+      <c r="K32" s="33" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>42.00/42.00</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>39.00/42.00</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="F34" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G34" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="35" t="n">
+        <v>95</v>
+      </c>
+      <c r="K34" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>39.00/42.00</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="n">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="F35" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G35" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="35" t="n">
+        <v>95</v>
+      </c>
+      <c r="K35" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>34.00/42.00</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="n">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G36" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="35" t="n">
+        <v>86.66666666666666</v>
+      </c>
+      <c r="K36" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
+        <is>
+          <t>29.00/42.00</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="n">
+        <v>69.04761904761905</v>
+      </c>
+      <c r="F37" s="35" t="n">
+        <v>48.33333333333334</v>
+      </c>
+      <c r="G37" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J37" s="35" t="n">
+        <v>78.33333333333334</v>
+      </c>
+      <c r="K37" s="33" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>32.00/42.00</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="n">
+        <v>76.19047619047619</v>
+      </c>
+      <c r="F38" s="35" t="n">
+        <v>53.33333333333333</v>
+      </c>
+      <c r="G38" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="35" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="K38" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>38.00/42.00</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="n">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="F39" s="35" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="G39" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="35" t="n">
+        <v>93.33333333333334</v>
+      </c>
+      <c r="K39" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>33.00/42.00</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="n">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="F40" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="G40" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="35" t="n">
+        <v>85</v>
+      </c>
+      <c r="K40" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>37.00/42.00</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="n">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="G41" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="35" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="K41" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>35.00/42.00</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F42" s="35" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G42" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="35" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K42" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>40.00/42.00</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="n">
+        <v>95.23809523809523</v>
+      </c>
+      <c r="F43" s="35" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G43" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="35" t="n">
+        <v>96.66666666666666</v>
+      </c>
+      <c r="K43" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>36.00/42.00</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="F44" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="G44" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="K44" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>34.00/42.00</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="n">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="F45" s="35" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G45" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>86.66666666666666</v>
+      </c>
+      <c r="K45" s="33" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="inlineStr">
+        <is>
+          <t>42.00/42.00</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="G46" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K46" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="inlineStr">
+        <is>
+          <t>37.00/42.00</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="n">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="G47" s="33" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="35" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="K47" s="33" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="38" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t>6610553173</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="inlineStr">
-        <is>
-          <t>8.00/42.00</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="n">
-        <v>19.04761904761905</v>
-      </c>
-      <c r="F4" s="32" t="n">
-        <v>13.33333333333333</v>
-      </c>
-      <c r="G4" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H4" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="32" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="K4" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>6610553181</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="inlineStr">
-        <is>
-          <t>26.00/42.00</t>
-        </is>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>61.90476190476191</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G5" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" s="32" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="K5" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="inlineStr">
-        <is>
-          <t>7.00/42.00</t>
-        </is>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="F6" s="32" t="n">
-        <v>11.66666666666667</v>
-      </c>
-      <c r="G6" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="32" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H7" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
-        <is>
-          <t>9.00/42.00</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="F8" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H8" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>27.00/42.00</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="n">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="F9" s="32" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H9" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="32" t="n">
-        <v>75</v>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F10" s="32" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G10" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H10" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="32" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="K10" s="30" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="30" t="inlineStr">
-        <is>
-          <t>28.00/42.00</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="F11" s="32" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="G11" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H11" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="32" t="n">
-        <v>76.66666666666666</v>
-      </c>
-      <c r="K11" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>10.00/42.00</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="n">
-        <v>23.80952380952381</v>
-      </c>
-      <c r="F12" s="32" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H12" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="32" t="n">
-        <v>31.66666666666666</v>
-      </c>
-      <c r="K12" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="30" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
-        <is>
-          <t>30.00/42.00</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="F14" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" s="30" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="K14" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="30" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F15" s="32" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G15" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H15" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J15" s="32" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="30" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F16" s="32" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="32" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K16" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>35.00/42.00</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F17" s="32" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H17" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="32" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K17" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E18" s="32" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F18" s="32" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G18" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="32" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K18" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>25.00/42.00</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="n">
-        <v>59.52380952380953</v>
-      </c>
-      <c r="F19" s="32" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="G19" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H19" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="32" t="n">
-        <v>71.66666666666666</v>
-      </c>
-      <c r="K19" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="30" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E20" s="32" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F20" s="32" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G20" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H20" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="32" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K20" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F21" s="32" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G21" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H21" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I21" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="32" t="n">
-        <v>51.66666666666667</v>
-      </c>
-      <c r="K21" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>18.00/42.00</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="F22" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="G22" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I22" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="32" t="n">
-        <v>45</v>
-      </c>
-      <c r="K22" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F23" s="32" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G23" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H23" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="32" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K23" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>41.50/42.00</t>
-        </is>
-      </c>
-      <c r="E24" s="32" t="n">
-        <v>98.80952380952381</v>
-      </c>
-      <c r="F24" s="32" t="n">
-        <v>69.16666666666667</v>
-      </c>
-      <c r="G24" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H24" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="32" t="n">
-        <v>99.16666666666667</v>
-      </c>
-      <c r="K24" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="30" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="30" t="inlineStr">
-        <is>
-          <t>41.00/42.00</t>
-        </is>
-      </c>
-      <c r="E26" s="32" t="n">
-        <v>97.61904761904762</v>
-      </c>
-      <c r="F26" s="32" t="n">
-        <v>68.33333333333333</v>
-      </c>
-      <c r="G26" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H26" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="32" t="n">
-        <v>98.33333333333333</v>
-      </c>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="30" t="inlineStr">
-        <is>
-          <t>25.00/42.00</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="n">
-        <v>59.52380952380953</v>
-      </c>
-      <c r="F27" s="32" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H27" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I27" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="32" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="K27" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>26.00/42.00</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="n">
-        <v>61.90476190476191</v>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G28" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H28" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I28" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="32" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="K28" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F29" s="32" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G29" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H29" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="32" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K29" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F30" s="32" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H30" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="32" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K30" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F31" s="32" t="n">
-        <v>65</v>
-      </c>
-      <c r="G31" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H31" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="32" t="n">
-        <v>95</v>
-      </c>
-      <c r="K31" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>20.00/42.00</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="n">
-        <v>47.61904761904761</v>
-      </c>
-      <c r="F32" s="32" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H32" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I32" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="32" t="n">
-        <v>48.33333333333333</v>
-      </c>
-      <c r="K32" s="30" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>42.00/42.00</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" s="32" t="n">
-        <v>70</v>
-      </c>
-      <c r="G33" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H33" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E34" s="32" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F34" s="32" t="n">
-        <v>65</v>
-      </c>
-      <c r="G34" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H34" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="32" t="n">
-        <v>95</v>
-      </c>
-      <c r="K34" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F35" s="32" t="n">
-        <v>65</v>
-      </c>
-      <c r="G35" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H35" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="32" t="n">
-        <v>95</v>
-      </c>
-      <c r="K35" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="30" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F36" s="32" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G36" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H36" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="32" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K36" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="30" t="inlineStr">
-        <is>
-          <t>29.00/42.00</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="n">
-        <v>69.04761904761905</v>
-      </c>
-      <c r="F37" s="32" t="n">
-        <v>48.33333333333334</v>
-      </c>
-      <c r="G37" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H37" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="32" t="n">
-        <v>78.33333333333334</v>
-      </c>
-      <c r="K37" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="30" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="30" t="inlineStr">
-        <is>
-          <t>32.00/42.00</t>
-        </is>
-      </c>
-      <c r="E38" s="32" t="n">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="F38" s="32" t="n">
-        <v>53.33333333333333</v>
-      </c>
-      <c r="G38" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H38" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="32" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="K38" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="30" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="30" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F39" s="32" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G39" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H39" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="32" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K39" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="30" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="30" t="inlineStr">
-        <is>
-          <t>26.00/42.00</t>
-        </is>
-      </c>
-      <c r="E40" s="32" t="n">
-        <v>61.90476190476191</v>
-      </c>
-      <c r="F40" s="32" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G40" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H40" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="32" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="K40" s="30" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E41" s="32" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F41" s="32" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G41" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H41" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="32" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K41" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="30" t="inlineStr">
-        <is>
-          <t>35.00/42.00</t>
-        </is>
-      </c>
-      <c r="E42" s="32" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F42" s="32" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G42" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H42" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="32" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K42" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="30" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="30" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>40.00/42.00</t>
-        </is>
-      </c>
-      <c r="E43" s="32" t="n">
-        <v>95.23809523809523</v>
-      </c>
-      <c r="F43" s="32" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="G43" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H43" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="32" t="n">
-        <v>96.66666666666666</v>
-      </c>
-      <c r="K43" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="30" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="30" t="inlineStr">
-        <is>
-          <t>36.00/42.00</t>
-        </is>
-      </c>
-      <c r="E44" s="32" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="F44" s="32" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H44" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="32" t="n">
-        <v>90</v>
-      </c>
-      <c r="K44" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="30" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E45" s="32" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F45" s="32" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G45" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H45" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="32" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K45" s="30" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="30" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="30" t="inlineStr">
-        <is>
-          <t>40.00/42.00</t>
-        </is>
-      </c>
-      <c r="E46" s="32" t="n">
-        <v>95.23809523809523</v>
-      </c>
-      <c r="F46" s="32" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="G46" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H46" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="32" t="n">
-        <v>96.66666666666666</v>
-      </c>
-      <c r="K46" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="30" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="38" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36" t="n"/>
+      <c r="B54" s="37" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="36" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="30" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E47" s="32" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F47" s="32" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G47" s="30" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H47" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="32" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K47" s="30" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="33" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="34" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="33" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="35" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="33" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="33" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="35" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="33" t="n"/>
-      <c r="B54" s="34" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="33" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="34" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
-        <v>70.05434782608695</v>
+      <c r="B56" s="39" t="n">
+        <v>71.15942028985508</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
-        <v>27.71512375871958</v>
+      <c r="B57" s="39" t="n">
+        <v>27.59671085302526</v>
       </c>
     </row>
   </sheetData>

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-5780" windowWidth="28800" windowHeight="15200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -79,7 +79,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -105,7 +105,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.0499893185216834"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -169,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,7 +212,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
@@ -210,8 +221,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -228,29 +237,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,7 +391,7 @@
       <col>3</col>
       <colOff>1313180</colOff>
       <row>5</row>
-      <rowOff>1420790</rowOff>
+      <rowOff>1423330</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -580,22 +616,20 @@
     <col width="20.6484375" customWidth="1" min="4" max="4"/>
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
-    <col hidden="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" min="12" max="13"/>
-    <col width="4.6484375" customWidth="1" style="8" min="14" max="14"/>
-    <col width="4.6484375" customWidth="1" min="15" max="20"/>
+    <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
+    <col width="4.6484375" customWidth="1" style="33" min="12" max="20"/>
     <col width="10.796875" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -612,7 +646,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -646,32 +680,32 @@
           <t>สรุปทั้งหมด 46 คน สถานะ Drop ติด W  0 คน</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>Ex.2 Intro to Geodesy</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>EX.3 Draw Sphere/Spheroid</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>Ex.4 EFG for Sphere</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>Ex.5 Guassian vs Mercator</t>
         </is>
       </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="n"/>
+      <c r="Q6" s="12" t="n"/>
       <c r="R6" s="10" t="n"/>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
@@ -727,23 +761,25 @@
           <t>Email Office365</t>
         </is>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="12" t="n"/>
+      <c r="M7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="35" t="n"/>
+      <c r="R7" s="35" t="n"/>
+      <c r="S7" s="35" t="n"/>
+      <c r="T7" s="35" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
@@ -796,17 +832,17 @@
           <t>theerapat.ke@live.ku.th</t>
         </is>
       </c>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="9" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="10" t="n"/>
       <c r="N8" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="9" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
@@ -859,19 +895,19 @@
           <t>naphatson.nu@live.ku.th</t>
         </is>
       </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="9" t="n">
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="10" t="n">
         <v>3</v>
       </c>
       <c r="N9" s="11" t="n"/>
-      <c r="O9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="9" t="n"/>
+      <c r="O9" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
@@ -924,19 +960,21 @@
           <t>naraporn.ja@live.ku.th</t>
         </is>
       </c>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="9" t="n">
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="10" t="n">
         <v>3</v>
       </c>
       <c r="N10" s="11" t="n"/>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="9" t="n"/>
+      <c r="P10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
@@ -989,23 +1027,25 @@
           <t>bunyamin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="10" t="n">
         <v>3</v>
       </c>
       <c r="N11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="9" t="n"/>
+      <c r="P11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
@@ -1058,17 +1098,19 @@
           <t>panyanan.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="9" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="10" t="n"/>
       <c r="N12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="9" t="n"/>
-      <c r="T12" s="9" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
@@ -1121,15 +1163,15 @@
           <t>phinyada.sr@live.ku.th</t>
         </is>
       </c>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="9" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="10" t="n"/>
       <c r="N13" s="11" t="n"/>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="9" t="n"/>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="9" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
@@ -1182,19 +1224,21 @@
           <t>purin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L14" s="17" t="n"/>
-      <c r="M14" s="9" t="n">
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="10" t="n">
         <v>4</v>
       </c>
       <c r="N14" s="11" t="n"/>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="9" t="n"/>
-      <c r="S14" s="9" t="n"/>
-      <c r="T14" s="9" t="n"/>
+      <c r="P14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -1247,23 +1291,25 @@
           <t>ratchanon.sakh@live.ku.th</t>
         </is>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="10" t="n">
         <v>2</v>
       </c>
       <c r="N15" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="9" t="n"/>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="9" t="n"/>
+      <c r="P15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
@@ -1316,21 +1362,21 @@
           <t>worapon.pl@live.ku.th</t>
         </is>
       </c>
-      <c r="L16" s="17" t="n"/>
-      <c r="M16" s="9" t="n">
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="10" t="n">
         <v>7</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O16" s="9" t="n">
+      <c r="O16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="9" t="n"/>
-      <c r="T16" s="9" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
@@ -1383,23 +1429,25 @@
           <t>suphanat.chan@live.ku.th</t>
         </is>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="10" t="n">
         <v>3</v>
       </c>
       <c r="N17" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="9" t="n"/>
+      <c r="P17" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
@@ -1452,19 +1500,21 @@
           <t>settakamol.wa@live.ku.th</t>
         </is>
       </c>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="9" t="n">
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="10" t="n">
         <v>5</v>
       </c>
       <c r="N18" s="11" t="n"/>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="9" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="9" t="n"/>
+      <c r="P18" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
@@ -1517,15 +1567,15 @@
           <t>arisara.len@live.ku.th</t>
         </is>
       </c>
-      <c r="L19" s="17" t="n"/>
-      <c r="M19" s="9" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="10" t="n"/>
       <c r="N19" s="11" t="n"/>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="9" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="9" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
@@ -1578,23 +1628,25 @@
           <t>pattarapon.ditt@live.ku.th</t>
         </is>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="10" t="n">
         <v>4</v>
       </c>
       <c r="N20" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="9" t="n"/>
-      <c r="S20" s="9" t="n"/>
-      <c r="T20" s="9" t="n"/>
+      <c r="P20" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
@@ -1647,21 +1699,21 @@
           <t>pakin.saen@live.ku.th</t>
         </is>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="10" t="n">
         <v>5</v>
       </c>
       <c r="N21" s="11" t="n"/>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="9" t="n"/>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="9" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
@@ -1714,23 +1766,25 @@
           <t>kanol.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L22" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" s="9" t="n">
+      <c r="L22" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" s="10" t="n">
         <v>7</v>
       </c>
       <c r="N22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O22" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="9" t="n"/>
-      <c r="T22" s="9" t="n"/>
+      <c r="O22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
@@ -1783,23 +1837,25 @@
           <t>kamonnit.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="10" t="n">
         <v>7</v>
       </c>
       <c r="N23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O23" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="9" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="9" t="n"/>
+      <c r="O23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
@@ -1852,23 +1908,25 @@
           <t>krisskon.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N24" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O24" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="9" t="n"/>
-      <c r="S24" s="9" t="n"/>
-      <c r="T24" s="9" t="n"/>
+      <c r="O24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="10" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
@@ -1921,23 +1979,25 @@
           <t>kantiwat.ta@live.ku.th</t>
         </is>
       </c>
-      <c r="L25" s="17" t="n">
+      <c r="L25" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>7</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="9" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="9" t="n"/>
+      <c r="P25" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
@@ -1990,23 +2050,25 @@
           <t>kasemchoke.na@live.ku.th</t>
         </is>
       </c>
-      <c r="L26" s="17" t="n">
+      <c r="L26" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>5</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O26" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="9" t="n"/>
-      <c r="S26" s="9" t="n"/>
-      <c r="T26" s="9" t="n"/>
+      <c r="O26" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
@@ -2059,21 +2121,23 @@
           <t>jakkarin.in@live.ku.th</t>
         </is>
       </c>
-      <c r="L27" s="17" t="n">
+      <c r="L27" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="10" t="n">
         <v>5</v>
       </c>
       <c r="N27" s="11" t="n"/>
-      <c r="O27" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="9" t="n"/>
+      <c r="O27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
@@ -2126,21 +2190,21 @@
           <t>chanchao.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L28" s="17" t="n">
+      <c r="L28" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="9" t="n"/>
+      <c r="M28" s="10" t="n"/>
       <c r="N28" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="9" t="n"/>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
@@ -2193,23 +2257,25 @@
           <t>tikamporn.tr@live.ku.th</t>
         </is>
       </c>
-      <c r="L29" s="17" t="n">
+      <c r="L29" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>8</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O29" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="9" t="n"/>
+      <c r="O29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="5" t="inlineStr">
@@ -2262,23 +2328,25 @@
           <t>napapach.bu@live.ku.th</t>
         </is>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O30" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="9" t="n"/>
-      <c r="S30" s="9" t="n"/>
-      <c r="T30" s="9" t="n"/>
+      <c r="O30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="5" t="inlineStr">
@@ -2331,15 +2399,15 @@
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="17" t="n"/>
-      <c r="M31" s="9" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="10" t="n"/>
       <c r="N31" s="11" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="9" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
@@ -2392,23 +2460,25 @@
           <t>thanaphum.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L32" s="17" t="n">
+      <c r="L32" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="10" t="n">
         <v>9</v>
       </c>
       <c r="N32" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O32" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="9" t="n"/>
-      <c r="S32" s="9" t="n"/>
-      <c r="T32" s="9" t="n"/>
+      <c r="O32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
@@ -2461,88 +2531,92 @@
           <t>thanakon.r@live.ku.th</t>
         </is>
       </c>
-      <c r="L33" s="17" t="n">
+      <c r="L33" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N33" s="11" t="n"/>
-      <c r="O33" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="9" t="n"/>
-      <c r="S33" s="9" t="n"/>
-      <c r="T33" s="9" t="n"/>
+      <c r="O33" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>6710553094</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>นายธรรมกร เจริญพร</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>Mr. THAMMAKORN CHAROENPORN</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="29" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="29" t="inlineStr">
         <is>
           <t>thammakorn.c@ku.th</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="K34" s="30" t="inlineStr">
         <is>
           <t>thammakorn.c@live.ku.th</t>
         </is>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="11" t="n"/>
-      <c r="O34" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="9" t="n"/>
-      <c r="S34" s="9" t="n"/>
-      <c r="T34" s="9" t="n"/>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="31" t="n"/>
+      <c r="R34" s="31" t="n"/>
+      <c r="S34" s="31" t="n"/>
+      <c r="T34" s="31" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
@@ -2595,23 +2669,25 @@
           <t>thattawan.y@live.ku.th</t>
         </is>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O35" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="9" t="n"/>
+      <c r="O35" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="5" t="inlineStr">
@@ -2664,23 +2740,25 @@
           <t>nonthakorn.j@live.ku.th</t>
         </is>
       </c>
-      <c r="L36" s="17" t="n">
+      <c r="L36" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="10" t="n">
         <v>8</v>
       </c>
       <c r="N36" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O36" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="9" t="n"/>
-      <c r="S36" s="9" t="n"/>
-      <c r="T36" s="9" t="n"/>
+      <c r="O36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
@@ -2733,23 +2811,25 @@
           <t>naputrapee.a@live.ku.th</t>
         </is>
       </c>
-      <c r="L37" s="17" t="n">
+      <c r="L37" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>8</v>
       </c>
       <c r="N37" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O37" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="9" t="n"/>
+      <c r="O37" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
@@ -2802,21 +2882,23 @@
           <t>pichayut.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L38" s="17" t="n"/>
-      <c r="M38" s="9" t="n">
+      <c r="L38" s="36" t="n"/>
+      <c r="M38" s="10" t="n">
         <v>5</v>
       </c>
       <c r="N38" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
-      <c r="R38" s="9" t="n"/>
-      <c r="S38" s="9" t="n"/>
-      <c r="T38" s="9" t="n"/>
+      <c r="P38" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="5" t="inlineStr">
@@ -2869,23 +2951,25 @@
           <t>pakhawat.p@live.ku.th</t>
         </is>
       </c>
-      <c r="L39" s="17" t="n">
+      <c r="L39" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N39" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O39" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
-      <c r="T39" s="9" t="n"/>
+      <c r="O39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="5" t="inlineStr">
@@ -2938,23 +3022,25 @@
           <t>phakkaphon.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L40" s="17" t="n">
+      <c r="L40" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="10" t="n">
         <v>9</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="O40" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
-      <c r="R40" s="9" t="n"/>
-      <c r="S40" s="9" t="n"/>
-      <c r="T40" s="9" t="n"/>
+      <c r="O40" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P40" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
@@ -3007,23 +3093,25 @@
           <t>pakkapon.i@live.ku.th</t>
         </is>
       </c>
-      <c r="L41" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M41" s="9" t="n">
+      <c r="L41" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M41" s="10" t="n">
         <v>9</v>
       </c>
       <c r="N41" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O41" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="9" t="n"/>
+      <c r="O41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
@@ -3076,23 +3164,23 @@
           <t>yuttana.sukku@live.ku.th</t>
         </is>
       </c>
-      <c r="L42" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M42" s="9" t="n">
+      <c r="L42" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>7</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O42" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="9" t="n"/>
-      <c r="S42" s="9" t="n"/>
-      <c r="T42" s="9" t="n"/>
+      <c r="O42" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="5" t="inlineStr">
@@ -3145,23 +3233,25 @@
           <t>rapeepat.mo@live.ku.th</t>
         </is>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L43" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="10" t="n">
         <v>6</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
-      <c r="T43" s="9" t="n"/>
+      <c r="P43" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="5" t="inlineStr">
@@ -3214,23 +3304,25 @@
           <t>veerapat.d@live.ku.th</t>
         </is>
       </c>
-      <c r="L44" s="17" t="n">
+      <c r="L44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O44" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
-      <c r="R44" s="9" t="n"/>
-      <c r="S44" s="9" t="n"/>
-      <c r="T44" s="9" t="n"/>
+      <c r="O44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="5" t="inlineStr">
@@ -3283,23 +3375,25 @@
           <t>savita.cha@live.ku.th</t>
         </is>
       </c>
-      <c r="L45" s="17" t="n">
+      <c r="L45" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O45" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
-      <c r="T45" s="9" t="n"/>
+      <c r="O45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="5" t="inlineStr">
@@ -3352,23 +3446,25 @@
           <t>sorasak.cot@live.ku.th</t>
         </is>
       </c>
-      <c r="L46" s="17" t="n">
+      <c r="L46" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
-      <c r="R46" s="9" t="n"/>
-      <c r="S46" s="9" t="n"/>
-      <c r="T46" s="9" t="n"/>
+      <c r="P46" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="5" t="inlineStr">
@@ -3421,23 +3517,25 @@
           <t>sarawut.ya@live.ku.th</t>
         </is>
       </c>
-      <c r="L47" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M47" s="9" t="n">
+      <c r="L47" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N47" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O47" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
-      <c r="T47" s="9" t="n"/>
+      <c r="O47" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P47" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="5" t="inlineStr">
@@ -3490,23 +3588,25 @@
           <t>sitthichailoet.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L48" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M48" s="9" t="n">
+      <c r="L48" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" s="10" t="n">
         <v>8</v>
       </c>
       <c r="N48" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O48" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
-      <c r="R48" s="9" t="n"/>
-      <c r="S48" s="9" t="n"/>
-      <c r="T48" s="9" t="n"/>
+      <c r="O48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="5" t="inlineStr">
@@ -3559,23 +3659,25 @@
           <t>sutichode.b@live.ku.th</t>
         </is>
       </c>
-      <c r="L49" s="17" t="n">
+      <c r="L49" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M49" s="9" t="n">
+      <c r="M49" s="10" t="n">
         <v>9</v>
       </c>
       <c r="N49" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O49" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="9" t="n"/>
+      <c r="O49" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P49" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="5" t="inlineStr">
@@ -3628,23 +3730,25 @@
           <t>sumath.o@live.ku.th</t>
         </is>
       </c>
-      <c r="L50" s="17" t="n">
+      <c r="L50" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="M50" s="9" t="n">
+      <c r="M50" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N50" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O50" s="9" t="n">
+      <c r="O50" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
-      <c r="R50" s="9" t="n"/>
-      <c r="S50" s="9" t="n"/>
-      <c r="T50" s="9" t="n"/>
+      <c r="P50" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="5" t="inlineStr">
@@ -3697,23 +3801,23 @@
           <t>aussanee.ko@live.ku.th</t>
         </is>
       </c>
-      <c r="L51" s="17" t="n">
+      <c r="L51" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N51" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="O51" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="9" t="n"/>
+      <c r="O51" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
@@ -3766,23 +3870,25 @@
           <t>atitaya.thai@live.ku.th</t>
         </is>
       </c>
-      <c r="L52" s="17" t="n">
+      <c r="L52" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="M52" s="9" t="n">
+      <c r="M52" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N52" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O52" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="9" t="n"/>
+      <c r="O52" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P52" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
@@ -3835,23 +3941,25 @@
           <t>araya.sansu@live.ku.th</t>
         </is>
       </c>
-      <c r="L53" s="17" t="n">
+      <c r="L53" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="M53" s="9" t="n">
+      <c r="M53" s="10" t="n">
         <v>9</v>
       </c>
       <c r="N53" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O53" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="9" t="n"/>
+      <c r="O53" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P53" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
     </row>
     <row r="54"/>
     <row r="55"/>
@@ -3886,10 +3994,11 @@
     <col width="6.94921875" customWidth="1" min="1" max="1"/>
     <col width="16.19921875" customWidth="1" min="2" max="2"/>
     <col width="31.046875" customWidth="1" min="3" max="3"/>
-    <col width="3.796875" customWidth="1" style="18" min="4" max="4"/>
+    <col width="3.796875" customWidth="1" style="15" min="4" max="4"/>
     <col width="3.796875" customWidth="1" min="5" max="5"/>
-    <col width="3.796875" customWidth="1" style="26" min="6" max="6"/>
-    <col width="3.796875" customWidth="1" min="7" max="14"/>
+    <col width="3.796875" customWidth="1" style="21" min="6" max="6"/>
+    <col width="3.796875" customWidth="1" style="24" min="7" max="7"/>
+    <col width="3.796875" customWidth="1" min="8" max="14"/>
     <col width="8.796875" customWidth="1" min="15" max="15"/>
     <col width="4.6484375" customWidth="1" min="16" max="26"/>
   </cols>
@@ -3903,29 +4012,33 @@
           <t>การเข้าเรียน</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>04-14JUL69</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n"/>
-      <c r="I6" s="23" t="n"/>
-      <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="23" t="n"/>
-      <c r="M6" s="23" t="n"/>
-      <c r="N6" s="23" t="n"/>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>24-Aug-2026\</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -3940,17 +4053,17 @@
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="25" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
       <c r="F7" s="27" t="n"/>
-      <c r="G7" s="25" t="n"/>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
-      <c r="J7" s="25" t="n"/>
-      <c r="K7" s="25" t="n"/>
-      <c r="L7" s="25" t="n"/>
-      <c r="M7" s="25" t="n"/>
-      <c r="N7" s="25" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="n"/>
+      <c r="N7" s="26" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -3965,14 +4078,14 @@
         <f>Exercise!D8</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="D8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
@@ -3994,12 +4107,14 @@
         <f>Exercise!D9</f>
         <v/>
       </c>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -4021,12 +4136,12 @@
         <f>Exercise!D10</f>
         <v/>
       </c>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="25" t="n"/>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
@@ -4048,16 +4163,18 @@
         <f>Exercise!D11</f>
         <v/>
       </c>
-      <c r="D11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="9" t="n"/>
+      <c r="D11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -4079,16 +4196,18 @@
         <f>Exercise!D12</f>
         <v/>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9" t="n"/>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
@@ -4110,12 +4229,14 @@
         <f>Exercise!D13</f>
         <v/>
       </c>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -4137,14 +4258,16 @@
         <f>Exercise!D14</f>
         <v/>
       </c>
-      <c r="D14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9" t="n"/>
+      <c r="D14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
@@ -4166,16 +4289,18 @@
         <f>Exercise!D15</f>
         <v/>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="9" t="n"/>
+      <c r="D15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
@@ -4197,16 +4322,18 @@
         <f>Exercise!D16</f>
         <v/>
       </c>
-      <c r="D16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9" t="n"/>
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
@@ -4228,16 +4355,18 @@
         <f>Exercise!D17</f>
         <v/>
       </c>
-      <c r="D17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9" t="n"/>
+      <c r="D17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
@@ -4259,14 +4388,16 @@
         <f>Exercise!D18</f>
         <v/>
       </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
@@ -4288,10 +4419,12 @@
         <f>Exercise!D19</f>
         <v/>
       </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="9" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
@@ -4313,12 +4446,14 @@
         <f>Exercise!D20</f>
         <v/>
       </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
@@ -4340,14 +4475,14 @@
         <f>Exercise!D21</f>
         <v/>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="9" t="n"/>
+      <c r="D21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="25" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
@@ -4369,16 +4504,18 @@
         <f>Exercise!D22</f>
         <v/>
       </c>
-      <c r="D22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9" t="n"/>
+      <c r="D22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
@@ -4400,16 +4537,18 @@
         <f>Exercise!D23</f>
         <v/>
       </c>
-      <c r="D23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9" t="n"/>
+      <c r="D23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
@@ -4431,16 +4570,18 @@
         <f>Exercise!D24</f>
         <v/>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9" t="n"/>
+      <c r="D24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
@@ -4462,16 +4603,18 @@
         <f>Exercise!D25</f>
         <v/>
       </c>
-      <c r="D25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="9" t="n"/>
+      <c r="D25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
@@ -4493,16 +4636,18 @@
         <f>Exercise!D26</f>
         <v/>
       </c>
-      <c r="D26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="9" t="n"/>
+      <c r="D26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
@@ -4524,14 +4669,16 @@
         <f>Exercise!D27</f>
         <v/>
       </c>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="9" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
@@ -4553,14 +4700,16 @@
         <f>Exercise!D28</f>
         <v/>
       </c>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="9" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="J28" s="9" t="n"/>
@@ -4582,16 +4731,18 @@
         <f>Exercise!D29</f>
         <v/>
       </c>
-      <c r="D29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="9" t="n"/>
+      <c r="D29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
       <c r="J29" s="9" t="n"/>
@@ -4613,16 +4764,18 @@
         <f>Exercise!D30</f>
         <v/>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9" t="n"/>
+      <c r="D30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="9" t="n"/>
@@ -4644,10 +4797,10 @@
         <f>Exercise!D31</f>
         <v/>
       </c>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="9" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="25" t="n"/>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
       <c r="J31" s="9" t="n"/>
@@ -4669,16 +4822,18 @@
         <f>Exercise!D32</f>
         <v/>
       </c>
-      <c r="D32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="9" t="n"/>
+      <c r="D32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
       <c r="J32" s="9" t="n"/>
@@ -4700,14 +4855,16 @@
         <f>Exercise!D33</f>
         <v/>
       </c>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="9" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
@@ -4729,16 +4886,18 @@
         <f>Exercise!D34</f>
         <v/>
       </c>
-      <c r="D34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="9" t="n"/>
+      <c r="D34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
@@ -4760,16 +4919,18 @@
         <f>Exercise!D35</f>
         <v/>
       </c>
-      <c r="D35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="9" t="n"/>
+      <c r="D35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="9" t="n"/>
@@ -4791,16 +4952,18 @@
         <f>Exercise!D36</f>
         <v/>
       </c>
-      <c r="D36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="9" t="n"/>
+      <c r="D36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
@@ -4822,16 +4985,18 @@
         <f>Exercise!D37</f>
         <v/>
       </c>
-      <c r="D37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9" t="n"/>
+      <c r="D37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="9" t="n"/>
@@ -4853,14 +5018,16 @@
         <f>Exercise!D38</f>
         <v/>
       </c>
-      <c r="D38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9" t="n"/>
+      <c r="D38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
@@ -4882,16 +5049,18 @@
         <f>Exercise!D39</f>
         <v/>
       </c>
-      <c r="D39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9" t="n"/>
+      <c r="D39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
       <c r="J39" s="9" t="n"/>
@@ -4913,16 +5082,18 @@
         <f>Exercise!D40</f>
         <v/>
       </c>
-      <c r="D40" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9" t="n"/>
+      <c r="D40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="9" t="n"/>
@@ -4944,16 +5115,18 @@
         <f>Exercise!D41</f>
         <v/>
       </c>
-      <c r="D41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="9" t="n"/>
+      <c r="D41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="n"/>
@@ -4975,16 +5148,18 @@
         <f>Exercise!D42</f>
         <v/>
       </c>
-      <c r="D42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9" t="n"/>
+      <c r="D42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="n"/>
@@ -5006,16 +5181,18 @@
         <f>Exercise!D43</f>
         <v/>
       </c>
-      <c r="D43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9" t="n"/>
+      <c r="D43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
       <c r="J43" s="9" t="n"/>
@@ -5037,16 +5214,18 @@
         <f>Exercise!D44</f>
         <v/>
       </c>
-      <c r="D44" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="9" t="n"/>
+      <c r="D44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="9" t="n"/>
@@ -5068,16 +5247,18 @@
         <f>Exercise!D45</f>
         <v/>
       </c>
-      <c r="D45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="9" t="n"/>
+      <c r="D45" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n"/>
       <c r="J45" s="9" t="n"/>
@@ -5099,16 +5280,18 @@
         <f>Exercise!D46</f>
         <v/>
       </c>
-      <c r="D46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="9" t="n"/>
+      <c r="D46" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
       <c r="J46" s="9" t="n"/>
@@ -5130,16 +5313,18 @@
         <f>Exercise!D47</f>
         <v/>
       </c>
-      <c r="D47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="9" t="n"/>
+      <c r="D47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
       <c r="J47" s="9" t="n"/>
@@ -5161,16 +5346,18 @@
         <f>Exercise!D48</f>
         <v/>
       </c>
-      <c r="D48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="9" t="n"/>
+      <c r="D48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="9" t="n"/>
@@ -5192,16 +5379,18 @@
         <f>Exercise!D49</f>
         <v/>
       </c>
-      <c r="D49" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="9" t="n"/>
+      <c r="D49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
       <c r="J49" s="9" t="n"/>
@@ -5223,16 +5412,18 @@
         <f>Exercise!D50</f>
         <v/>
       </c>
-      <c r="D50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="9" t="n"/>
+      <c r="D50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
       <c r="J50" s="9" t="n"/>
@@ -5254,16 +5445,18 @@
         <f>Exercise!D51</f>
         <v/>
       </c>
-      <c r="D51" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="9" t="n"/>
+      <c r="D51" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
       <c r="J51" s="9" t="n"/>
@@ -5285,16 +5478,18 @@
         <f>Exercise!D52</f>
         <v/>
       </c>
-      <c r="D52" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="9" t="n"/>
+      <c r="D52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="n"/>
@@ -5316,16 +5511,18 @@
         <f>Exercise!D53</f>
         <v/>
       </c>
-      <c r="D53" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="9" t="n"/>
+      <c r="D53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
       <c r="J53" s="9" t="n"/>
@@ -5362,2204 +5559,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="32" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="32" t="inlineStr">
+      <c r="C1" s="38" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="32" t="inlineStr">
+      <c r="D1" s="38" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="32" t="inlineStr">
+      <c r="E1" s="38" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="32" t="inlineStr">
+      <c r="F1" s="38" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="32" t="inlineStr">
+      <c r="G1" s="38" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="32" t="inlineStr">
+      <c r="H1" s="38" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="32" t="inlineStr">
+      <c r="I1" s="38" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="32" t="inlineStr">
+      <c r="J1" s="38" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="32" t="inlineStr">
+      <c r="K1" s="38" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="A2" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="40" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
-        <is>
-          <t>8.00/42.00</t>
-        </is>
-      </c>
-      <c r="E2" s="35" t="n">
-        <v>19.04761904761905</v>
-      </c>
-      <c r="F2" s="35" t="n">
-        <v>13.33333333333333</v>
-      </c>
-      <c r="G2" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H2" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I2" s="35" t="n">
+      <c r="D2" s="39" t="inlineStr">
+        <is>
+          <t>8.00/52.00</t>
+        </is>
+      </c>
+      <c r="E2" s="41" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="F2" s="41" t="n">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="G2" s="39" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H2" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" s="41" t="n">
+        <v>25.76923076923077</v>
+      </c>
+      <c r="K2" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>6610553165</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="inlineStr">
+        <is>
+          <t>13.00/52.00</t>
+        </is>
+      </c>
+      <c r="E3" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" s="41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H3" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" s="41" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>6610553173</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>16.00/52.00</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="F4" s="41" t="n">
+        <v>21.53846153846154</v>
+      </c>
+      <c r="G4" s="39" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" s="41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J4" s="41" t="n">
+        <v>29.03846153846154</v>
+      </c>
+      <c r="K4" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>6610553181</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>35.00/52.00</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="F5" s="41" t="n">
+        <v>47.11538461538462</v>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="41" t="n">
+        <v>77.11538461538461</v>
+      </c>
+      <c r="K5" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>17.00/52.00</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>32.69230769230769</v>
+      </c>
+      <c r="F6" s="41" t="n">
+        <v>22.88461538461538</v>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H6" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="41" t="n">
+        <v>52.88461538461539</v>
+      </c>
+      <c r="K6" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>0.00/52.00</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H7" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>17.00/52.00</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="n">
+        <v>32.69230769230769</v>
+      </c>
+      <c r="F8" s="41" t="n">
+        <v>22.88461538461538</v>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I8" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J8" s="41" t="n">
+        <v>45.38461538461539</v>
+      </c>
+      <c r="K8" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>35.00/52.00</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="F9" s="41" t="n">
+        <v>47.11538461538462</v>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="41" t="n">
+        <v>77.11538461538461</v>
+      </c>
+      <c r="K9" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>22.00/52.00</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>42.30769230769231</v>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>29.61538461538462</v>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="41" t="n">
+        <v>59.61538461538461</v>
+      </c>
+      <c r="K10" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>38.00/52.00</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>73.07692307692307</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>51.15384615384615</v>
+      </c>
+      <c r="G11" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="41" t="n">
+        <v>81.15384615384616</v>
+      </c>
+      <c r="K11" s="39" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>19.00/52.00</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>36.53846153846153</v>
+      </c>
+      <c r="F12" s="41" t="n">
+        <v>25.57692307692308</v>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H12" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>48.07692307692308</v>
+      </c>
+      <c r="K12" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t>0.00/52.00</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" s="41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K13" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>40.00/52.00</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="F14" s="41" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H14" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="41" t="n">
+        <v>68.84615384615384</v>
+      </c>
+      <c r="K14" s="39" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>22.00/52.00</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="n">
+        <v>42.30769230769231</v>
+      </c>
+      <c r="F15" s="41" t="n">
+        <v>29.61538461538462</v>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="41" t="n">
+        <v>44.61538461538461</v>
+      </c>
+      <c r="K15" s="39" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>44.00/52.00</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="n">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="F16" s="41" t="n">
+        <v>59.23076923076923</v>
+      </c>
+      <c r="G16" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H16" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="41" t="n">
+        <v>89.23076923076923</v>
+      </c>
+      <c r="K16" s="39" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>45.00/52.00</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="n">
+        <v>86.53846153846155</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <v>60.57692307692308</v>
+      </c>
+      <c r="G17" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H17" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="41" t="n">
+        <v>90.57692307692308</v>
+      </c>
+      <c r="K17" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>48.00/52.00</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="F18" s="41" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H18" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="41" t="n">
+        <v>94.61538461538461</v>
+      </c>
+      <c r="K18" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>35.00/52.00</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="F19" s="41" t="n">
+        <v>47.11538461538462</v>
+      </c>
+      <c r="G19" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H19" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="41" t="n">
+        <v>77.11538461538461</v>
+      </c>
+      <c r="K19" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>47.00/52.00</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="n">
+        <v>90.38461538461539</v>
+      </c>
+      <c r="F20" s="41" t="n">
+        <v>63.26923076923077</v>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H20" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="41" t="n">
+        <v>93.26923076923077</v>
+      </c>
+      <c r="K20" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="J2" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="K2" s="33" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>32.00/52.00</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="n">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>43.07692307692308</v>
+      </c>
+      <c r="G21" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J21" s="41" t="n">
+        <v>65.57692307692308</v>
+      </c>
+      <c r="K21" s="39" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>18.00/52.00</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="n">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="F22" s="41" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="G22" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H22" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J22" s="41" t="n">
+        <v>46.73076923076923</v>
+      </c>
+      <c r="K22" s="39" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>6610553165</t>
-        </is>
-      </c>
-      <c r="C3" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="39" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
-        <is>
-          <t>13.00/42.00</t>
-        </is>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>30.95238095238095</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="G3" s="33" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="I3" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="35" t="n">
-        <v>31.66666666666667</v>
-      </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="D23" s="39" t="inlineStr">
+        <is>
+          <t>44.00/52.00</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="n">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="F23" s="41" t="n">
+        <v>59.23076923076923</v>
+      </c>
+      <c r="G23" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="41" t="n">
+        <v>89.23076923076923</v>
+      </c>
+      <c r="K23" s="39" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>52.00/52.00</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="41" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H24" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>0.00/52.00</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="39" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="33" t="inlineStr">
-        <is>
-          <t>6610553173</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="39" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
-        <is>
-          <t>8.00/42.00</t>
-        </is>
-      </c>
-      <c r="E4" s="35" t="n">
-        <v>19.04761904761905</v>
-      </c>
-      <c r="F4" s="35" t="n">
-        <v>13.33333333333333</v>
-      </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="I4" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="35" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="K4" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>51.00/52.00</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>98.07692307692307</v>
+      </c>
+      <c r="F26" s="41" t="n">
+        <v>68.65384615384615</v>
+      </c>
+      <c r="G26" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H26" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="41" t="n">
+        <v>98.65384615384615</v>
+      </c>
+      <c r="K26" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>35.00/52.00</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="F27" s="41" t="n">
+        <v>47.11538461538462</v>
+      </c>
+      <c r="G27" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H27" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I27" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J27" s="41" t="n">
+        <v>69.61538461538461</v>
+      </c>
+      <c r="K27" s="39" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>36.00/52.00</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="F28" s="41" t="n">
+        <v>48.46153846153846</v>
+      </c>
+      <c r="G28" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="41" t="n">
+        <v>78.46153846153845</v>
+      </c>
+      <c r="K28" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="inlineStr">
+        <is>
+          <t>48.00/52.00</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="F29" s="41" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="G29" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H29" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="41" t="n">
+        <v>94.61538461538461</v>
+      </c>
+      <c r="K29" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>47.00/52.00</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="n">
+        <v>90.38461538461539</v>
+      </c>
+      <c r="F30" s="41" t="n">
+        <v>63.26923076923077</v>
+      </c>
+      <c r="G30" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H30" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="41" t="n">
+        <v>93.26923076923077</v>
+      </c>
+      <c r="K30" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="inlineStr">
+        <is>
+          <t>48.00/52.00</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="F31" s="41" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="G31" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H31" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="41" t="n">
+        <v>94.61538461538461</v>
+      </c>
+      <c r="K31" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="inlineStr">
+        <is>
+          <t>30.00/52.00</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>57.69230769230769</v>
+      </c>
+      <c r="F32" s="41" t="n">
+        <v>40.38461538461538</v>
+      </c>
+      <c r="G32" s="39" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H32" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="I32" s="41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J32" s="41" t="n">
+        <v>62.88461538461538</v>
+      </c>
+      <c r="K32" s="39" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="inlineStr">
+        <is>
+          <t>52.00/52.00</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="41" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H33" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>49.00/52.00</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="n">
+        <v>94.23076923076923</v>
+      </c>
+      <c r="F34" s="41" t="n">
+        <v>65.96153846153847</v>
+      </c>
+      <c r="G34" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H34" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="41" t="n">
+        <v>95.96153846153847</v>
+      </c>
+      <c r="K34" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="inlineStr">
+        <is>
+          <t>49.00/52.00</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="n">
+        <v>94.23076923076923</v>
+      </c>
+      <c r="F35" s="41" t="n">
+        <v>65.96153846153847</v>
+      </c>
+      <c r="G35" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H35" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="41" t="n">
+        <v>95.96153846153847</v>
+      </c>
+      <c r="K35" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>34.00/52.00</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="n">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="F36" s="41" t="n">
+        <v>45.76923076923077</v>
+      </c>
+      <c r="G36" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H36" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="41" t="n">
+        <v>75.76923076923077</v>
+      </c>
+      <c r="K36" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D37" s="39" t="inlineStr">
+        <is>
+          <t>38.00/52.00</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="n">
+        <v>73.07692307692307</v>
+      </c>
+      <c r="F37" s="41" t="n">
+        <v>51.15384615384615</v>
+      </c>
+      <c r="G37" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J37" s="41" t="n">
+        <v>81.15384615384616</v>
+      </c>
+      <c r="K37" s="39" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>37.00/52.00</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="n">
+        <v>71.15384615384616</v>
+      </c>
+      <c r="F38" s="41" t="n">
+        <v>49.80769230769231</v>
+      </c>
+      <c r="G38" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H38" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="41" t="n">
+        <v>79.80769230769231</v>
+      </c>
+      <c r="K38" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="inlineStr">
+        <is>
+          <t>47.00/52.00</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="n">
+        <v>90.38461538461539</v>
+      </c>
+      <c r="F39" s="41" t="n">
+        <v>63.26923076923077</v>
+      </c>
+      <c r="G39" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H39" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="41" t="n">
+        <v>93.26923076923077</v>
+      </c>
+      <c r="K39" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="39" t="inlineStr">
+        <is>
+          <t>43.00/52.00</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="n">
+        <v>82.69230769230769</v>
+      </c>
+      <c r="F40" s="41" t="n">
+        <v>57.88461538461538</v>
+      </c>
+      <c r="G40" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H40" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="41" t="n">
+        <v>87.88461538461539</v>
+      </c>
+      <c r="K40" s="39" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="inlineStr">
+        <is>
+          <t>47.00/52.00</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>90.38461538461539</v>
+      </c>
+      <c r="F41" s="41" t="n">
+        <v>63.26923076923077</v>
+      </c>
+      <c r="G41" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H41" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="41" t="n">
+        <v>93.26923076923077</v>
+      </c>
+      <c r="K41" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="inlineStr">
+        <is>
+          <t>45.00/52.00</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="n">
+        <v>86.53846153846155</v>
+      </c>
+      <c r="F42" s="41" t="n">
+        <v>60.57692307692308</v>
+      </c>
+      <c r="G42" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H42" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="41" t="n">
+        <v>90.57692307692308</v>
+      </c>
+      <c r="K42" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="inlineStr">
+        <is>
+          <t>50.00/52.00</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>96.15384615384616</v>
+      </c>
+      <c r="F43" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="G43" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H43" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="41" t="n">
+        <v>97.30769230769231</v>
+      </c>
+      <c r="K43" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="39" t="inlineStr">
+        <is>
+          <t>46.00/52.00</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="n">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="F44" s="41" t="n">
+        <v>61.92307692307692</v>
+      </c>
+      <c r="G44" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H44" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="41" t="n">
+        <v>91.92307692307692</v>
+      </c>
+      <c r="K44" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="inlineStr">
+        <is>
+          <t>34.00/52.00</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="F45" s="41" t="n">
+        <v>45.76923076923077</v>
+      </c>
+      <c r="G45" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H45" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="41" t="n">
+        <v>75.76923076923077</v>
+      </c>
+      <c r="K45" s="39" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D46" s="39" t="inlineStr">
+        <is>
+          <t>50.00/52.00</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="n">
+        <v>96.15384615384616</v>
+      </c>
+      <c r="F46" s="41" t="n">
+        <v>67.30769230769231</v>
+      </c>
+      <c r="G46" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H46" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="41" t="n">
+        <v>97.30769230769231</v>
+      </c>
+      <c r="K46" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>47.00/52.00</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="n">
+        <v>90.38461538461539</v>
+      </c>
+      <c r="F47" s="41" t="n">
+        <v>63.26923076923077</v>
+      </c>
+      <c r="G47" s="39" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H47" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="41" t="n">
+        <v>93.26923076923077</v>
+      </c>
+      <c r="K47" s="39" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>6610553181</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>26.00/42.00</t>
-        </is>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>61.90476190476191</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H5" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" s="35" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="K5" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>7.00/42.00</t>
-        </is>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="F6" s="35" t="n">
-        <v>11.66666666666667</v>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H6" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="35" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="K6" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="I7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>9.00/42.00</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="F8" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H8" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I8" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J8" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="K8" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>27.00/42.00</t>
-        </is>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="35" t="n">
-        <v>75</v>
-      </c>
-      <c r="K9" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F10" s="35" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G10" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H10" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="35" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="K10" s="33" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>28.00/42.00</t>
-        </is>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="35" t="n">
-        <v>76.66666666666666</v>
-      </c>
-      <c r="K11" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="inlineStr">
-        <is>
-          <t>10.00/42.00</t>
-        </is>
-      </c>
-      <c r="E12" s="35" t="n">
-        <v>23.80952380952381</v>
-      </c>
-      <c r="F12" s="35" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="G12" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H12" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I12" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="35" t="n">
-        <v>36.66666666666666</v>
-      </c>
-      <c r="K12" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="33" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="33" t="inlineStr">
-        <is>
-          <t>30.00/42.00</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="F14" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" s="33" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H14" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="I14" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="35" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" s="33" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I15" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>56.66666666666667</v>
-      </c>
-      <c r="K15" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F16" s="35" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K16" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>35.00/42.00</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K17" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F18" s="35" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G18" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="35" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K18" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>25.00/42.00</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>59.52380952380953</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>71.66666666666666</v>
-      </c>
-      <c r="K19" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F20" s="35" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G20" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K20" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>22.00/42.00</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>36.66666666666667</v>
-      </c>
-      <c r="G21" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I21" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>56.66666666666667</v>
-      </c>
-      <c r="K21" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="33" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>18.00/42.00</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="F22" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="G22" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="K22" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G23" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K23" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>42.00/42.00</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" s="35" t="n">
-        <v>70</v>
-      </c>
-      <c r="G24" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="K24" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>0.00/42.00</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>41.00/42.00</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="n">
-        <v>97.61904761904762</v>
-      </c>
-      <c r="F26" s="35" t="n">
-        <v>68.33333333333333</v>
-      </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>98.33333333333333</v>
-      </c>
-      <c r="K26" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>25.00/42.00</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>59.52380952380953</v>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="G27" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I27" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="K27" s="33" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>26.00/42.00</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="n">
-        <v>61.90476190476191</v>
-      </c>
-      <c r="F28" s="35" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H28" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="35" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="K28" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K29" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F30" s="35" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="35" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K30" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F31" s="35" t="n">
-        <v>65</v>
-      </c>
-      <c r="G31" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="35" t="n">
-        <v>95</v>
-      </c>
-      <c r="K31" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>20.00/42.00</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="n">
-        <v>47.61904761904761</v>
-      </c>
-      <c r="F32" s="35" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="G32" s="33" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H32" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I32" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" s="35" t="n">
-        <v>53.33333333333333</v>
-      </c>
-      <c r="K32" s="33" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>42.00/42.00</t>
-        </is>
-      </c>
-      <c r="E33" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" s="35" t="n">
-        <v>70</v>
-      </c>
-      <c r="G33" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H33" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F34" s="35" t="n">
-        <v>65</v>
-      </c>
-      <c r="G34" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H34" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="35" t="n">
-        <v>95</v>
-      </c>
-      <c r="K34" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>39.00/42.00</t>
-        </is>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="F35" s="35" t="n">
-        <v>65</v>
-      </c>
-      <c r="G35" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H35" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="35" t="n">
-        <v>95</v>
-      </c>
-      <c r="K35" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F36" s="35" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G36" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H36" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="35" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K36" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>29.00/42.00</t>
-        </is>
-      </c>
-      <c r="E37" s="35" t="n">
-        <v>69.04761904761905</v>
-      </c>
-      <c r="F37" s="35" t="n">
-        <v>48.33333333333334</v>
-      </c>
-      <c r="G37" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H37" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="35" t="n">
-        <v>78.33333333333334</v>
-      </c>
-      <c r="K37" s="33" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="33" t="inlineStr">
-        <is>
-          <t>32.00/42.00</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="n">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="F38" s="35" t="n">
-        <v>53.33333333333333</v>
-      </c>
-      <c r="G38" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H38" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="35" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="K38" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="33" t="inlineStr">
-        <is>
-          <t>38.00/42.00</t>
-        </is>
-      </c>
-      <c r="E39" s="35" t="n">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="F39" s="35" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="G39" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H39" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="35" t="n">
-        <v>93.33333333333334</v>
-      </c>
-      <c r="K39" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="33" t="inlineStr">
-        <is>
-          <t>33.00/42.00</t>
-        </is>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="F40" s="35" t="n">
-        <v>55</v>
-      </c>
-      <c r="G40" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H40" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="35" t="n">
-        <v>85</v>
-      </c>
-      <c r="K40" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="33" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F41" s="35" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G41" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H41" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="35" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K41" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="33" t="inlineStr">
-        <is>
-          <t>35.00/42.00</t>
-        </is>
-      </c>
-      <c r="E42" s="35" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F42" s="35" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G42" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H42" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="35" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K42" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="33" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="33" t="inlineStr">
-        <is>
-          <t>40.00/42.00</t>
-        </is>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>95.23809523809523</v>
-      </c>
-      <c r="F43" s="35" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="G43" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H43" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="35" t="n">
-        <v>96.66666666666666</v>
-      </c>
-      <c r="K43" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="33" t="inlineStr">
-        <is>
-          <t>36.00/42.00</t>
-        </is>
-      </c>
-      <c r="E44" s="35" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="F44" s="35" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H44" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="K44" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="33" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="33" t="inlineStr">
-        <is>
-          <t>34.00/42.00</t>
-        </is>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="F45" s="35" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="G45" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H45" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="35" t="n">
-        <v>86.66666666666666</v>
-      </c>
-      <c r="K45" s="33" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="33" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="33" t="inlineStr">
-        <is>
-          <t>42.00/42.00</t>
-        </is>
-      </c>
-      <c r="E46" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="F46" s="35" t="n">
-        <v>70</v>
-      </c>
-      <c r="G46" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H46" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="K46" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="33" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="n"/>
+      <c r="B54" s="43" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="43" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="33" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="inlineStr">
-        <is>
-          <t>37.00/42.00</t>
-        </is>
-      </c>
-      <c r="E47" s="35" t="n">
-        <v>88.09523809523809</v>
-      </c>
-      <c r="F47" s="35" t="n">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="G47" s="33" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H47" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="35" t="n">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="K47" s="33" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="36" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="36" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="38" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="36" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="36" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="38" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="36" t="n"/>
-      <c r="B54" s="37" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="36" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="37" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="39" t="n">
-        <v>71.15942028985508</v>
+      <c r="B56" s="45" t="n">
+        <v>72.876254180602</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="39" t="n">
-        <v>27.59671085302526</v>
+      <c r="B57" s="45" t="n">
+        <v>26.47537326107639</v>
       </c>
     </row>
   </sheetData>

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-5780" windowWidth="28800" windowHeight="15200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-5780" windowWidth="25130" windowHeight="19430" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -61,6 +61,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1" tint="0.0499893185216834"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
     <font>
@@ -181,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -268,12 +288,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -283,25 +297,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -617,19 +646,19 @@
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
     <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" style="33" min="12" max="20"/>
+    <col width="4.6484375" customWidth="1" style="36" min="12" max="20"/>
     <col width="10.796875" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -646,7 +675,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="33" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -705,7 +734,11 @@
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="n"/>
+      <c r="Q6" s="39" t="inlineStr">
+        <is>
+          <t>MidTerm</t>
+        </is>
+      </c>
       <c r="R6" s="10" t="n"/>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
@@ -761,25 +794,27 @@
           <t>Email Office365</t>
         </is>
       </c>
-      <c r="L7" s="34" t="n">
+      <c r="L7" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="35" t="n"/>
-      <c r="R7" s="35" t="n"/>
-      <c r="S7" s="35" t="n"/>
-      <c r="T7" s="35" t="n"/>
+      <c r="M7" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="37" t="n">
+        <v>26</v>
+      </c>
+      <c r="R7" s="33" t="n"/>
+      <c r="S7" s="33" t="n"/>
+      <c r="T7" s="33" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
@@ -832,14 +867,16 @@
           <t>theerapat.ke@live.ku.th</t>
         </is>
       </c>
-      <c r="L8" s="36" t="n"/>
+      <c r="L8" s="34" t="n"/>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="R8" s="10" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
@@ -895,7 +932,7 @@
           <t>naphatson.nu@live.ku.th</t>
         </is>
       </c>
-      <c r="L9" s="36" t="n"/>
+      <c r="L9" s="34" t="n"/>
       <c r="M9" s="10" t="n">
         <v>3</v>
       </c>
@@ -904,7 +941,9 @@
         <v>10</v>
       </c>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
@@ -960,7 +999,7 @@
           <t>naraporn.ja@live.ku.th</t>
         </is>
       </c>
-      <c r="L10" s="36" t="n"/>
+      <c r="L10" s="34" t="n"/>
       <c r="M10" s="10" t="n">
         <v>3</v>
       </c>
@@ -971,7 +1010,9 @@
       <c r="P10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R10" s="10" t="n"/>
       <c r="S10" s="10" t="n"/>
       <c r="T10" s="10" t="n"/>
@@ -1027,7 +1068,7 @@
           <t>bunyamin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L11" s="36" t="n">
+      <c r="L11" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="10" t="n">
@@ -1042,7 +1083,9 @@
       <c r="P11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="R11" s="10" t="n"/>
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
@@ -1098,7 +1141,7 @@
           <t>panyanan.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L12" s="36" t="n"/>
+      <c r="L12" s="34" t="n"/>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="11" t="n">
         <v>7</v>
@@ -1107,7 +1150,9 @@
       <c r="P12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="R12" s="10" t="n"/>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
@@ -1163,12 +1208,14 @@
           <t>phinyada.sr@live.ku.th</t>
         </is>
       </c>
-      <c r="L13" s="36" t="n"/>
+      <c r="L13" s="34" t="n"/>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="R13" s="10" t="n"/>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
@@ -1224,7 +1271,7 @@
           <t>purin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L14" s="36" t="n"/>
+      <c r="L14" s="34" t="n"/>
       <c r="M14" s="10" t="n">
         <v>4</v>
       </c>
@@ -1235,7 +1282,9 @@
       <c r="P14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="R14" s="10" t="n"/>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
@@ -1291,7 +1340,7 @@
           <t>ratchanon.sakh@live.ku.th</t>
         </is>
       </c>
-      <c r="L15" s="36" t="n">
+      <c r="L15" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="10" t="n">
@@ -1306,7 +1355,9 @@
       <c r="P15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="R15" s="10" t="n"/>
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
@@ -1362,7 +1413,7 @@
           <t>worapon.pl@live.ku.th</t>
         </is>
       </c>
-      <c r="L16" s="36" t="n"/>
+      <c r="L16" s="34" t="n"/>
       <c r="M16" s="10" t="n">
         <v>7</v>
       </c>
@@ -1373,7 +1424,9 @@
         <v>5</v>
       </c>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="R16" s="10" t="n"/>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
@@ -1429,7 +1482,7 @@
           <t>suphanat.chan@live.ku.th</t>
         </is>
       </c>
-      <c r="L17" s="36" t="n">
+      <c r="L17" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="10" t="n">
@@ -1444,7 +1497,9 @@
       <c r="P17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="R17" s="10" t="n"/>
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
@@ -1500,7 +1555,7 @@
           <t>settakamol.wa@live.ku.th</t>
         </is>
       </c>
-      <c r="L18" s="36" t="n"/>
+      <c r="L18" s="34" t="n"/>
       <c r="M18" s="10" t="n">
         <v>5</v>
       </c>
@@ -1511,7 +1566,9 @@
       <c r="P18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="R18" s="10" t="n"/>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
@@ -1567,12 +1624,14 @@
           <t>arisara.len@live.ku.th</t>
         </is>
       </c>
-      <c r="L19" s="36" t="n"/>
+      <c r="L19" s="34" t="n"/>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="R19" s="10" t="n"/>
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
@@ -1628,7 +1687,7 @@
           <t>pattarapon.ditt@live.ku.th</t>
         </is>
       </c>
-      <c r="L20" s="36" t="n">
+      <c r="L20" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M20" s="10" t="n">
@@ -1643,7 +1702,9 @@
       <c r="P20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="R20" s="10" t="n"/>
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
@@ -1699,7 +1760,7 @@
           <t>pakin.saen@live.ku.th</t>
         </is>
       </c>
-      <c r="L21" s="36" t="n">
+      <c r="L21" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M21" s="10" t="n">
@@ -1710,7 +1771,9 @@
         <v>5</v>
       </c>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="R21" s="10" t="n"/>
       <c r="S21" s="10" t="n"/>
       <c r="T21" s="10" t="n"/>
@@ -1766,7 +1829,7 @@
           <t>kanol.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L22" s="36" t="n">
+      <c r="L22" s="34" t="n">
         <v>10</v>
       </c>
       <c r="M22" s="10" t="n">
@@ -1781,7 +1844,9 @@
       <c r="P22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="10" t="n"/>
@@ -1837,7 +1902,7 @@
           <t>kamonnit.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L23" s="36" t="n">
+      <c r="L23" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M23" s="10" t="n">
@@ -1852,7 +1917,9 @@
       <c r="P23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="R23" s="10" t="n"/>
       <c r="S23" s="10" t="n"/>
       <c r="T23" s="10" t="n"/>
@@ -1908,7 +1975,7 @@
           <t>krisskon.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L24" s="36" t="n">
+      <c r="L24" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M24" s="10" t="n">
@@ -1923,7 +1990,9 @@
       <c r="P24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n">
+        <v>12</v>
+      </c>
       <c r="R24" s="10" t="n"/>
       <c r="S24" s="10" t="n"/>
       <c r="T24" s="10" t="n"/>
@@ -1979,7 +2048,7 @@
           <t>kantiwat.ta@live.ku.th</t>
         </is>
       </c>
-      <c r="L25" s="36" t="n">
+      <c r="L25" s="34" t="n">
         <v>6</v>
       </c>
       <c r="M25" s="10" t="n">
@@ -1994,7 +2063,9 @@
       <c r="P25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="R25" s="10" t="n"/>
       <c r="S25" s="10" t="n"/>
       <c r="T25" s="10" t="n"/>
@@ -2050,7 +2121,7 @@
           <t>kasemchoke.na@live.ku.th</t>
         </is>
       </c>
-      <c r="L26" s="36" t="n">
+      <c r="L26" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M26" s="10" t="n">
@@ -2065,7 +2136,9 @@
       <c r="P26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" s="10" t="n"/>
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
@@ -2121,7 +2194,7 @@
           <t>jakkarin.in@live.ku.th</t>
         </is>
       </c>
-      <c r="L27" s="36" t="n">
+      <c r="L27" s="34" t="n">
         <v>7</v>
       </c>
       <c r="M27" s="10" t="n">
@@ -2134,7 +2207,9 @@
       <c r="P27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
@@ -2190,7 +2265,7 @@
           <t>chanchao.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L28" s="36" t="n">
+      <c r="L28" s="34" t="n">
         <v>7</v>
       </c>
       <c r="M28" s="10" t="n"/>
@@ -2201,7 +2276,9 @@
         <v>4</v>
       </c>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
@@ -2257,7 +2334,7 @@
           <t>tikamporn.tr@live.ku.th</t>
         </is>
       </c>
-      <c r="L29" s="36" t="n">
+      <c r="L29" s="34" t="n">
         <v>6</v>
       </c>
       <c r="M29" s="10" t="n">
@@ -2272,7 +2349,9 @@
       <c r="P29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="R29" s="10" t="n"/>
       <c r="S29" s="10" t="n"/>
       <c r="T29" s="10" t="n"/>
@@ -2328,7 +2407,7 @@
           <t>napapach.bu@live.ku.th</t>
         </is>
       </c>
-      <c r="L30" s="36" t="n">
+      <c r="L30" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M30" s="10" t="n">
@@ -2343,7 +2422,9 @@
       <c r="P30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
@@ -2399,7 +2480,7 @@
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="36" t="n"/>
+      <c r="L31" s="34" t="n"/>
       <c r="M31" s="10" t="n"/>
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="10" t="n"/>
@@ -2460,7 +2541,7 @@
           <t>thanaphum.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L32" s="36" t="n">
+      <c r="L32" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M32" s="10" t="n">
@@ -2475,7 +2556,9 @@
       <c r="P32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
@@ -2531,7 +2614,7 @@
           <t>thanakon.r@live.ku.th</t>
         </is>
       </c>
-      <c r="L33" s="36" t="n">
+      <c r="L33" s="34" t="n">
         <v>5</v>
       </c>
       <c r="M33" s="10" t="n">
@@ -2544,7 +2627,9 @@
       <c r="P33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="R33" s="10" t="n"/>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
@@ -2613,7 +2698,9 @@
       <c r="P34" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" s="31" t="n"/>
+      <c r="Q34" s="31" t="n">
+        <v>25</v>
+      </c>
       <c r="R34" s="31" t="n"/>
       <c r="S34" s="31" t="n"/>
       <c r="T34" s="31" t="n"/>
@@ -2669,7 +2756,7 @@
           <t>thattawan.y@live.ku.th</t>
         </is>
       </c>
-      <c r="L35" s="36" t="n">
+      <c r="L35" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M35" s="10" t="n">
@@ -2684,7 +2771,9 @@
       <c r="P35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n">
+        <v>17</v>
+      </c>
       <c r="R35" s="10" t="n"/>
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
@@ -2740,7 +2829,7 @@
           <t>nonthakorn.j@live.ku.th</t>
         </is>
       </c>
-      <c r="L36" s="36" t="n">
+      <c r="L36" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M36" s="10" t="n">
@@ -2755,7 +2844,9 @@
       <c r="P36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="10" t="n"/>
       <c r="T36" s="10" t="n"/>
@@ -2811,7 +2902,7 @@
           <t>naputrapee.a@live.ku.th</t>
         </is>
       </c>
-      <c r="L37" s="36" t="n">
+      <c r="L37" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M37" s="10" t="n">
@@ -2826,7 +2917,9 @@
       <c r="P37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n">
+        <v>17</v>
+      </c>
       <c r="R37" s="10" t="n"/>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
@@ -2882,7 +2975,7 @@
           <t>pichayut.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L38" s="36" t="n"/>
+      <c r="L38" s="34" t="n"/>
       <c r="M38" s="10" t="n">
         <v>5</v>
       </c>
@@ -2895,7 +2988,9 @@
       <c r="P38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
@@ -2951,7 +3046,7 @@
           <t>pakhawat.p@live.ku.th</t>
         </is>
       </c>
-      <c r="L39" s="36" t="n">
+      <c r="L39" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M39" s="10" t="n">
@@ -2966,7 +3061,9 @@
       <c r="P39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n">
+        <v>22</v>
+      </c>
       <c r="R39" s="10" t="n"/>
       <c r="S39" s="10" t="n"/>
       <c r="T39" s="10" t="n"/>
@@ -3022,7 +3119,7 @@
           <t>phakkaphon.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L40" s="36" t="n">
+      <c r="L40" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M40" s="10" t="n">
@@ -3037,7 +3134,9 @@
       <c r="P40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="R40" s="10" t="n"/>
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="10" t="n"/>
@@ -3093,7 +3192,7 @@
           <t>pakkapon.i@live.ku.th</t>
         </is>
       </c>
-      <c r="L41" s="36" t="n">
+      <c r="L41" s="34" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="10" t="n">
@@ -3108,7 +3207,9 @@
       <c r="P41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="R41" s="10" t="n"/>
       <c r="S41" s="10" t="n"/>
       <c r="T41" s="10" t="n"/>
@@ -3164,7 +3265,7 @@
           <t>yuttana.sukku@live.ku.th</t>
         </is>
       </c>
-      <c r="L42" s="36" t="n">
+      <c r="L42" s="34" t="n">
         <v>10</v>
       </c>
       <c r="M42" s="10" t="n">
@@ -3177,7 +3278,9 @@
         <v>10</v>
       </c>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R42" s="10" t="n"/>
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
@@ -3233,7 +3336,7 @@
           <t>rapeepat.mo@live.ku.th</t>
         </is>
       </c>
-      <c r="L43" s="36" t="n">
+      <c r="L43" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M43" s="10" t="n">
@@ -3248,7 +3351,9 @@
       <c r="P43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
@@ -3304,7 +3409,7 @@
           <t>veerapat.d@live.ku.th</t>
         </is>
       </c>
-      <c r="L44" s="36" t="n">
+      <c r="L44" s="34" t="n">
         <v>5</v>
       </c>
       <c r="M44" s="10" t="n">
@@ -3319,7 +3424,9 @@
       <c r="P44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R44" s="10" t="n"/>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
@@ -3375,7 +3482,7 @@
           <t>savita.cha@live.ku.th</t>
         </is>
       </c>
-      <c r="L45" s="36" t="n">
+      <c r="L45" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M45" s="10" t="n">
@@ -3390,7 +3497,9 @@
       <c r="P45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="R45" s="10" t="n"/>
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
@@ -3446,7 +3555,7 @@
           <t>sorasak.cot@live.ku.th</t>
         </is>
       </c>
-      <c r="L46" s="36" t="n">
+      <c r="L46" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M46" s="10" t="n">
@@ -3461,7 +3570,9 @@
       <c r="P46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
@@ -3517,7 +3628,7 @@
           <t>sarawut.ya@live.ku.th</t>
         </is>
       </c>
-      <c r="L47" s="36" t="n">
+      <c r="L47" s="34" t="n">
         <v>10</v>
       </c>
       <c r="M47" s="10" t="n">
@@ -3532,7 +3643,9 @@
       <c r="P47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n">
+        <v>13</v>
+      </c>
       <c r="R47" s="10" t="n"/>
       <c r="S47" s="10" t="n"/>
       <c r="T47" s="10" t="n"/>
@@ -3588,7 +3701,7 @@
           <t>sitthichailoet.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L48" s="36" t="n">
+      <c r="L48" s="34" t="n">
         <v>10</v>
       </c>
       <c r="M48" s="10" t="n">
@@ -3603,7 +3716,9 @@
       <c r="P48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="R48" s="10" t="n"/>
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="n"/>
@@ -3659,7 +3774,7 @@
           <t>sutichode.b@live.ku.th</t>
         </is>
       </c>
-      <c r="L49" s="36" t="n">
+      <c r="L49" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M49" s="10" t="n">
@@ -3674,7 +3789,9 @@
       <c r="P49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n">
+        <v>21</v>
+      </c>
       <c r="R49" s="10" t="n"/>
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
@@ -3730,7 +3847,7 @@
           <t>sumath.o@live.ku.th</t>
         </is>
       </c>
-      <c r="L50" s="36" t="n">
+      <c r="L50" s="34" t="n">
         <v>11</v>
       </c>
       <c r="M50" s="10" t="n">
@@ -3745,7 +3862,9 @@
       <c r="P50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n">
+        <v>20</v>
+      </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="10" t="n"/>
       <c r="T50" s="10" t="n"/>
@@ -3801,7 +3920,7 @@
           <t>aussanee.ko@live.ku.th</t>
         </is>
       </c>
-      <c r="L51" s="36" t="n">
+      <c r="L51" s="34" t="n">
         <v>7</v>
       </c>
       <c r="M51" s="10" t="n">
@@ -3814,7 +3933,9 @@
         <v>10</v>
       </c>
       <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="R51" s="10" t="n"/>
       <c r="S51" s="10" t="n"/>
       <c r="T51" s="10" t="n"/>
@@ -3870,7 +3991,7 @@
           <t>atitaya.thai@live.ku.th</t>
         </is>
       </c>
-      <c r="L52" s="36" t="n">
+      <c r="L52" s="34" t="n">
         <v>12</v>
       </c>
       <c r="M52" s="10" t="n">
@@ -3885,7 +4006,9 @@
       <c r="P52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n">
+        <v>22</v>
+      </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
@@ -3941,7 +4064,7 @@
           <t>araya.sansu@live.ku.th</t>
         </is>
       </c>
-      <c r="L53" s="36" t="n">
+      <c r="L53" s="34" t="n">
         <v>8</v>
       </c>
       <c r="M53" s="10" t="n">
@@ -3956,12 +4079,20 @@
       <c r="P53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n">
+        <v>19</v>
+      </c>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="10" t="n"/>
       <c r="T53" s="10" t="n"/>
     </row>
-    <row r="54"/>
+    <row r="54">
+      <c r="Q54" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
     <row r="55"/>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="1" t="n"/>
@@ -3978,6 +4109,7 @@
     <mergeCell ref="M4:T4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -4022,7 +4154,7 @@
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
@@ -5559,2204 +5691,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="38" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="38" t="inlineStr">
+      <c r="C1" s="41" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="38" t="inlineStr">
+      <c r="D1" s="41" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="38" t="inlineStr">
+      <c r="E1" s="41" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="38" t="inlineStr">
+      <c r="F1" s="41" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="38" t="inlineStr">
+      <c r="G1" s="41" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="38" t="inlineStr">
+      <c r="H1" s="41" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="38" t="inlineStr">
+      <c r="I1" s="41" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="38" t="inlineStr">
+      <c r="J1" s="41" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="38" t="inlineStr">
+      <c r="K1" s="41" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="A2" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="40" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="39" t="inlineStr">
-        <is>
-          <t>8.00/52.00</t>
-        </is>
-      </c>
-      <c r="E2" s="41" t="n">
-        <v>15.38461538461539</v>
-      </c>
-      <c r="F2" s="41" t="n">
-        <v>10.76923076923077</v>
-      </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="D2" s="42" t="inlineStr">
+        <is>
+          <t>18.00/78.00</t>
+        </is>
+      </c>
+      <c r="E2" s="44" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="F2" s="44" t="n">
+        <v>16.15384615384615</v>
+      </c>
+      <c r="G2" s="42" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="H2" s="41" t="n">
+      <c r="H2" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="I2" s="41" t="n">
+      <c r="I2" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="41" t="n">
-        <v>25.76923076923077</v>
-      </c>
-      <c r="K2" s="39" t="inlineStr">
+      <c r="J2" s="44" t="n">
+        <v>31.15384615384615</v>
+      </c>
+      <c r="K2" s="42" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="n">
+      <c r="A3" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>6610553165</t>
         </is>
       </c>
-      <c r="C3" s="40" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
-        <is>
-          <t>13.00/52.00</t>
-        </is>
-      </c>
-      <c r="E3" s="41" t="n">
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t>17.00/78.00</t>
+        </is>
+      </c>
+      <c r="E3" s="44" t="n">
+        <v>21.7948717948718</v>
+      </c>
+      <c r="F3" s="44" t="n">
+        <v>15.25641025641026</v>
+      </c>
+      <c r="G3" s="42" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H3" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" s="44" t="n">
+        <v>30.25641025641026</v>
+      </c>
+      <c r="K3" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>6610553173</t>
+        </is>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>20.00/78.00</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="n">
+        <v>25.64102564102564</v>
+      </c>
+      <c r="F4" s="44" t="n">
+        <v>17.94871794871795</v>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H4" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="F3" s="41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="I4" s="44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J4" s="44" t="n">
+        <v>25.44871794871795</v>
+      </c>
+      <c r="K4" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>6610553181</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>44.00/78.00</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>56.41025641025641</v>
+      </c>
+      <c r="F5" s="44" t="n">
+        <v>39.48717948717949</v>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H5" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="44" t="n">
+        <v>69.48717948717949</v>
+      </c>
+      <c r="K5" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>26.00/78.00</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F6" s="44" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="44" t="n">
+        <v>53.33333333333333</v>
+      </c>
+      <c r="K6" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>0.00/78.00</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="H3" s="41" t="n">
+      <c r="H7" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="I3" s="41" t="n">
+      <c r="I7" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="41" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="K3" s="39" t="inlineStr">
+      <c r="J7" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" s="42" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>6610553173</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
-        <is>
-          <t>16.00/52.00</t>
-        </is>
-      </c>
-      <c r="E4" s="41" t="n">
-        <v>30.76923076923077</v>
-      </c>
-      <c r="F4" s="41" t="n">
-        <v>21.53846153846154</v>
-      </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>19.00/78.00</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="F8" s="44" t="n">
+        <v>17.05128205128205</v>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J8" s="44" t="n">
+        <v>39.55128205128205</v>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>46.00/78.00</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>58.97435897435898</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>41.28205128205128</v>
+      </c>
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>71.28205128205128</v>
+      </c>
+      <c r="K9" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>36.00/78.00</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>32.30769230769231</v>
+      </c>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>62.30769230769231</v>
+      </c>
+      <c r="K10" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>47.00/78.00</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>60.25641025641026</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>42.17948717948718</v>
+      </c>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H11" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>72.17948717948718</v>
+      </c>
+      <c r="K11" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>21.00/78.00</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>26.92307692307692</v>
+      </c>
+      <c r="F12" s="44" t="n">
+        <v>18.84615384615385</v>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J12" s="44" t="n">
+        <v>41.34615384615385</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>0.00/78.00</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="42" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="H4" s="41" t="n">
+      <c r="H13" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="I4" s="41" t="n">
+      <c r="I13" s="44" t="n">
         <v>7.5</v>
       </c>
-      <c r="J4" s="41" t="n">
-        <v>29.03846153846154</v>
-      </c>
-      <c r="K4" s="39" t="inlineStr">
+      <c r="J13" s="44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="39" t="n">
+    <row r="14">
+      <c r="A14" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>45.00/78.00</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>57.69230769230769</v>
+      </c>
+      <c r="F14" s="44" t="n">
+        <v>40.38461538461538</v>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="44" t="n">
+        <v>55.38461538461538</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>28.00/78.00</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="n">
+        <v>35.8974358974359</v>
+      </c>
+      <c r="F15" s="44" t="n">
+        <v>25.12820512820513</v>
+      </c>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H15" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="44" t="n">
+        <v>40.12820512820512</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>46.00/78.00</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>58.97435897435898</v>
+      </c>
+      <c r="F16" s="44" t="n">
+        <v>41.28205128205128</v>
+      </c>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>71.28205128205128</v>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>61.00/78.00</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>78.2051282051282</v>
+      </c>
+      <c r="F17" s="44" t="n">
+        <v>54.74358974358974</v>
+      </c>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H17" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>84.74358974358975</v>
+      </c>
+      <c r="K17" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>60.00/78.00</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="F18" s="44" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="44" t="n">
+        <v>83.84615384615384</v>
+      </c>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>44.00/78.00</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>56.41025641025641</v>
+      </c>
+      <c r="F19" s="44" t="n">
+        <v>39.48717948717949</v>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="44" t="n">
+        <v>69.48717948717949</v>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>48.00/78.00</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="n">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="F20" s="44" t="n">
+        <v>43.07692307692308</v>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="44" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="K20" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>33.00/78.00</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>42.30769230769231</v>
+      </c>
+      <c r="F21" s="44" t="n">
+        <v>29.61538461538462</v>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J21" s="44" t="n">
+        <v>52.11538461538461</v>
+      </c>
+      <c r="K21" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>26.00/78.00</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F22" s="44" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="G22" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J22" s="44" t="n">
+        <v>45.83333333333333</v>
+      </c>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>53.00/78.00</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>67.94871794871796</v>
+      </c>
+      <c r="F23" s="44" t="n">
+        <v>47.56410256410257</v>
+      </c>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="44" t="n">
+        <v>77.56410256410257</v>
+      </c>
+      <c r="K23" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>63.00/78.00</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>80.76923076923077</v>
+      </c>
+      <c r="F24" s="44" t="n">
+        <v>56.53846153846154</v>
+      </c>
+      <c r="G24" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="44" t="n">
+        <v>86.53846153846155</v>
+      </c>
+      <c r="K24" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>0.00/78.00</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="42" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>65.00/78.00</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G26" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="44" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K26" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>38.00/78.00</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>48.71794871794872</v>
+      </c>
+      <c r="F27" s="44" t="n">
+        <v>34.1025641025641</v>
+      </c>
+      <c r="G27" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I27" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J27" s="44" t="n">
+        <v>56.6025641025641</v>
+      </c>
+      <c r="K27" s="42" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr">
+        <is>
+          <t>61.00/78.00</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="n">
+        <v>78.2051282051282</v>
+      </c>
+      <c r="F28" s="44" t="n">
+        <v>54.74358974358974</v>
+      </c>
+      <c r="G28" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="44" t="n">
+        <v>84.74358974358975</v>
+      </c>
+      <c r="K28" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>65.00/78.00</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F29" s="44" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G29" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="44" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K29" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>54.00/78.00</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="n">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="F30" s="44" t="n">
+        <v>48.46153846153846</v>
+      </c>
+      <c r="G30" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="44" t="n">
+        <v>78.46153846153845</v>
+      </c>
+      <c r="K30" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>65.00/78.00</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F31" s="44" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G31" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H31" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="44" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K31" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>46.00/78.00</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="n">
+        <v>58.97435897435898</v>
+      </c>
+      <c r="F32" s="44" t="n">
+        <v>41.28205128205128</v>
+      </c>
+      <c r="G32" s="42" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H32" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I32" s="44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J32" s="44" t="n">
+        <v>63.78205128205128</v>
+      </c>
+      <c r="K32" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>74.00/78.00</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="n">
+        <v>94.87179487179486</v>
+      </c>
+      <c r="F33" s="44" t="n">
+        <v>66.41025641025641</v>
+      </c>
+      <c r="G33" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H33" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="44" t="n">
+        <v>96.41025641025641</v>
+      </c>
+      <c r="K33" s="42" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>64.00/78.00</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>82.05128205128204</v>
+      </c>
+      <c r="F34" s="44" t="n">
+        <v>57.43589743589743</v>
+      </c>
+      <c r="G34" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="44" t="n">
+        <v>87.43589743589743</v>
+      </c>
+      <c r="K34" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>55.00/78.00</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="n">
+        <v>70.51282051282051</v>
+      </c>
+      <c r="F35" s="44" t="n">
+        <v>49.35897435897436</v>
+      </c>
+      <c r="G35" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H35" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="44" t="n">
+        <v>79.35897435897436</v>
+      </c>
+      <c r="K35" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
+        <is>
+          <t>38.00/78.00</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="n">
+        <v>48.71794871794872</v>
+      </c>
+      <c r="F36" s="44" t="n">
+        <v>34.1025641025641</v>
+      </c>
+      <c r="G36" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="44" t="n">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="K36" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>42.00/78.00</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="F37" s="44" t="n">
+        <v>37.69230769230769</v>
+      </c>
+      <c r="G37" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H37" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J37" s="44" t="n">
+        <v>67.69230769230769</v>
+      </c>
+      <c r="K37" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>41.00/78.00</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="n">
+        <v>52.56410256410257</v>
+      </c>
+      <c r="F38" s="44" t="n">
+        <v>36.7948717948718</v>
+      </c>
+      <c r="G38" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H38" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="44" t="n">
+        <v>66.7948717948718</v>
+      </c>
+      <c r="K38" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>65.00/78.00</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F39" s="44" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G39" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H39" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="44" t="n">
+        <v>88.33333333333334</v>
+      </c>
+      <c r="K39" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>46.00/78.00</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="n">
+        <v>58.97435897435898</v>
+      </c>
+      <c r="F40" s="44" t="n">
+        <v>41.28205128205128</v>
+      </c>
+      <c r="G40" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="44" t="n">
+        <v>71.28205128205128</v>
+      </c>
+      <c r="K40" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>60.00/78.00</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="n">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="F41" s="44" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="G41" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H41" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="44" t="n">
+        <v>83.84615384615384</v>
+      </c>
+      <c r="K41" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>51.00/78.00</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="n">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="F42" s="44" t="n">
+        <v>45.76923076923077</v>
+      </c>
+      <c r="G42" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="44" t="n">
+        <v>75.76923076923077</v>
+      </c>
+      <c r="K42" s="42" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>71.00/78.00</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="n">
+        <v>91.02564102564102</v>
+      </c>
+      <c r="F43" s="44" t="n">
+        <v>63.71794871794872</v>
+      </c>
+      <c r="G43" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H43" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="44" t="n">
+        <v>93.71794871794872</v>
+      </c>
+      <c r="K43" s="42" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="42" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>66.00/78.00</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="n">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="F44" s="44" t="n">
+        <v>59.23076923076923</v>
+      </c>
+      <c r="G44" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H44" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="44" t="n">
+        <v>89.23076923076923</v>
+      </c>
+      <c r="K44" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="42" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
+        <is>
+          <t>38.00/78.00</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="n">
+        <v>48.71794871794872</v>
+      </c>
+      <c r="F45" s="44" t="n">
+        <v>34.1025641025641</v>
+      </c>
+      <c r="G45" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H45" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="44" t="n">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="K45" s="42" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="42" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
+        <is>
+          <t>72.00/78.00</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="F46" s="44" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="G46" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H46" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="44" t="n">
+        <v>94.61538461538461</v>
+      </c>
+      <c r="K46" s="42" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>66.00/78.00</t>
+        </is>
+      </c>
+      <c r="E47" s="44" t="n">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="F47" s="44" t="n">
+        <v>59.23076923076923</v>
+      </c>
+      <c r="G47" s="42" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H47" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="44" t="n">
+        <v>89.23076923076923</v>
+      </c>
+      <c r="K47" s="42" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="47" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>6610553181</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D5" s="39" t="inlineStr">
-        <is>
-          <t>35.00/52.00</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="F5" s="41" t="n">
-        <v>47.11538461538462</v>
-      </c>
-      <c r="G5" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H5" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" s="41" t="n">
-        <v>77.11538461538461</v>
-      </c>
-      <c r="K5" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>17.00/52.00</t>
-        </is>
-      </c>
-      <c r="E6" s="41" t="n">
-        <v>32.69230769230769</v>
-      </c>
-      <c r="F6" s="41" t="n">
-        <v>22.88461538461538</v>
-      </c>
-      <c r="G6" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H6" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="41" t="n">
-        <v>52.88461538461539</v>
-      </c>
-      <c r="K6" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D7" s="39" t="inlineStr">
-        <is>
-          <t>0.00/52.00</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="39" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H7" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="inlineStr">
-        <is>
-          <t>17.00/52.00</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="n">
-        <v>32.69230769230769</v>
-      </c>
-      <c r="F8" s="41" t="n">
-        <v>22.88461538461538</v>
-      </c>
-      <c r="G8" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H8" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I8" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J8" s="41" t="n">
-        <v>45.38461538461539</v>
-      </c>
-      <c r="K8" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="39" t="inlineStr">
-        <is>
-          <t>35.00/52.00</t>
-        </is>
-      </c>
-      <c r="E9" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="F9" s="41" t="n">
-        <v>47.11538461538462</v>
-      </c>
-      <c r="G9" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H9" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="41" t="n">
-        <v>77.11538461538461</v>
-      </c>
-      <c r="K9" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>22.00/52.00</t>
-        </is>
-      </c>
-      <c r="E10" s="41" t="n">
-        <v>42.30769230769231</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <v>29.61538461538462</v>
-      </c>
-      <c r="G10" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H10" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="41" t="n">
-        <v>59.61538461538461</v>
-      </c>
-      <c r="K10" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="39" t="inlineStr">
-        <is>
-          <t>38.00/52.00</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="n">
-        <v>73.07692307692307</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>51.15384615384615</v>
-      </c>
-      <c r="G11" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H11" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="41" t="n">
-        <v>81.15384615384616</v>
-      </c>
-      <c r="K11" s="39" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>19.00/52.00</t>
-        </is>
-      </c>
-      <c r="E12" s="41" t="n">
-        <v>36.53846153846153</v>
-      </c>
-      <c r="F12" s="41" t="n">
-        <v>25.57692307692308</v>
-      </c>
-      <c r="G12" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H12" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I12" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J12" s="41" t="n">
-        <v>48.07692307692308</v>
-      </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="39" t="inlineStr">
-        <is>
-          <t>0.00/52.00</t>
-        </is>
-      </c>
-      <c r="E13" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H13" s="41" t="n">
-        <v>25</v>
-      </c>
-      <c r="I13" s="41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J13" s="41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K13" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="39" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>40.00/52.00</t>
-        </is>
-      </c>
-      <c r="E14" s="41" t="n">
-        <v>76.92307692307693</v>
-      </c>
-      <c r="F14" s="41" t="n">
-        <v>53.84615384615385</v>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H14" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="I14" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="41" t="n">
-        <v>68.84615384615384</v>
-      </c>
-      <c r="K14" s="39" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="39" t="inlineStr">
-        <is>
-          <t>22.00/52.00</t>
-        </is>
-      </c>
-      <c r="E15" s="41" t="n">
-        <v>42.30769230769231</v>
-      </c>
-      <c r="F15" s="41" t="n">
-        <v>29.61538461538462</v>
-      </c>
-      <c r="G15" s="39" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H15" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="I15" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="41" t="n">
-        <v>44.61538461538461</v>
-      </c>
-      <c r="K15" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>44.00/52.00</t>
-        </is>
-      </c>
-      <c r="E16" s="41" t="n">
-        <v>84.61538461538461</v>
-      </c>
-      <c r="F16" s="41" t="n">
-        <v>59.23076923076923</v>
-      </c>
-      <c r="G16" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H16" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="41" t="n">
-        <v>89.23076923076923</v>
-      </c>
-      <c r="K16" s="39" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="39" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>45.00/52.00</t>
-        </is>
-      </c>
-      <c r="E17" s="41" t="n">
-        <v>86.53846153846155</v>
-      </c>
-      <c r="F17" s="41" t="n">
-        <v>60.57692307692308</v>
-      </c>
-      <c r="G17" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H17" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="41" t="n">
-        <v>90.57692307692308</v>
-      </c>
-      <c r="K17" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>48.00/52.00</t>
-        </is>
-      </c>
-      <c r="E18" s="41" t="n">
-        <v>92.30769230769231</v>
-      </c>
-      <c r="F18" s="41" t="n">
-        <v>64.61538461538461</v>
-      </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H18" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="41" t="n">
-        <v>94.61538461538461</v>
-      </c>
-      <c r="K18" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
-        <is>
-          <t>35.00/52.00</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="F19" s="41" t="n">
-        <v>47.11538461538462</v>
-      </c>
-      <c r="G19" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="41" t="n">
-        <v>77.11538461538461</v>
-      </c>
-      <c r="K19" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>47.00/52.00</t>
-        </is>
-      </c>
-      <c r="E20" s="41" t="n">
-        <v>90.38461538461539</v>
-      </c>
-      <c r="F20" s="41" t="n">
-        <v>63.26923076923077</v>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H20" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="41" t="n">
-        <v>93.26923076923077</v>
-      </c>
-      <c r="K20" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
-        <is>
-          <t>32.00/52.00</t>
-        </is>
-      </c>
-      <c r="E21" s="41" t="n">
-        <v>61.53846153846154</v>
-      </c>
-      <c r="F21" s="41" t="n">
-        <v>43.07692307692308</v>
-      </c>
-      <c r="G21" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H21" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I21" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J21" s="41" t="n">
-        <v>65.57692307692308</v>
-      </c>
-      <c r="K21" s="39" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="39" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>18.00/52.00</t>
-        </is>
-      </c>
-      <c r="E22" s="41" t="n">
-        <v>34.61538461538461</v>
-      </c>
-      <c r="F22" s="41" t="n">
-        <v>24.23076923076923</v>
-      </c>
-      <c r="G22" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H22" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I22" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J22" s="41" t="n">
-        <v>46.73076923076923</v>
-      </c>
-      <c r="K22" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="39" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="39" t="inlineStr">
-        <is>
-          <t>44.00/52.00</t>
-        </is>
-      </c>
-      <c r="E23" s="41" t="n">
-        <v>84.61538461538461</v>
-      </c>
-      <c r="F23" s="41" t="n">
-        <v>59.23076923076923</v>
-      </c>
-      <c r="G23" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H23" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="41" t="n">
-        <v>89.23076923076923</v>
-      </c>
-      <c r="K23" s="39" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="39" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>52.00/52.00</t>
-        </is>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="G24" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H24" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="K24" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="39" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="39" t="inlineStr">
-        <is>
-          <t>0.00/52.00</t>
-        </is>
-      </c>
-      <c r="E25" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="39" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H25" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="39" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="39" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>51.00/52.00</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="n">
-        <v>98.07692307692307</v>
-      </c>
-      <c r="F26" s="41" t="n">
-        <v>68.65384615384615</v>
-      </c>
-      <c r="G26" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H26" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="41" t="n">
-        <v>98.65384615384615</v>
-      </c>
-      <c r="K26" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="inlineStr">
-        <is>
-          <t>35.00/52.00</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="F27" s="41" t="n">
-        <v>47.11538461538462</v>
-      </c>
-      <c r="G27" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H27" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I27" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J27" s="41" t="n">
-        <v>69.61538461538461</v>
-      </c>
-      <c r="K27" s="39" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="39" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>36.00/52.00</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="n">
-        <v>69.23076923076923</v>
-      </c>
-      <c r="F28" s="41" t="n">
-        <v>48.46153846153846</v>
-      </c>
-      <c r="G28" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H28" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="41" t="n">
-        <v>78.46153846153845</v>
-      </c>
-      <c r="K28" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="39" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="39" t="inlineStr">
-        <is>
-          <t>48.00/52.00</t>
-        </is>
-      </c>
-      <c r="E29" s="41" t="n">
-        <v>92.30769230769231</v>
-      </c>
-      <c r="F29" s="41" t="n">
-        <v>64.61538461538461</v>
-      </c>
-      <c r="G29" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H29" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="41" t="n">
-        <v>94.61538461538461</v>
-      </c>
-      <c r="K29" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="39" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>47.00/52.00</t>
-        </is>
-      </c>
-      <c r="E30" s="41" t="n">
-        <v>90.38461538461539</v>
-      </c>
-      <c r="F30" s="41" t="n">
-        <v>63.26923076923077</v>
-      </c>
-      <c r="G30" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H30" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="41" t="n">
-        <v>93.26923076923077</v>
-      </c>
-      <c r="K30" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="39" t="inlineStr">
-        <is>
-          <t>48.00/52.00</t>
-        </is>
-      </c>
-      <c r="E31" s="41" t="n">
-        <v>92.30769230769231</v>
-      </c>
-      <c r="F31" s="41" t="n">
-        <v>64.61538461538461</v>
-      </c>
-      <c r="G31" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H31" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="41" t="n">
-        <v>94.61538461538461</v>
-      </c>
-      <c r="K31" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="39" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>30.00/52.00</t>
-        </is>
-      </c>
-      <c r="E32" s="41" t="n">
-        <v>57.69230769230769</v>
-      </c>
-      <c r="F32" s="41" t="n">
-        <v>40.38461538461538</v>
-      </c>
-      <c r="G32" s="39" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H32" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="I32" s="41" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J32" s="41" t="n">
-        <v>62.88461538461538</v>
-      </c>
-      <c r="K32" s="39" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="39" t="inlineStr">
-        <is>
-          <t>52.00/52.00</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="G33" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H33" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="39" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>49.00/52.00</t>
-        </is>
-      </c>
-      <c r="E34" s="41" t="n">
-        <v>94.23076923076923</v>
-      </c>
-      <c r="F34" s="41" t="n">
-        <v>65.96153846153847</v>
-      </c>
-      <c r="G34" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H34" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="41" t="n">
-        <v>95.96153846153847</v>
-      </c>
-      <c r="K34" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="39" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="39" t="inlineStr">
-        <is>
-          <t>49.00/52.00</t>
-        </is>
-      </c>
-      <c r="E35" s="41" t="n">
-        <v>94.23076923076923</v>
-      </c>
-      <c r="F35" s="41" t="n">
-        <v>65.96153846153847</v>
-      </c>
-      <c r="G35" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H35" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="41" t="n">
-        <v>95.96153846153847</v>
-      </c>
-      <c r="K35" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>34.00/52.00</t>
-        </is>
-      </c>
-      <c r="E36" s="41" t="n">
-        <v>65.38461538461539</v>
-      </c>
-      <c r="F36" s="41" t="n">
-        <v>45.76923076923077</v>
-      </c>
-      <c r="G36" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H36" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="41" t="n">
-        <v>75.76923076923077</v>
-      </c>
-      <c r="K36" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="39" t="inlineStr">
-        <is>
-          <t>38.00/52.00</t>
-        </is>
-      </c>
-      <c r="E37" s="41" t="n">
-        <v>73.07692307692307</v>
-      </c>
-      <c r="F37" s="41" t="n">
-        <v>51.15384615384615</v>
-      </c>
-      <c r="G37" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H37" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="41" t="n">
-        <v>81.15384615384616</v>
-      </c>
-      <c r="K37" s="39" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="39" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>37.00/52.00</t>
-        </is>
-      </c>
-      <c r="E38" s="41" t="n">
-        <v>71.15384615384616</v>
-      </c>
-      <c r="F38" s="41" t="n">
-        <v>49.80769230769231</v>
-      </c>
-      <c r="G38" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H38" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="41" t="n">
-        <v>79.80769230769231</v>
-      </c>
-      <c r="K38" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="39" t="inlineStr">
-        <is>
-          <t>47.00/52.00</t>
-        </is>
-      </c>
-      <c r="E39" s="41" t="n">
-        <v>90.38461538461539</v>
-      </c>
-      <c r="F39" s="41" t="n">
-        <v>63.26923076923077</v>
-      </c>
-      <c r="G39" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H39" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="41" t="n">
-        <v>93.26923076923077</v>
-      </c>
-      <c r="K39" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="39" t="inlineStr">
-        <is>
-          <t>43.00/52.00</t>
-        </is>
-      </c>
-      <c r="E40" s="41" t="n">
-        <v>82.69230769230769</v>
-      </c>
-      <c r="F40" s="41" t="n">
-        <v>57.88461538461538</v>
-      </c>
-      <c r="G40" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H40" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="41" t="n">
-        <v>87.88461538461539</v>
-      </c>
-      <c r="K40" s="39" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="39" t="inlineStr">
-        <is>
-          <t>47.00/52.00</t>
-        </is>
-      </c>
-      <c r="E41" s="41" t="n">
-        <v>90.38461538461539</v>
-      </c>
-      <c r="F41" s="41" t="n">
-        <v>63.26923076923077</v>
-      </c>
-      <c r="G41" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H41" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="41" t="n">
-        <v>93.26923076923077</v>
-      </c>
-      <c r="K41" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="39" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="39" t="inlineStr">
-        <is>
-          <t>45.00/52.00</t>
-        </is>
-      </c>
-      <c r="E42" s="41" t="n">
-        <v>86.53846153846155</v>
-      </c>
-      <c r="F42" s="41" t="n">
-        <v>60.57692307692308</v>
-      </c>
-      <c r="G42" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H42" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="41" t="n">
-        <v>90.57692307692308</v>
-      </c>
-      <c r="K42" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="39" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="39" t="inlineStr">
-        <is>
-          <t>50.00/52.00</t>
-        </is>
-      </c>
-      <c r="E43" s="41" t="n">
-        <v>96.15384615384616</v>
-      </c>
-      <c r="F43" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="G43" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H43" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="41" t="n">
-        <v>97.30769230769231</v>
-      </c>
-      <c r="K43" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="39" t="inlineStr">
-        <is>
-          <t>46.00/52.00</t>
-        </is>
-      </c>
-      <c r="E44" s="41" t="n">
-        <v>88.46153846153845</v>
-      </c>
-      <c r="F44" s="41" t="n">
-        <v>61.92307692307692</v>
-      </c>
-      <c r="G44" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H44" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="41" t="n">
-        <v>91.92307692307692</v>
-      </c>
-      <c r="K44" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="39" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="39" t="inlineStr">
-        <is>
-          <t>34.00/52.00</t>
-        </is>
-      </c>
-      <c r="E45" s="41" t="n">
-        <v>65.38461538461539</v>
-      </c>
-      <c r="F45" s="41" t="n">
-        <v>45.76923076923077</v>
-      </c>
-      <c r="G45" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H45" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="41" t="n">
-        <v>75.76923076923077</v>
-      </c>
-      <c r="K45" s="39" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="39" t="inlineStr">
-        <is>
-          <t>50.00/52.00</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="n">
-        <v>96.15384615384616</v>
-      </c>
-      <c r="F46" s="41" t="n">
-        <v>67.30769230769231</v>
-      </c>
-      <c r="G46" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H46" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="41" t="n">
-        <v>97.30769230769231</v>
-      </c>
-      <c r="K46" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="39" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="45" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="47" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="45" t="n"/>
+      <c r="B54" s="46" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="45" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="46" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="39" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="39" t="inlineStr">
-        <is>
-          <t>47.00/52.00</t>
-        </is>
-      </c>
-      <c r="E47" s="41" t="n">
-        <v>90.38461538461539</v>
-      </c>
-      <c r="F47" s="41" t="n">
-        <v>63.26923076923077</v>
-      </c>
-      <c r="G47" s="39" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H47" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="41" t="n">
-        <v>93.26923076923077</v>
-      </c>
-      <c r="K47" s="39" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="42" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="42" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="44" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="42" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="43" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="42" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="42" t="n"/>
-      <c r="B54" s="43" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="42" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="43" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="42" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="45" t="n">
-        <v>72.876254180602</v>
+      <c r="B56" s="48" t="n">
+        <v>65.63823857302118</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="42" t="inlineStr">
+      <c r="A57" s="45" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="45" t="n">
-        <v>26.47537326107639</v>
+      <c r="B57" s="48" t="n">
+        <v>23.79389133235755</v>
       </c>
     </row>
   </sheetData>

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-5780" windowWidth="25130" windowHeight="19430" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43480" yWindow="-5060" windowWidth="25130" windowHeight="19430" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -99,23 +99,12 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,13 +120,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -201,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,72 +224,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -303,19 +299,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T56"/>
+  <dimension ref="B2:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col width="1" customWidth="1" min="1" max="1"/>
@@ -646,19 +636,19 @@
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
     <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" style="36" min="12" max="20"/>
-    <col width="10.796875" customWidth="1" min="21" max="21"/>
+    <col width="4.6484375" customWidth="1" style="37" min="12" max="20"/>
+    <col width="4.796875" customWidth="1" min="21" max="26"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -675,7 +665,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -709,39 +699,49 @@
           <t>สรุปทั้งหมด 46 คน สถานะ Drop ติด W  0 คน</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Ex.2 Intro to Geodesy</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>EX.3 Draw Sphere/Spheroid</t>
         </is>
       </c>
-      <c r="N6" s="13" t="inlineStr">
+      <c r="N6" s="32" t="inlineStr">
         <is>
           <t>Ex.4 EFG for Sphere</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Ex.5 Guassian vs Mercator</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="39" t="inlineStr">
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>MidTerm</t>
         </is>
       </c>
-      <c r="R6" s="10" t="n"/>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>Ex.7 Lambert Conformal Conic</t>
+        </is>
+      </c>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="9" t="n"/>
     </row>
     <row r="7" ht="20.4" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
@@ -794,27 +794,35 @@
           <t>Email Office365</t>
         </is>
       </c>
-      <c r="L7" s="32" t="n">
+      <c r="L7" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="37" t="n">
+      <c r="M7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="34" t="n">
         <v>26</v>
       </c>
-      <c r="R7" s="33" t="n"/>
-      <c r="S7" s="33" t="n"/>
-      <c r="T7" s="33" t="n"/>
+      <c r="R7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="26" t="n"/>
+      <c r="T7" s="26" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="9" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
@@ -867,19 +875,27 @@
           <t>theerapat.ke@live.ku.th</t>
         </is>
       </c>
-      <c r="L8" s="34" t="n"/>
+      <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="10" t="n">
         <v>8</v>
       </c>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R8" s="10" t="n"/>
+      <c r="Q8" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="9" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
@@ -932,21 +948,29 @@
           <t>naphatson.nu@live.ku.th</t>
         </is>
       </c>
-      <c r="L9" s="34" t="n"/>
+      <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="11" t="n"/>
+      <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n">
         <v>10</v>
       </c>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="R9" s="10" t="n"/>
+      <c r="R9" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="9" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
@@ -999,23 +1023,29 @@
           <t>naraporn.ja@live.ku.th</t>
         </is>
       </c>
-      <c r="L10" s="34" t="n"/>
+      <c r="L10" s="10" t="n"/>
       <c r="M10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="11" t="n"/>
+      <c r="N10" s="10" t="n"/>
       <c r="O10" s="10" t="n">
         <v>5</v>
       </c>
       <c r="P10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="35" t="n">
         <v>4</v>
       </c>
       <c r="R10" s="10" t="n"/>
       <c r="S10" s="10" t="n"/>
       <c r="T10" s="10" t="n"/>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="9" t="n"/>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="9" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
@@ -1068,13 +1098,13 @@
           <t>bunyamin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L11" s="34" t="n">
+      <c r="L11" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O11" s="10" t="n">
@@ -1083,12 +1113,20 @@
       <c r="P11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="R11" s="10" t="n"/>
+      <c r="R11" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
@@ -1141,21 +1179,29 @@
           <t>panyanan.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L12" s="34" t="n"/>
+      <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
-      <c r="N12" s="11" t="n">
+      <c r="N12" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="10" t="n"/>
       <c r="P12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="Q12" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="R12" s="10" t="n"/>
+      <c r="R12" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="9" t="n"/>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="9" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
@@ -1208,17 +1254,25 @@
           <t>phinyada.sr@live.ku.th</t>
         </is>
       </c>
-      <c r="L13" s="34" t="n"/>
+      <c r="L13" s="10" t="n"/>
       <c r="M13" s="10" t="n"/>
-      <c r="N13" s="11" t="n"/>
+      <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="10" t="n"/>
+      <c r="R13" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="9" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
@@ -1271,23 +1325,31 @@
           <t>purin.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L14" s="34" t="n"/>
+      <c r="L14" s="10" t="n"/>
       <c r="M14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="11" t="n"/>
+      <c r="N14" s="10" t="n"/>
       <c r="O14" s="10" t="n">
         <v>5</v>
       </c>
       <c r="P14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="10" t="n"/>
+      <c r="R14" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -1340,13 +1402,13 @@
           <t>ratchanon.sakh@live.ku.th</t>
         </is>
       </c>
-      <c r="L15" s="34" t="n">
+      <c r="L15" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="10" t="n">
         <v>8</v>
       </c>
       <c r="O15" s="10" t="n">
@@ -1355,12 +1417,20 @@
       <c r="P15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="R15" s="10" t="n"/>
+      <c r="R15" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
@@ -1413,23 +1483,31 @@
           <t>worapon.pl@live.ku.th</t>
         </is>
       </c>
-      <c r="L16" s="34" t="n"/>
+      <c r="L16" s="10" t="n"/>
       <c r="M16" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O16" s="10" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="10" t="n"/>
+      <c r="R16" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
@@ -1482,13 +1560,13 @@
           <t>suphanat.chan@live.ku.th</t>
         </is>
       </c>
-      <c r="L17" s="34" t="n">
+      <c r="L17" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="10" t="n">
         <v>8</v>
       </c>
       <c r="O17" s="10" t="n">
@@ -1497,12 +1575,20 @@
       <c r="P17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="R17" s="10" t="n"/>
+      <c r="R17" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
@@ -1555,23 +1641,31 @@
           <t>settakamol.wa@live.ku.th</t>
         </is>
       </c>
-      <c r="L18" s="34" t="n"/>
+      <c r="L18" s="10" t="n"/>
       <c r="M18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="11" t="n"/>
+      <c r="N18" s="10" t="n"/>
       <c r="O18" s="10" t="n">
         <v>5</v>
       </c>
       <c r="P18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="R18" s="10" t="n"/>
+      <c r="R18" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="9" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
@@ -1624,17 +1718,25 @@
           <t>arisara.len@live.ku.th</t>
         </is>
       </c>
-      <c r="L19" s="34" t="n"/>
+      <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
-      <c r="N19" s="11" t="n"/>
+      <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n">
+      <c r="Q19" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="10" t="n"/>
+      <c r="R19" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
@@ -1687,13 +1789,13 @@
           <t>pattarapon.ditt@live.ku.th</t>
         </is>
       </c>
-      <c r="L20" s="34" t="n">
+      <c r="L20" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="N20" s="10" t="n">
         <v>9</v>
       </c>
       <c r="O20" s="10" t="n">
@@ -1702,12 +1804,20 @@
       <c r="P20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="R20" s="10" t="n"/>
+      <c r="R20" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="9" t="n"/>
+      <c r="Y20" s="9" t="n"/>
+      <c r="Z20" s="9" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
@@ -1760,23 +1870,29 @@
           <t>pakin.saen@live.ku.th</t>
         </is>
       </c>
-      <c r="L21" s="34" t="n">
+      <c r="L21" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="11" t="n"/>
+      <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n">
         <v>5</v>
       </c>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="35" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="10" t="n"/>
       <c r="S21" s="10" t="n"/>
       <c r="T21" s="10" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="9" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
@@ -1829,13 +1945,13 @@
           <t>kanol.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L22" s="34" t="n">
+      <c r="L22" s="10" t="n">
         <v>10</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O22" s="10" t="n">
@@ -1844,12 +1960,20 @@
       <c r="P22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="R22" s="10" t="n"/>
+      <c r="R22" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="10" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="9" t="n"/>
+      <c r="Y22" s="9" t="n"/>
+      <c r="Z22" s="9" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
@@ -1902,13 +2026,13 @@
           <t>kamonnit.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L23" s="34" t="n">
+      <c r="L23" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="N23" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O23" s="10" t="n">
@@ -1917,12 +2041,20 @@
       <c r="P23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="R23" s="10" t="n"/>
+      <c r="R23" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S23" s="10" t="n"/>
       <c r="T23" s="10" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
@@ -1975,13 +2107,13 @@
           <t>krisskon.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L24" s="34" t="n">
+      <c r="L24" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="N24" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O24" s="10" t="n">
@@ -1990,12 +2122,20 @@
       <c r="P24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="10" t="n"/>
+      <c r="R24" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S24" s="10" t="n"/>
       <c r="T24" s="10" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
@@ -2048,13 +2188,13 @@
           <t>kantiwat.ta@live.ku.th</t>
         </is>
       </c>
-      <c r="L25" s="34" t="n">
+      <c r="L25" s="10" t="n">
         <v>6</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="N25" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O25" s="10" t="n">
@@ -2063,12 +2203,20 @@
       <c r="P25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="R25" s="10" t="n"/>
+      <c r="R25" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S25" s="10" t="n"/>
       <c r="T25" s="10" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="9" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
@@ -2121,13 +2269,13 @@
           <t>kasemchoke.na@live.ku.th</t>
         </is>
       </c>
-      <c r="L26" s="34" t="n">
+      <c r="L26" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M26" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N26" s="11" t="n">
+      <c r="N26" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O26" s="10" t="n">
@@ -2136,12 +2284,20 @@
       <c r="P26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" s="10" t="n"/>
+      <c r="Q26" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
@@ -2194,25 +2350,33 @@
           <t>jakkarin.in@live.ku.th</t>
         </is>
       </c>
-      <c r="L27" s="34" t="n">
+      <c r="L27" s="10" t="n">
         <v>7</v>
       </c>
       <c r="M27" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N27" s="11" t="n"/>
+      <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n">
         <v>10</v>
       </c>
       <c r="P27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="10" t="n"/>
+      <c r="Q27" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="9" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
@@ -2265,23 +2429,31 @@
           <t>chanchao.t@live.ku.th</t>
         </is>
       </c>
-      <c r="L28" s="34" t="n">
+      <c r="L28" s="10" t="n">
         <v>7</v>
       </c>
       <c r="M28" s="10" t="n"/>
-      <c r="N28" s="11" t="n">
+      <c r="N28" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O28" s="10" t="n">
         <v>4</v>
       </c>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="R28" s="10" t="n"/>
+      <c r="R28" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="9" t="n"/>
+      <c r="Y28" s="9" t="n"/>
+      <c r="Z28" s="9" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
@@ -2334,13 +2506,13 @@
           <t>tikamporn.tr@live.ku.th</t>
         </is>
       </c>
-      <c r="L29" s="34" t="n">
+      <c r="L29" s="10" t="n">
         <v>6</v>
       </c>
       <c r="M29" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="N29" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O29" s="10" t="n">
@@ -2349,12 +2521,20 @@
       <c r="P29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="R29" s="10" t="n"/>
+      <c r="R29" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S29" s="10" t="n"/>
       <c r="T29" s="10" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="9" t="n"/>
+      <c r="Y29" s="9" t="n"/>
+      <c r="Z29" s="9" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="5" t="inlineStr">
@@ -2407,13 +2587,13 @@
           <t>napapach.bu@live.ku.th</t>
         </is>
       </c>
-      <c r="L30" s="34" t="n">
+      <c r="L30" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="N30" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O30" s="10" t="n">
@@ -2422,12 +2602,20 @@
       <c r="P30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="R30" s="10" t="n"/>
+      <c r="R30" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="9" t="n"/>
+      <c r="Z30" s="9" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="5" t="inlineStr">
@@ -2480,15 +2668,21 @@
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="34" t="n"/>
+      <c r="L31" s="10" t="n"/>
       <c r="M31" s="10" t="n"/>
-      <c r="N31" s="11" t="n"/>
+      <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
-      <c r="Q31" s="10" t="n"/>
+      <c r="Q31" s="35" t="n"/>
       <c r="R31" s="10" t="n"/>
       <c r="S31" s="10" t="n"/>
       <c r="T31" s="10" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="9" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
@@ -2541,13 +2735,13 @@
           <t>thanaphum.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L32" s="34" t="n">
+      <c r="L32" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M32" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N32" s="11" t="n">
+      <c r="N32" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O32" s="10" t="n">
@@ -2556,12 +2750,20 @@
       <c r="P32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="R32" s="10" t="n"/>
+      <c r="R32" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
+      <c r="Y32" s="9" t="n"/>
+      <c r="Z32" s="9" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
@@ -2614,96 +2816,112 @@
           <t>thanakon.r@live.ku.th</t>
         </is>
       </c>
-      <c r="L33" s="34" t="n">
+      <c r="L33" s="10" t="n">
         <v>5</v>
       </c>
       <c r="M33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N33" s="11" t="n"/>
+      <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n">
         <v>10</v>
       </c>
       <c r="P33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="R33" s="10" t="n"/>
+      <c r="R33" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>6710553094</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>นายธรรมกร เจริญพร</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>Mr. THAMMAKORN CHAROENPORN</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G34" s="29" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H34" s="29" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I34" s="29" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J34" s="29" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>thammakorn.c@ku.th</t>
         </is>
       </c>
-      <c r="K34" s="30" t="inlineStr">
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>thammakorn.c@live.ku.th</t>
         </is>
       </c>
-      <c r="L34" s="31" t="n">
+      <c r="L34" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="M34" s="31" t="n">
+      <c r="M34" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="31" t="n">
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
+      <c r="R34" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" s="25" t="n"/>
+      <c r="T34" s="25" t="n"/>
+      <c r="U34" s="9" t="n"/>
+      <c r="V34" s="9" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="9" t="n"/>
+      <c r="Y34" s="9" t="n"/>
+      <c r="Z34" s="9" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
@@ -2756,13 +2974,13 @@
           <t>thattawan.y@live.ku.th</t>
         </is>
       </c>
-      <c r="L35" s="34" t="n">
+      <c r="L35" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N35" s="11" t="n">
+      <c r="N35" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O35" s="10" t="n">
@@ -2771,12 +2989,20 @@
       <c r="P35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="R35" s="10" t="n"/>
+      <c r="R35" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="5" t="inlineStr">
@@ -2829,13 +3055,13 @@
           <t>nonthakorn.j@live.ku.th</t>
         </is>
       </c>
-      <c r="L36" s="34" t="n">
+      <c r="L36" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M36" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="11" t="n">
+      <c r="N36" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O36" s="10" t="n">
@@ -2844,12 +3070,20 @@
       <c r="P36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="R36" s="10" t="n"/>
+      <c r="R36" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S36" s="10" t="n"/>
       <c r="T36" s="10" t="n"/>
+      <c r="U36" s="9" t="n"/>
+      <c r="V36" s="9" t="n"/>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="9" t="n"/>
+      <c r="Y36" s="9" t="n"/>
+      <c r="Z36" s="9" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
@@ -2902,13 +3136,13 @@
           <t>naputrapee.a@live.ku.th</t>
         </is>
       </c>
-      <c r="L37" s="34" t="n">
+      <c r="L37" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M37" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="N37" s="11" t="n">
+      <c r="N37" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O37" s="10" t="n">
@@ -2917,12 +3151,20 @@
       <c r="P37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="R37" s="10" t="n"/>
+      <c r="R37" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="9" t="n"/>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="9" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
@@ -2975,11 +3217,11 @@
           <t>pichayut.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L38" s="34" t="n"/>
+      <c r="L38" s="10" t="n"/>
       <c r="M38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N38" s="11" t="n">
+      <c r="N38" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O38" s="10" t="n">
@@ -2988,12 +3230,20 @@
       <c r="P38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="R38" s="10" t="n"/>
+      <c r="R38" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="9" t="n"/>
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="9" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="5" t="inlineStr">
@@ -3046,13 +3296,13 @@
           <t>pakhawat.p@live.ku.th</t>
         </is>
       </c>
-      <c r="L39" s="34" t="n">
+      <c r="L39" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N39" s="11" t="n">
+      <c r="N39" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O39" s="10" t="n">
@@ -3061,12 +3311,20 @@
       <c r="P39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="R39" s="10" t="n"/>
+      <c r="R39" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S39" s="10" t="n"/>
       <c r="T39" s="10" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="9" t="n"/>
+      <c r="Y39" s="9" t="n"/>
+      <c r="Z39" s="9" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="5" t="inlineStr">
@@ -3119,13 +3377,13 @@
           <t>phakkaphon.l@live.ku.th</t>
         </is>
       </c>
-      <c r="L40" s="34" t="n">
+      <c r="L40" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M40" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N40" s="11" t="n">
+      <c r="N40" s="10" t="n">
         <v>9</v>
       </c>
       <c r="O40" s="10" t="n">
@@ -3134,12 +3392,20 @@
       <c r="P40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="R40" s="10" t="n"/>
+      <c r="R40" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="10" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="V40" s="9" t="n"/>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="9" t="n"/>
+      <c r="Y40" s="9" t="n"/>
+      <c r="Z40" s="9" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
@@ -3192,13 +3458,13 @@
           <t>pakkapon.i@live.ku.th</t>
         </is>
       </c>
-      <c r="L41" s="34" t="n">
+      <c r="L41" s="10" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N41" s="11" t="n">
+      <c r="N41" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O41" s="10" t="n">
@@ -3207,12 +3473,20 @@
       <c r="P41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="10" t="n"/>
+      <c r="R41" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="S41" s="10" t="n"/>
       <c r="T41" s="10" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n"/>
+      <c r="Y41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
@@ -3265,25 +3539,33 @@
           <t>yuttana.sukku@live.ku.th</t>
         </is>
       </c>
-      <c r="L42" s="34" t="n">
+      <c r="L42" s="10" t="n">
         <v>10</v>
       </c>
       <c r="M42" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N42" s="11" t="n">
+      <c r="N42" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O42" s="10" t="n">
         <v>10</v>
       </c>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="R42" s="10" t="n"/>
+      <c r="R42" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="V42" s="9" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="9" t="n"/>
+      <c r="Y42" s="9" t="n"/>
+      <c r="Z42" s="9" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="5" t="inlineStr">
@@ -3336,13 +3618,13 @@
           <t>rapeepat.mo@live.ku.th</t>
         </is>
       </c>
-      <c r="L43" s="34" t="n">
+      <c r="L43" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M43" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="N43" s="11" t="n">
+      <c r="N43" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O43" s="10" t="n">
@@ -3351,12 +3633,20 @@
       <c r="P43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="R43" s="10" t="n"/>
+      <c r="R43" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n"/>
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="9" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="5" t="inlineStr">
@@ -3409,13 +3699,13 @@
           <t>veerapat.d@live.ku.th</t>
         </is>
       </c>
-      <c r="L44" s="34" t="n">
+      <c r="L44" s="10" t="n">
         <v>5</v>
       </c>
       <c r="M44" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N44" s="11" t="n">
+      <c r="N44" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O44" s="10" t="n">
@@ -3424,12 +3714,20 @@
       <c r="P44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="R44" s="10" t="n"/>
+      <c r="R44" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
+      <c r="U44" s="9" t="n"/>
+      <c r="V44" s="9" t="n"/>
+      <c r="W44" s="9" t="n"/>
+      <c r="X44" s="9" t="n"/>
+      <c r="Y44" s="9" t="n"/>
+      <c r="Z44" s="9" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="5" t="inlineStr">
@@ -3482,13 +3780,13 @@
           <t>savita.cha@live.ku.th</t>
         </is>
       </c>
-      <c r="L45" s="34" t="n">
+      <c r="L45" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M45" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="11" t="n">
+      <c r="N45" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O45" s="10" t="n">
@@ -3497,12 +3795,20 @@
       <c r="P45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" s="10" t="n">
+      <c r="Q45" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="R45" s="10" t="n"/>
+      <c r="R45" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="9" t="n"/>
+      <c r="Z45" s="9" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="5" t="inlineStr">
@@ -3555,13 +3861,13 @@
           <t>sorasak.cot@live.ku.th</t>
         </is>
       </c>
-      <c r="L46" s="34" t="n">
+      <c r="L46" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N46" s="11" t="n">
+      <c r="N46" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O46" s="10" t="n">
@@ -3570,12 +3876,20 @@
       <c r="P46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="R46" s="10" t="n"/>
+      <c r="R46" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
+      <c r="U46" s="9" t="n"/>
+      <c r="V46" s="9" t="n"/>
+      <c r="W46" s="9" t="n"/>
+      <c r="X46" s="9" t="n"/>
+      <c r="Y46" s="9" t="n"/>
+      <c r="Z46" s="9" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="5" t="inlineStr">
@@ -3628,13 +3942,13 @@
           <t>sarawut.ya@live.ku.th</t>
         </is>
       </c>
-      <c r="L47" s="34" t="n">
+      <c r="L47" s="10" t="n">
         <v>10</v>
       </c>
       <c r="M47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N47" s="11" t="n">
+      <c r="N47" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O47" s="10" t="n">
@@ -3643,12 +3957,20 @@
       <c r="P47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="Q47" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="R47" s="10" t="n"/>
+      <c r="R47" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="S47" s="10" t="n"/>
       <c r="T47" s="10" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="9" t="n"/>
+      <c r="Z47" s="9" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="5" t="inlineStr">
@@ -3701,13 +4023,13 @@
           <t>sitthichailoet.s@live.ku.th</t>
         </is>
       </c>
-      <c r="L48" s="34" t="n">
+      <c r="L48" s="10" t="n">
         <v>10</v>
       </c>
       <c r="M48" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="N48" s="11" t="n">
+      <c r="N48" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O48" s="10" t="n">
@@ -3716,12 +4038,20 @@
       <c r="P48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="R48" s="10" t="n"/>
+      <c r="R48" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="n"/>
+      <c r="U48" s="9" t="n"/>
+      <c r="V48" s="9" t="n"/>
+      <c r="W48" s="9" t="n"/>
+      <c r="X48" s="9" t="n"/>
+      <c r="Y48" s="9" t="n"/>
+      <c r="Z48" s="9" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="5" t="inlineStr">
@@ -3774,13 +4104,13 @@
           <t>sutichode.b@live.ku.th</t>
         </is>
       </c>
-      <c r="L49" s="34" t="n">
+      <c r="L49" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M49" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N49" s="11" t="n">
+      <c r="N49" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O49" s="10" t="n">
@@ -3789,12 +4119,20 @@
       <c r="P49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="R49" s="10" t="n"/>
+      <c r="R49" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="9" t="n"/>
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="9" t="n"/>
+      <c r="Y49" s="9" t="n"/>
+      <c r="Z49" s="9" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="5" t="inlineStr">
@@ -3847,13 +4185,13 @@
           <t>sumath.o@live.ku.th</t>
         </is>
       </c>
-      <c r="L50" s="34" t="n">
+      <c r="L50" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N50" s="11" t="n">
+      <c r="N50" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O50" s="10" t="n">
@@ -3862,12 +4200,20 @@
       <c r="P50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="R50" s="10" t="n"/>
+      <c r="R50" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S50" s="10" t="n"/>
       <c r="T50" s="10" t="n"/>
+      <c r="U50" s="9" t="n"/>
+      <c r="V50" s="9" t="n"/>
+      <c r="W50" s="9" t="n"/>
+      <c r="X50" s="9" t="n"/>
+      <c r="Y50" s="9" t="n"/>
+      <c r="Z50" s="9" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="5" t="inlineStr">
@@ -3920,25 +4266,33 @@
           <t>aussanee.ko@live.ku.th</t>
         </is>
       </c>
-      <c r="L51" s="34" t="n">
+      <c r="L51" s="10" t="n">
         <v>7</v>
       </c>
       <c r="M51" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N51" s="11" t="n">
+      <c r="N51" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O51" s="10" t="n">
         <v>10</v>
       </c>
       <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="R51" s="10" t="n"/>
+      <c r="R51" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="S51" s="10" t="n"/>
       <c r="T51" s="10" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="9" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="X51" s="9" t="n"/>
+      <c r="Y51" s="9" t="n"/>
+      <c r="Z51" s="9" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
@@ -3991,13 +4345,13 @@
           <t>atitaya.thai@live.ku.th</t>
         </is>
       </c>
-      <c r="L52" s="34" t="n">
+      <c r="L52" s="10" t="n">
         <v>12</v>
       </c>
       <c r="M52" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="N52" s="11" t="n">
+      <c r="N52" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O52" s="10" t="n">
@@ -4006,12 +4360,20 @@
       <c r="P52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" s="10" t="n">
+      <c r="Q52" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="R52" s="10" t="n"/>
+      <c r="R52" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
+      <c r="U52" s="9" t="n"/>
+      <c r="V52" s="9" t="n"/>
+      <c r="W52" s="9" t="n"/>
+      <c r="X52" s="9" t="n"/>
+      <c r="Y52" s="9" t="n"/>
+      <c r="Z52" s="9" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
@@ -4064,13 +4426,13 @@
           <t>araya.sansu@live.ku.th</t>
         </is>
       </c>
-      <c r="L53" s="34" t="n">
+      <c r="L53" s="10" t="n">
         <v>8</v>
       </c>
       <c r="M53" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N53" s="11" t="n">
+      <c r="N53" s="10" t="n">
         <v>10</v>
       </c>
       <c r="O53" s="10" t="n">
@@ -4079,15 +4441,23 @@
       <c r="P53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="10" t="n">
+      <c r="Q53" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="R53" s="10" t="n"/>
+      <c r="R53" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="S53" s="10" t="n"/>
       <c r="T53" s="10" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="9" t="n"/>
+      <c r="X53" s="9" t="n"/>
+      <c r="Y53" s="9" t="n"/>
+      <c r="Z53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="Q54" s="38" t="inlineStr">
+      <c r="Q54" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4126,10 +4496,10 @@
     <col width="6.94921875" customWidth="1" min="1" max="1"/>
     <col width="16.19921875" customWidth="1" min="2" max="2"/>
     <col width="31.046875" customWidth="1" min="3" max="3"/>
-    <col width="3.796875" customWidth="1" style="15" min="4" max="4"/>
+    <col width="3.796875" customWidth="1" style="12" min="4" max="4"/>
     <col width="3.796875" customWidth="1" min="5" max="5"/>
-    <col width="3.796875" customWidth="1" style="21" min="6" max="6"/>
-    <col width="3.796875" customWidth="1" style="24" min="7" max="7"/>
+    <col width="3.796875" customWidth="1" style="18" min="6" max="6"/>
+    <col width="3.796875" customWidth="1" style="20" min="7" max="7"/>
     <col width="3.796875" customWidth="1" min="8" max="14"/>
     <col width="8.796875" customWidth="1" min="15" max="15"/>
     <col width="4.6484375" customWidth="1" min="16" max="26"/>
@@ -4144,58 +4514,56 @@
           <t>การเข้าเรียน</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>04-14JUL69</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="38" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>24-Aug-2026\</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="n"/>
+      <c r="G6" s="39" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="29">
         <f>Exercise!B7</f>
         <v/>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="29">
         <f>Exercise!C7</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="29">
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="26" t="n"/>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="26" t="n"/>
-      <c r="K7" s="26" t="n"/>
-      <c r="L7" s="26" t="n"/>
-      <c r="M7" s="26" t="n"/>
-      <c r="N7" s="26" t="n"/>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="30" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="30" t="n"/>
+      <c r="I7" s="30" t="n"/>
+      <c r="J7" s="30" t="n"/>
+      <c r="K7" s="30" t="n"/>
+      <c r="L7" s="30" t="n"/>
+      <c r="M7" s="30" t="n"/>
+      <c r="N7" s="30" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -4210,14 +4578,14 @@
         <f>Exercise!D8</f>
         <v/>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="n"/>
+      <c r="D8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
@@ -4239,12 +4607,12 @@
         <f>Exercise!D9</f>
         <v/>
       </c>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="25" t="n">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n"/>
@@ -4268,12 +4636,12 @@
         <f>Exercise!D10</f>
         <v/>
       </c>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="25" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="21" t="n"/>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
@@ -4295,16 +4663,16 @@
         <f>Exercise!D11</f>
         <v/>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="25" t="n">
+      <c r="D11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="9" t="n"/>
@@ -4328,16 +4696,16 @@
         <f>Exercise!D12</f>
         <v/>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="n">
+      <c r="D12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="9" t="n"/>
@@ -4361,12 +4729,12 @@
         <f>Exercise!D13</f>
         <v/>
       </c>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="25" t="n">
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="9" t="n"/>
@@ -4390,14 +4758,14 @@
         <f>Exercise!D14</f>
         <v/>
       </c>
-      <c r="D14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25" t="n">
+      <c r="D14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="9" t="n"/>
@@ -4421,16 +4789,16 @@
         <f>Exercise!D15</f>
         <v/>
       </c>
-      <c r="D15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="25" t="n">
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="9" t="n"/>
@@ -4454,16 +4822,16 @@
         <f>Exercise!D16</f>
         <v/>
       </c>
-      <c r="D16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="n">
+      <c r="D16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="9" t="n"/>
@@ -4487,16 +4855,16 @@
         <f>Exercise!D17</f>
         <v/>
       </c>
-      <c r="D17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="25" t="n">
+      <c r="D17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="9" t="n"/>
@@ -4520,14 +4888,14 @@
         <f>Exercise!D18</f>
         <v/>
       </c>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="n">
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="n"/>
@@ -4551,10 +4919,10 @@
         <f>Exercise!D19</f>
         <v/>
       </c>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="25" t="n">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="n"/>
@@ -4578,12 +4946,12 @@
         <f>Exercise!D20</f>
         <v/>
       </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="n">
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="n"/>
@@ -4607,14 +4975,14 @@
         <f>Exercise!D21</f>
         <v/>
       </c>
-      <c r="D21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="25" t="n"/>
+      <c r="D21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="21" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
@@ -4636,16 +5004,16 @@
         <f>Exercise!D22</f>
         <v/>
       </c>
-      <c r="D22" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="n">
+      <c r="D22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="9" t="n"/>
@@ -4669,16 +5037,16 @@
         <f>Exercise!D23</f>
         <v/>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25" t="n">
+      <c r="D23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="9" t="n"/>
@@ -4702,16 +5070,16 @@
         <f>Exercise!D24</f>
         <v/>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="n">
+      <c r="D24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="9" t="n"/>
@@ -4735,16 +5103,16 @@
         <f>Exercise!D25</f>
         <v/>
       </c>
-      <c r="D25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="25" t="n">
+      <c r="D25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="9" t="n"/>
@@ -4768,16 +5136,16 @@
         <f>Exercise!D26</f>
         <v/>
       </c>
-      <c r="D26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25" t="n">
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="9" t="n"/>
@@ -4801,14 +5169,14 @@
         <f>Exercise!D27</f>
         <v/>
       </c>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="25" t="n">
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="9" t="n"/>
@@ -4832,14 +5200,14 @@
         <f>Exercise!D28</f>
         <v/>
       </c>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="25" t="n">
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="9" t="n"/>
@@ -4863,16 +5231,16 @@
         <f>Exercise!D29</f>
         <v/>
       </c>
-      <c r="D29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25" t="n">
+      <c r="D29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="9" t="n"/>
@@ -4896,16 +5264,16 @@
         <f>Exercise!D30</f>
         <v/>
       </c>
-      <c r="D30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="25" t="n">
+      <c r="D30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="9" t="n"/>
@@ -4929,10 +5297,10 @@
         <f>Exercise!D31</f>
         <v/>
       </c>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="25" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="21" t="n"/>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
       <c r="J31" s="9" t="n"/>
@@ -4954,16 +5322,16 @@
         <f>Exercise!D32</f>
         <v/>
       </c>
-      <c r="D32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="25" t="n">
+      <c r="D32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="9" t="n"/>
@@ -4987,14 +5355,14 @@
         <f>Exercise!D33</f>
         <v/>
       </c>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="25" t="n">
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="n"/>
@@ -5018,16 +5386,16 @@
         <f>Exercise!D34</f>
         <v/>
       </c>
-      <c r="D34" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="25" t="n">
+      <c r="D34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="9" t="n"/>
@@ -5051,16 +5419,16 @@
         <f>Exercise!D35</f>
         <v/>
       </c>
-      <c r="D35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="25" t="n">
+      <c r="D35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="9" t="n"/>
@@ -5084,16 +5452,16 @@
         <f>Exercise!D36</f>
         <v/>
       </c>
-      <c r="D36" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="25" t="n">
+      <c r="D36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="9" t="n"/>
@@ -5117,16 +5485,16 @@
         <f>Exercise!D37</f>
         <v/>
       </c>
-      <c r="D37" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="25" t="n">
+      <c r="D37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="n"/>
@@ -5150,14 +5518,14 @@
         <f>Exercise!D38</f>
         <v/>
       </c>
-      <c r="D38" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="25" t="n">
+      <c r="D38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="9" t="n"/>
@@ -5181,16 +5549,16 @@
         <f>Exercise!D39</f>
         <v/>
       </c>
-      <c r="D39" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="25" t="n">
+      <c r="D39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="n"/>
@@ -5214,16 +5582,16 @@
         <f>Exercise!D40</f>
         <v/>
       </c>
-      <c r="D40" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="25" t="n">
+      <c r="D40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -5247,16 +5615,16 @@
         <f>Exercise!D41</f>
         <v/>
       </c>
-      <c r="D41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="25" t="n">
+      <c r="D41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="9" t="n"/>
@@ -5280,16 +5648,16 @@
         <f>Exercise!D42</f>
         <v/>
       </c>
-      <c r="D42" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="25" t="n">
+      <c r="D42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="9" t="n"/>
@@ -5313,16 +5681,16 @@
         <f>Exercise!D43</f>
         <v/>
       </c>
-      <c r="D43" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="25" t="n">
+      <c r="D43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="9" t="n"/>
@@ -5346,16 +5714,16 @@
         <f>Exercise!D44</f>
         <v/>
       </c>
-      <c r="D44" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="25" t="n">
+      <c r="D44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -5379,16 +5747,16 @@
         <f>Exercise!D45</f>
         <v/>
       </c>
-      <c r="D45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="25" t="n">
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="9" t="n"/>
@@ -5412,16 +5780,16 @@
         <f>Exercise!D46</f>
         <v/>
       </c>
-      <c r="D46" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="25" t="n">
+      <c r="D46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -5445,16 +5813,16 @@
         <f>Exercise!D47</f>
         <v/>
       </c>
-      <c r="D47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="25" t="n">
+      <c r="D47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="9" t="n"/>
@@ -5478,16 +5846,16 @@
         <f>Exercise!D48</f>
         <v/>
       </c>
-      <c r="D48" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="25" t="n">
+      <c r="D48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="9" t="n"/>
@@ -5511,16 +5879,16 @@
         <f>Exercise!D49</f>
         <v/>
       </c>
-      <c r="D49" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="25" t="n">
+      <c r="D49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="9" t="n"/>
@@ -5544,16 +5912,16 @@
         <f>Exercise!D50</f>
         <v/>
       </c>
-      <c r="D50" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="25" t="n">
+      <c r="D50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="9" t="n"/>
@@ -5577,16 +5945,16 @@
         <f>Exercise!D51</f>
         <v/>
       </c>
-      <c r="D51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="25" t="n">
+      <c r="D51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="9" t="n"/>
@@ -5610,16 +5978,16 @@
         <f>Exercise!D52</f>
         <v/>
       </c>
-      <c r="D52" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="25" t="n">
+      <c r="D52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="9" t="n"/>
@@ -5643,16 +6011,16 @@
         <f>Exercise!D53</f>
         <v/>
       </c>
-      <c r="D53" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="25" t="n">
+      <c r="D53" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="9" t="n"/>
@@ -5691,2204 +6059,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
+      <c r="E1" s="40" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="41" t="inlineStr">
+      <c r="F1" s="40" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="41" t="inlineStr">
+      <c r="G1" s="40" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="41" t="inlineStr">
+      <c r="H1" s="40" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="41" t="inlineStr">
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="41" t="inlineStr">
+      <c r="J1" s="40" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="41" t="inlineStr">
+      <c r="K1" s="40" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="A2" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="43" t="inlineStr">
+      <c r="C2" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr">
-        <is>
-          <t>18.00/78.00</t>
-        </is>
-      </c>
-      <c r="E2" s="44" t="n">
-        <v>23.07692307692308</v>
-      </c>
-      <c r="F2" s="44" t="n">
-        <v>16.15384615384615</v>
-      </c>
-      <c r="G2" s="42" t="inlineStr">
+      <c r="D2" s="41" t="inlineStr">
+        <is>
+          <t>23.00/88.00</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="n">
+        <v>26.13636363636364</v>
+      </c>
+      <c r="F2" s="43" t="n">
+        <v>18.29545454545454</v>
+      </c>
+      <c r="G2" s="41" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="H2" s="44" t="n">
+      <c r="H2" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="I2" s="44" t="n">
+      <c r="I2" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="44" t="n">
-        <v>31.15384615384615</v>
-      </c>
-      <c r="K2" s="42" t="inlineStr">
+      <c r="J2" s="43" t="n">
+        <v>33.29545454545455</v>
+      </c>
+      <c r="K2" s="41" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="n">
+      <c r="A3" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>6610553165</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
-        <is>
-          <t>17.00/78.00</t>
-        </is>
-      </c>
-      <c r="E3" s="44" t="n">
-        <v>21.7948717948718</v>
-      </c>
-      <c r="F3" s="44" t="n">
-        <v>15.25641025641026</v>
-      </c>
-      <c r="G3" s="42" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
+        <is>
+          <t>27.00/88.00</t>
+        </is>
+      </c>
+      <c r="E3" s="43" t="n">
+        <v>30.68181818181818</v>
+      </c>
+      <c r="F3" s="43" t="n">
+        <v>21.47727272727273</v>
+      </c>
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="H3" s="44" t="n">
+      <c r="H3" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="I3" s="44" t="n">
+      <c r="I3" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="44" t="n">
-        <v>30.25641025641026</v>
-      </c>
-      <c r="K3" s="42" t="inlineStr">
+      <c r="J3" s="43" t="n">
+        <v>36.47727272727273</v>
+      </c>
+      <c r="K3" s="41" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="n">
+      <c r="A4" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>6610553173</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>20.00/78.00</t>
-        </is>
-      </c>
-      <c r="E4" s="44" t="n">
-        <v>25.64102564102564</v>
-      </c>
-      <c r="F4" s="44" t="n">
-        <v>17.94871794871795</v>
-      </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>20.00/88.00</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="F4" s="43" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="H4" s="44" t="n">
+      <c r="H4" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="I4" s="44" t="n">
+      <c r="I4" s="43" t="n">
         <v>7.5</v>
       </c>
-      <c r="J4" s="44" t="n">
-        <v>25.44871794871795</v>
-      </c>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="J4" s="43" t="n">
+        <v>23.40909090909091</v>
+      </c>
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="n">
+      <c r="A5" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>6610553181</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>44.00/78.00</t>
-        </is>
-      </c>
-      <c r="E5" s="44" t="n">
-        <v>56.41025641025641</v>
-      </c>
-      <c r="F5" s="44" t="n">
-        <v>39.48717948717949</v>
-      </c>
-      <c r="G5" s="42" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>54.00/88.00</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="n">
+        <v>61.36363636363637</v>
+      </c>
+      <c r="F5" s="43" t="n">
+        <v>42.95454545454545</v>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H5" s="44" t="n">
+      <c r="H5" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="44" t="n">
-        <v>69.48717948717949</v>
-      </c>
-      <c r="K5" s="42" t="inlineStr">
+      <c r="J5" s="43" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="K5" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="inlineStr">
+        <is>
+          <t>36.00/88.00</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <v>28.63636363636364</v>
+      </c>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="43" t="n">
+        <v>58.63636363636364</v>
+      </c>
+      <c r="K6" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>5.00/88.00</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>5.681818181818182</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <v>3.977272727272727</v>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="43" t="n">
+        <v>18.97727272727273</v>
+      </c>
+      <c r="K7" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>29.00/88.00</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>32.95454545454545</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>23.06818181818182</v>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="I8" s="43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J8" s="43" t="n">
+        <v>45.56818181818181</v>
+      </c>
+      <c r="K8" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>54.00/88.00</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>61.36363636363637</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>42.95454545454545</v>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="43" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="K9" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="inlineStr">
+        <is>
+          <t>39.00/88.00</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>44.31818181818182</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>31.02272727272727</v>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H10" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="43" t="n">
+        <v>61.02272727272727</v>
+      </c>
+      <c r="K10" s="41" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="42" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>26.00/78.00</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="F6" s="44" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="G6" s="42" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>57.00/88.00</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>64.77272727272727</v>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>45.34090909090909</v>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H6" s="44" t="n">
+      <c r="H11" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="44" t="n">
+      <c r="I11" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J6" s="44" t="n">
-        <v>53.33333333333333</v>
-      </c>
-      <c r="K6" s="42" t="inlineStr">
+      <c r="J11" s="43" t="n">
+        <v>75.34090909090909</v>
+      </c>
+      <c r="K11" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>31.00/88.00</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="F12" s="43" t="n">
+        <v>24.65909090909091</v>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H12" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" s="43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J12" s="43" t="n">
+        <v>47.15909090909091</v>
+      </c>
+      <c r="K12" s="41" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>0.00/78.00</t>
-        </is>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>10.00/88.00</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="F13" s="43" t="n">
+        <v>7.954545454545454</v>
+      </c>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>15.45454545454545</v>
+      </c>
+      <c r="K13" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>50.00/88.00</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>56.81818181818182</v>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>39.77272727272727</v>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H14" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="43" t="n">
+        <v>54.77272727272727</v>
+      </c>
+      <c r="K14" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>28.00/88.00</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>31.81818181818182</v>
+      </c>
+      <c r="F15" s="43" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H15" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="43" t="n">
+        <v>37.27272727272727</v>
+      </c>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>56.00/88.00</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>44.54545454545455</v>
+      </c>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H16" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="43" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>71.00/88.00</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>80.68181818181817</v>
+      </c>
+      <c r="F17" s="43" t="n">
+        <v>56.47727272727273</v>
+      </c>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H17" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="43" t="n">
+        <v>86.47727272727272</v>
+      </c>
+      <c r="K17" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="inlineStr">
+        <is>
+          <t>70.00/88.00</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>79.54545454545455</v>
+      </c>
+      <c r="F18" s="43" t="n">
+        <v>55.68181818181818</v>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H18" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="43" t="n">
+        <v>85.68181818181819</v>
+      </c>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="41" t="inlineStr">
+        <is>
+          <t>54.00/88.00</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>61.36363636363637</v>
+      </c>
+      <c r="F19" s="43" t="n">
+        <v>42.95454545454545</v>
+      </c>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="43" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
+        <is>
+          <t>58.00/88.00</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>65.90909090909091</v>
+      </c>
+      <c r="F20" s="43" t="n">
+        <v>46.13636363636363</v>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H20" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="43" t="n">
+        <v>76.13636363636363</v>
+      </c>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
+        <is>
+          <t>43.00/88.00</t>
+        </is>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>48.86363636363637</v>
+      </c>
+      <c r="F21" s="43" t="n">
+        <v>34.20454545454545</v>
+      </c>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H21" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" s="43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J21" s="43" t="n">
+        <v>56.70454545454545</v>
+      </c>
+      <c r="K21" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="41" t="inlineStr">
+        <is>
+          <t>36.00/88.00</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="F22" s="43" t="n">
+        <v>28.63636363636364</v>
+      </c>
+      <c r="G22" s="41" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H22" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" s="43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J22" s="43" t="n">
+        <v>51.13636363636364</v>
+      </c>
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>63.00/88.00</t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>71.59090909090909</v>
+      </c>
+      <c r="F23" s="43" t="n">
+        <v>50.11363636363637</v>
+      </c>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H23" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="43" t="n">
+        <v>80.11363636363637</v>
+      </c>
+      <c r="K23" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="41" t="inlineStr">
+        <is>
+          <t>73.00/88.00</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>82.95454545454545</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <v>58.06818181818182</v>
+      </c>
+      <c r="G24" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H24" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="43" t="n">
+        <v>88.06818181818181</v>
+      </c>
+      <c r="K24" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>0.00/88.00</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F25" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="42" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H7" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="42" t="inlineStr">
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H25" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="41" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>19.00/78.00</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="n">
-        <v>24.35897435897436</v>
-      </c>
-      <c r="F8" s="44" t="n">
-        <v>17.05128205128205</v>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>70.00/88.00</t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="n">
+        <v>79.54545454545455</v>
+      </c>
+      <c r="F26" s="43" t="n">
+        <v>55.68181818181818</v>
+      </c>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H26" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="43" t="n">
+        <v>85.68181818181819</v>
+      </c>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="41" t="inlineStr">
+        <is>
+          <t>48.00/88.00</t>
+        </is>
+      </c>
+      <c r="E27" s="43" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="F27" s="43" t="n">
+        <v>38.18181818181818</v>
+      </c>
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H27" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="I8" s="44" t="n">
+      <c r="I27" s="43" t="n">
         <v>22.5</v>
       </c>
-      <c r="J8" s="44" t="n">
-        <v>39.55128205128205</v>
-      </c>
-      <c r="K8" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="42" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="J27" s="43" t="n">
+        <v>60.68181818181818</v>
+      </c>
+      <c r="K27" s="41" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>46.00/78.00</t>
-        </is>
-      </c>
-      <c r="E9" s="44" t="n">
-        <v>58.97435897435898</v>
-      </c>
-      <c r="F9" s="44" t="n">
-        <v>41.28205128205128</v>
-      </c>
-      <c r="G9" s="42" t="inlineStr">
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>71.00/88.00</t>
+        </is>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>80.68181818181817</v>
+      </c>
+      <c r="F28" s="43" t="n">
+        <v>56.47727272727273</v>
+      </c>
+      <c r="G28" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H28" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="44" t="n">
+      <c r="I28" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J9" s="44" t="n">
-        <v>71.28205128205128</v>
-      </c>
-      <c r="K9" s="42" t="inlineStr">
+      <c r="J28" s="43" t="n">
+        <v>86.47727272727272</v>
+      </c>
+      <c r="K28" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>72.00/88.00</t>
+        </is>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>81.81818181818183</v>
+      </c>
+      <c r="F29" s="43" t="n">
+        <v>57.27272727272727</v>
+      </c>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H29" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="43" t="n">
+        <v>87.27272727272728</v>
+      </c>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>64.00/88.00</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="F30" s="43" t="n">
+        <v>50.90909090909091</v>
+      </c>
+      <c r="G30" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H30" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="43" t="n">
+        <v>80.90909090909091</v>
+      </c>
+      <c r="K30" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="41" t="inlineStr">
+        <is>
+          <t>75.00/88.00</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>85.22727272727273</v>
+      </c>
+      <c r="F31" s="43" t="n">
+        <v>59.65909090909091</v>
+      </c>
+      <c r="G31" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H31" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="43" t="n">
+        <v>89.65909090909091</v>
+      </c>
+      <c r="K31" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>51.00/88.00</t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>57.95454545454546</v>
+      </c>
+      <c r="F32" s="43" t="n">
+        <v>40.56818181818182</v>
+      </c>
+      <c r="G32" s="41" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H32" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="I32" s="43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J32" s="43" t="n">
+        <v>63.06818181818182</v>
+      </c>
+      <c r="K32" s="41" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>84.00/88.00</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="n">
+        <v>95.45454545454545</v>
+      </c>
+      <c r="F33" s="43" t="n">
+        <v>66.81818181818183</v>
+      </c>
+      <c r="G33" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H33" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="43" t="n">
+        <v>96.81818181818183</v>
+      </c>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="41" t="inlineStr">
+        <is>
+          <t>69.00/88.00</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>78.40909090909091</v>
+      </c>
+      <c r="F34" s="43" t="n">
+        <v>54.88636363636363</v>
+      </c>
+      <c r="G34" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H34" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="43" t="n">
+        <v>84.88636363636363</v>
+      </c>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>60.00/88.00</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="n">
+        <v>68.18181818181817</v>
+      </c>
+      <c r="F35" s="43" t="n">
+        <v>47.72727272727273</v>
+      </c>
+      <c r="G35" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H35" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="43" t="n">
+        <v>77.72727272727272</v>
+      </c>
+      <c r="K35" s="41" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>36.00/78.00</t>
-        </is>
-      </c>
-      <c r="E10" s="44" t="n">
-        <v>46.15384615384615</v>
-      </c>
-      <c r="F10" s="44" t="n">
-        <v>32.30769230769231</v>
-      </c>
-      <c r="G10" s="42" t="inlineStr">
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>48.00/88.00</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="F36" s="43" t="n">
+        <v>38.18181818181818</v>
+      </c>
+      <c r="G36" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H36" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I10" s="44" t="n">
+      <c r="I36" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J10" s="44" t="n">
-        <v>62.30769230769231</v>
-      </c>
-      <c r="K10" s="42" t="inlineStr">
+      <c r="J36" s="43" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="K36" s="41" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
-        <is>
-          <t>47.00/78.00</t>
-        </is>
-      </c>
-      <c r="E11" s="44" t="n">
-        <v>60.25641025641026</v>
-      </c>
-      <c r="F11" s="44" t="n">
-        <v>42.17948717948718</v>
-      </c>
-      <c r="G11" s="42" t="inlineStr">
+      <c r="D37" s="41" t="inlineStr">
+        <is>
+          <t>49.00/88.00</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>55.68181818181818</v>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>38.97727272727273</v>
+      </c>
+      <c r="G37" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H37" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="44" t="n">
+      <c r="I37" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J11" s="44" t="n">
-        <v>72.17948717948718</v>
-      </c>
-      <c r="K11" s="42" t="inlineStr">
+      <c r="J37" s="43" t="n">
+        <v>68.97727272727272</v>
+      </c>
+      <c r="K37" s="41" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr">
+        <is>
+          <t>48.00/88.00</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="F38" s="43" t="n">
+        <v>38.18181818181818</v>
+      </c>
+      <c r="G38" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H38" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="43" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="K38" s="41" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="41" t="inlineStr">
+        <is>
+          <t>75.00/88.00</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>85.22727272727273</v>
+      </c>
+      <c r="F39" s="43" t="n">
+        <v>59.65909090909091</v>
+      </c>
+      <c r="G39" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H39" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="43" t="n">
+        <v>89.65909090909091</v>
+      </c>
+      <c r="K39" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="41" t="inlineStr">
+        <is>
+          <t>56.00/88.00</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="F40" s="43" t="n">
+        <v>44.54545454545455</v>
+      </c>
+      <c r="G40" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H40" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="43" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="K40" s="41" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="42" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="42" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t>21.00/78.00</t>
-        </is>
-      </c>
-      <c r="E12" s="44" t="n">
-        <v>26.92307692307692</v>
-      </c>
-      <c r="F12" s="44" t="n">
-        <v>18.84615384615385</v>
-      </c>
-      <c r="G12" s="42" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H12" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="I12" s="44" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>41.34615384615385</v>
-      </c>
-      <c r="K12" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="42" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
+        <is>
+          <t>67.00/88.00</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>76.13636363636364</v>
+      </c>
+      <c r="F41" s="43" t="n">
+        <v>53.29545454545455</v>
+      </c>
+      <c r="G41" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="43" t="n">
+        <v>83.29545454545455</v>
+      </c>
+      <c r="K41" s="41" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
-        <is>
-          <t>0.00/78.00</t>
-        </is>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="42" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H13" s="44" t="n">
-        <v>25</v>
-      </c>
-      <c r="I13" s="44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K13" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="42" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="42" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
+        <is>
+          <t>61.00/88.00</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>69.31818181818183</v>
+      </c>
+      <c r="F42" s="43" t="n">
+        <v>48.52272727272727</v>
+      </c>
+      <c r="G42" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H42" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="43" t="n">
+        <v>78.52272727272728</v>
+      </c>
+      <c r="K42" s="41" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>45.00/78.00</t>
-        </is>
-      </c>
-      <c r="E14" s="44" t="n">
-        <v>57.69230769230769</v>
-      </c>
-      <c r="F14" s="44" t="n">
-        <v>40.38461538461538</v>
-      </c>
-      <c r="G14" s="42" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H14" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="I14" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>55.38461538461538</v>
-      </c>
-      <c r="K14" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>77.00/88.00</t>
+        </is>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F43" s="43" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="G43" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H43" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="43" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="K43" s="41" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
-        <is>
-          <t>28.00/78.00</t>
-        </is>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>35.8974358974359</v>
-      </c>
-      <c r="F15" s="44" t="n">
-        <v>25.12820512820513</v>
-      </c>
-      <c r="G15" s="42" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H15" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="I15" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="44" t="n">
-        <v>40.12820512820512</v>
-      </c>
-      <c r="K15" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="42" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>76.00/88.00</t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="F44" s="43" t="n">
+        <v>60.45454545454545</v>
+      </c>
+      <c r="G44" s="41" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H44" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="43" t="n">
+        <v>90.45454545454545</v>
+      </c>
+      <c r="K44" s="41" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr">
-        <is>
-          <t>46.00/78.00</t>
-        </is>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>58.97435897435898</v>
-      </c>
-      <c r="F16" s="44" t="n">
-        <v>41.28205128205128</v>
-      </c>
-      <c r="G16" s="42" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>42.00/88.00</t>
+        </is>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>47.72727272727273</v>
+      </c>
+      <c r="F45" s="43" t="n">
+        <v>33.40909090909091</v>
+      </c>
+      <c r="G45" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H16" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I16" s="44" t="n">
+      <c r="I45" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J16" s="44" t="n">
-        <v>71.28205128205128</v>
-      </c>
-      <c r="K16" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="42" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="J45" s="43" t="n">
+        <v>63.40909090909091</v>
+      </c>
+      <c r="K45" s="41" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
-        <is>
-          <t>61.00/78.00</t>
-        </is>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>78.2051282051282</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>54.74358974358974</v>
-      </c>
-      <c r="G17" s="42" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
+        <is>
+          <t>82.00/88.00</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>93.18181818181817</v>
+      </c>
+      <c r="F46" s="43" t="n">
+        <v>65.22727272727272</v>
+      </c>
+      <c r="G46" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H17" s="44" t="n">
+      <c r="H46" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I17" s="44" t="n">
+      <c r="I46" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="44" t="n">
-        <v>84.74358974358975</v>
-      </c>
-      <c r="K17" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="42" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="J46" s="43" t="n">
+        <v>95.22727272727272</v>
+      </c>
+      <c r="K46" s="41" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
-        <is>
-          <t>60.00/78.00</t>
-        </is>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>76.92307692307693</v>
-      </c>
-      <c r="F18" s="44" t="n">
-        <v>53.84615384615385</v>
-      </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>76.00/88.00</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="F47" s="43" t="n">
+        <v>60.45454545454545</v>
+      </c>
+      <c r="G47" s="41" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="H18" s="44" t="n">
+      <c r="H47" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="44" t="n">
+      <c r="I47" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="J18" s="44" t="n">
-        <v>83.84615384615384</v>
-      </c>
-      <c r="K18" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="42" t="inlineStr">
-        <is>
-          <t>44.00/78.00</t>
-        </is>
-      </c>
-      <c r="E19" s="44" t="n">
-        <v>56.41025641025641</v>
-      </c>
-      <c r="F19" s="44" t="n">
-        <v>39.48717948717949</v>
-      </c>
-      <c r="G19" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="44" t="n">
-        <v>69.48717948717949</v>
-      </c>
-      <c r="K19" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="42" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="42" t="inlineStr">
-        <is>
-          <t>48.00/78.00</t>
-        </is>
-      </c>
-      <c r="E20" s="44" t="n">
-        <v>61.53846153846154</v>
-      </c>
-      <c r="F20" s="44" t="n">
-        <v>43.07692307692308</v>
-      </c>
-      <c r="G20" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H20" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="44" t="n">
-        <v>73.07692307692308</v>
-      </c>
-      <c r="K20" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="42" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>33.00/78.00</t>
-        </is>
-      </c>
-      <c r="E21" s="44" t="n">
-        <v>42.30769230769231</v>
-      </c>
-      <c r="F21" s="44" t="n">
-        <v>29.61538461538462</v>
-      </c>
-      <c r="G21" s="42" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H21" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="I21" s="44" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J21" s="44" t="n">
-        <v>52.11538461538461</v>
-      </c>
-      <c r="K21" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="42" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="42" t="inlineStr">
-        <is>
-          <t>26.00/78.00</t>
-        </is>
-      </c>
-      <c r="E22" s="44" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="F22" s="44" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="G22" s="42" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H22" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="I22" s="44" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J22" s="44" t="n">
-        <v>45.83333333333333</v>
-      </c>
-      <c r="K22" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="42" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>53.00/78.00</t>
-        </is>
-      </c>
-      <c r="E23" s="44" t="n">
-        <v>67.94871794871796</v>
-      </c>
-      <c r="F23" s="44" t="n">
-        <v>47.56410256410257</v>
-      </c>
-      <c r="G23" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H23" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="44" t="n">
-        <v>77.56410256410257</v>
-      </c>
-      <c r="K23" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="42" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="42" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="42" t="inlineStr">
-        <is>
-          <t>63.00/78.00</t>
-        </is>
-      </c>
-      <c r="E24" s="44" t="n">
-        <v>80.76923076923077</v>
-      </c>
-      <c r="F24" s="44" t="n">
-        <v>56.53846153846154</v>
-      </c>
-      <c r="G24" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H24" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="44" t="n">
-        <v>86.53846153846155</v>
-      </c>
-      <c r="K24" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="42" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="42" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="42" t="inlineStr">
-        <is>
-          <t>0.00/78.00</t>
-        </is>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="42" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="42" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="42" t="inlineStr">
-        <is>
-          <t>65.00/78.00</t>
-        </is>
-      </c>
-      <c r="E26" s="44" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G26" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H26" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="44" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K26" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="42" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
-        <is>
-          <t>38.00/78.00</t>
-        </is>
-      </c>
-      <c r="E27" s="44" t="n">
-        <v>48.71794871794872</v>
-      </c>
-      <c r="F27" s="44" t="n">
-        <v>34.1025641025641</v>
-      </c>
-      <c r="G27" s="42" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H27" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="I27" s="44" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J27" s="44" t="n">
-        <v>56.6025641025641</v>
-      </c>
-      <c r="K27" s="42" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="42" t="inlineStr">
-        <is>
-          <t>61.00/78.00</t>
-        </is>
-      </c>
-      <c r="E28" s="44" t="n">
-        <v>78.2051282051282</v>
-      </c>
-      <c r="F28" s="44" t="n">
-        <v>54.74358974358974</v>
-      </c>
-      <c r="G28" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H28" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="44" t="n">
-        <v>84.74358974358975</v>
-      </c>
-      <c r="K28" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="42" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="42" t="inlineStr">
-        <is>
-          <t>65.00/78.00</t>
-        </is>
-      </c>
-      <c r="E29" s="44" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F29" s="44" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G29" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H29" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="44" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K29" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="42" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="42" t="inlineStr">
-        <is>
-          <t>54.00/78.00</t>
-        </is>
-      </c>
-      <c r="E30" s="44" t="n">
-        <v>69.23076923076923</v>
-      </c>
-      <c r="F30" s="44" t="n">
-        <v>48.46153846153846</v>
-      </c>
-      <c r="G30" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H30" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="44" t="n">
-        <v>78.46153846153845</v>
-      </c>
-      <c r="K30" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="42" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="42" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="42" t="inlineStr">
-        <is>
-          <t>65.00/78.00</t>
-        </is>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F31" s="44" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G31" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H31" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="44" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K31" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="42" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="42" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="42" t="inlineStr">
-        <is>
-          <t>46.00/78.00</t>
-        </is>
-      </c>
-      <c r="E32" s="44" t="n">
-        <v>58.97435897435898</v>
-      </c>
-      <c r="F32" s="44" t="n">
-        <v>41.28205128205128</v>
-      </c>
-      <c r="G32" s="42" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H32" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="I32" s="44" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J32" s="44" t="n">
-        <v>63.78205128205128</v>
-      </c>
-      <c r="K32" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="42" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="42" t="inlineStr">
-        <is>
-          <t>74.00/78.00</t>
-        </is>
-      </c>
-      <c r="E33" s="44" t="n">
-        <v>94.87179487179486</v>
-      </c>
-      <c r="F33" s="44" t="n">
-        <v>66.41025641025641</v>
-      </c>
-      <c r="G33" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H33" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="44" t="n">
-        <v>96.41025641025641</v>
-      </c>
-      <c r="K33" s="42" t="inlineStr">
+      <c r="J47" s="43" t="n">
+        <v>90.45454545454545</v>
+      </c>
+      <c r="K47" s="41" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="42" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="42" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="42" t="inlineStr">
-        <is>
-          <t>64.00/78.00</t>
-        </is>
-      </c>
-      <c r="E34" s="44" t="n">
-        <v>82.05128205128204</v>
-      </c>
-      <c r="F34" s="44" t="n">
-        <v>57.43589743589743</v>
-      </c>
-      <c r="G34" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H34" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="44" t="n">
-        <v>87.43589743589743</v>
-      </c>
-      <c r="K34" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="42" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="42" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="42" t="inlineStr">
-        <is>
-          <t>55.00/78.00</t>
-        </is>
-      </c>
-      <c r="E35" s="44" t="n">
-        <v>70.51282051282051</v>
-      </c>
-      <c r="F35" s="44" t="n">
-        <v>49.35897435897436</v>
-      </c>
-      <c r="G35" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H35" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="44" t="n">
-        <v>79.35897435897436</v>
-      </c>
-      <c r="K35" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="42" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="42" t="inlineStr">
-        <is>
-          <t>38.00/78.00</t>
-        </is>
-      </c>
-      <c r="E36" s="44" t="n">
-        <v>48.71794871794872</v>
-      </c>
-      <c r="F36" s="44" t="n">
-        <v>34.1025641025641</v>
-      </c>
-      <c r="G36" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H36" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="44" t="n">
-        <v>64.1025641025641</v>
-      </c>
-      <c r="K36" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="42" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="42" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="42" t="inlineStr">
-        <is>
-          <t>42.00/78.00</t>
-        </is>
-      </c>
-      <c r="E37" s="44" t="n">
-        <v>53.84615384615385</v>
-      </c>
-      <c r="F37" s="44" t="n">
-        <v>37.69230769230769</v>
-      </c>
-      <c r="G37" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H37" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="44" t="n">
-        <v>67.69230769230769</v>
-      </c>
-      <c r="K37" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="42" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
-        <is>
-          <t>41.00/78.00</t>
-        </is>
-      </c>
-      <c r="E38" s="44" t="n">
-        <v>52.56410256410257</v>
-      </c>
-      <c r="F38" s="44" t="n">
-        <v>36.7948717948718</v>
-      </c>
-      <c r="G38" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H38" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="44" t="n">
-        <v>66.7948717948718</v>
-      </c>
-      <c r="K38" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="42" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="42" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="42" t="inlineStr">
-        <is>
-          <t>65.00/78.00</t>
-        </is>
-      </c>
-      <c r="E39" s="44" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="F39" s="44" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G39" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H39" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="44" t="n">
-        <v>88.33333333333334</v>
-      </c>
-      <c r="K39" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="42" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="42" t="inlineStr">
-        <is>
-          <t>46.00/78.00</t>
-        </is>
-      </c>
-      <c r="E40" s="44" t="n">
-        <v>58.97435897435898</v>
-      </c>
-      <c r="F40" s="44" t="n">
-        <v>41.28205128205128</v>
-      </c>
-      <c r="G40" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H40" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="44" t="n">
-        <v>71.28205128205128</v>
-      </c>
-      <c r="K40" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="42" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>60.00/78.00</t>
-        </is>
-      </c>
-      <c r="E41" s="44" t="n">
-        <v>76.92307692307693</v>
-      </c>
-      <c r="F41" s="44" t="n">
-        <v>53.84615384615385</v>
-      </c>
-      <c r="G41" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H41" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="44" t="n">
-        <v>83.84615384615384</v>
-      </c>
-      <c r="K41" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="42" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="42" t="inlineStr">
-        <is>
-          <t>51.00/78.00</t>
-        </is>
-      </c>
-      <c r="E42" s="44" t="n">
-        <v>65.38461538461539</v>
-      </c>
-      <c r="F42" s="44" t="n">
-        <v>45.76923076923077</v>
-      </c>
-      <c r="G42" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H42" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="44" t="n">
-        <v>75.76923076923077</v>
-      </c>
-      <c r="K42" s="42" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="42" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="42" t="inlineStr">
-        <is>
-          <t>71.00/78.00</t>
-        </is>
-      </c>
-      <c r="E43" s="44" t="n">
-        <v>91.02564102564102</v>
-      </c>
-      <c r="F43" s="44" t="n">
-        <v>63.71794871794872</v>
-      </c>
-      <c r="G43" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H43" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="44" t="n">
-        <v>93.71794871794872</v>
-      </c>
-      <c r="K43" s="42" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="42" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="42" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>66.00/78.00</t>
-        </is>
-      </c>
-      <c r="E44" s="44" t="n">
-        <v>84.61538461538461</v>
-      </c>
-      <c r="F44" s="44" t="n">
-        <v>59.23076923076923</v>
-      </c>
-      <c r="G44" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H44" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="44" t="n">
-        <v>89.23076923076923</v>
-      </c>
-      <c r="K44" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="42" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="42" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>38.00/78.00</t>
-        </is>
-      </c>
-      <c r="E45" s="44" t="n">
-        <v>48.71794871794872</v>
-      </c>
-      <c r="F45" s="44" t="n">
-        <v>34.1025641025641</v>
-      </c>
-      <c r="G45" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H45" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="44" t="n">
-        <v>64.1025641025641</v>
-      </c>
-      <c r="K45" s="42" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="42" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="42" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="42" t="inlineStr">
-        <is>
-          <t>72.00/78.00</t>
-        </is>
-      </c>
-      <c r="E46" s="44" t="n">
-        <v>92.30769230769231</v>
-      </c>
-      <c r="F46" s="44" t="n">
-        <v>64.61538461538461</v>
-      </c>
-      <c r="G46" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H46" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="44" t="n">
-        <v>94.61538461538461</v>
-      </c>
-      <c r="K46" s="42" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="42" t="n">
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="45" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="46" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="n"/>
+      <c r="B54" s="45" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="42" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="43" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>66.00/78.00</t>
-        </is>
-      </c>
-      <c r="E47" s="44" t="n">
-        <v>84.61538461538461</v>
-      </c>
-      <c r="F47" s="44" t="n">
-        <v>59.23076923076923</v>
-      </c>
-      <c r="G47" s="42" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H47" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="44" t="n">
-        <v>89.23076923076923</v>
-      </c>
-      <c r="K47" s="42" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="45" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="46" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="45" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="47" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="45" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="46" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="45" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="47" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="45" t="n"/>
-      <c r="B54" s="46" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="45" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="46" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="45" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="48" t="n">
-        <v>65.63823857302118</v>
+      <c r="B56" s="47" t="n">
+        <v>67.40118577075098</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="45" t="inlineStr">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="48" t="n">
-        <v>23.79389133235755</v>
+      <c r="B57" s="47" t="n">
+        <v>22.89945411126535</v>
       </c>
     </row>
   </sheetData>

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43480" yWindow="-5060" windowWidth="25130" windowHeight="19430" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38300" yWindow="-7000" windowWidth="18380" windowHeight="20970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -120,12 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -133,6 +127,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,18 +255,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -276,22 +264,38 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -303,6 +307,9 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,19 +643,19 @@
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
     <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" style="37" min="12" max="20"/>
+    <col width="4.6484375" customWidth="1" style="39" min="12" max="20"/>
     <col width="4.796875" customWidth="1" min="21" max="26"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -665,7 +672,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -709,7 +716,7 @@
           <t>EX.3 Draw Sphere/Spheroid</t>
         </is>
       </c>
-      <c r="N6" s="32" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>Ex.4 EFG for Sphere</t>
         </is>
@@ -724,7 +731,7 @@
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="33" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t>MidTerm</t>
         </is>
@@ -734,7 +741,11 @@
           <t>Ex.7 Lambert Conformal Conic</t>
         </is>
       </c>
-      <c r="S6" s="10" t="n"/>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>Ex.8 Planar Map Projection</t>
+        </is>
+      </c>
       <c r="T6" s="10" t="n"/>
       <c r="U6" s="9" t="n"/>
       <c r="V6" s="9" t="n"/>
@@ -794,29 +805,31 @@
           <t>Email Office365</t>
         </is>
       </c>
-      <c r="L7" s="26" t="n">
+      <c r="L7" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="34" t="n">
+      <c r="M7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="R7" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S7" s="26" t="n"/>
-      <c r="T7" s="26" t="n"/>
+      <c r="R7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" s="22" t="n"/>
       <c r="U7" s="9" t="n"/>
       <c r="V7" s="9" t="n"/>
       <c r="W7" s="9" t="n"/>
@@ -881,14 +894,18 @@
         <v>8</v>
       </c>
       <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="35" t="n">
+      <c r="P8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="31" t="n">
         <v>10</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S8" s="10" t="n"/>
+      <c r="S8" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="T8" s="10" t="n"/>
       <c r="U8" s="9" t="n"/>
       <c r="V8" s="9" t="n"/>
@@ -957,13 +974,15 @@
         <v>10</v>
       </c>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="35" t="n">
+      <c r="Q9" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S9" s="10" t="n"/>
+      <c r="S9" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T9" s="10" t="n"/>
       <c r="U9" s="9" t="n"/>
       <c r="V9" s="9" t="n"/>
@@ -1034,11 +1053,13 @@
       <c r="P10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="35" t="n">
+      <c r="Q10" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R10" s="10" t="n"/>
-      <c r="S10" s="10" t="n"/>
+      <c r="S10" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T10" s="10" t="n"/>
       <c r="U10" s="9" t="n"/>
       <c r="V10" s="9" t="n"/>
@@ -1113,13 +1134,15 @@
       <c r="P11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="35" t="n">
+      <c r="Q11" s="31" t="n">
         <v>9</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S11" s="10" t="n"/>
+      <c r="S11" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="9" t="n"/>
       <c r="V11" s="9" t="n"/>
@@ -1188,13 +1211,15 @@
       <c r="P12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="35" t="n">
+      <c r="Q12" s="31" t="n">
         <v>9</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S12" s="10" t="n"/>
+      <c r="S12" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T12" s="10" t="n"/>
       <c r="U12" s="9" t="n"/>
       <c r="V12" s="9" t="n"/>
@@ -1259,13 +1284,15 @@
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="35" t="n">
+      <c r="Q13" s="31" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S13" s="10" t="n"/>
+      <c r="S13" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T13" s="10" t="n"/>
       <c r="U13" s="9" t="n"/>
       <c r="V13" s="9" t="n"/>
@@ -1336,13 +1363,15 @@
       <c r="P14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" s="35" t="n">
+      <c r="Q14" s="31" t="n">
         <v>2</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S14" s="10" t="n"/>
+      <c r="S14" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="T14" s="10" t="n"/>
       <c r="U14" s="9" t="n"/>
       <c r="V14" s="9" t="n"/>
@@ -1417,13 +1446,15 @@
       <c r="P15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" s="35" t="n">
+      <c r="Q15" s="31" t="n">
         <v>11</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="S15" s="10" t="n"/>
+      <c r="S15" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="T15" s="10" t="n"/>
       <c r="U15" s="9" t="n"/>
       <c r="V15" s="9" t="n"/>
@@ -1494,13 +1525,15 @@
         <v>5</v>
       </c>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="35" t="n">
+      <c r="Q16" s="31" t="n">
         <v>14</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="S16" s="10" t="n"/>
+      <c r="S16" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T16" s="10" t="n"/>
       <c r="U16" s="9" t="n"/>
       <c r="V16" s="9" t="n"/>
@@ -1575,13 +1608,15 @@
       <c r="P17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="35" t="n">
+      <c r="Q17" s="31" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="10" t="n"/>
+      <c r="S17" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T17" s="10" t="n"/>
       <c r="U17" s="9" t="n"/>
       <c r="V17" s="9" t="n"/>
@@ -1652,13 +1687,15 @@
       <c r="P18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="35" t="n">
+      <c r="Q18" s="31" t="n">
         <v>2</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S18" s="10" t="n"/>
+      <c r="S18" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T18" s="10" t="n"/>
       <c r="U18" s="9" t="n"/>
       <c r="V18" s="9" t="n"/>
@@ -1723,13 +1760,15 @@
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="35" t="n">
+      <c r="Q19" s="31" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S19" s="10" t="n"/>
+      <c r="S19" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="9" t="n"/>
       <c r="V19" s="9" t="n"/>
@@ -1804,7 +1843,7 @@
       <c r="P20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="35" t="n">
+      <c r="Q20" s="31" t="n">
         <v>5</v>
       </c>
       <c r="R20" s="10" t="n">
@@ -1881,11 +1920,13 @@
         <v>5</v>
       </c>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="35" t="n">
+      <c r="Q21" s="31" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
+      <c r="S21" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T21" s="10" t="n"/>
       <c r="U21" s="9" t="n"/>
       <c r="V21" s="9" t="n"/>
@@ -1960,13 +2001,15 @@
       <c r="P22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="35" t="n">
+      <c r="Q22" s="31" t="n">
         <v>2</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S22" s="10" t="n"/>
+      <c r="S22" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="T22" s="10" t="n"/>
       <c r="U22" s="9" t="n"/>
       <c r="V22" s="9" t="n"/>
@@ -2041,13 +2084,15 @@
       <c r="P23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="35" t="n">
+      <c r="Q23" s="31" t="n">
         <v>16</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S23" s="10" t="n"/>
+      <c r="S23" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T23" s="10" t="n"/>
       <c r="U23" s="9" t="n"/>
       <c r="V23" s="9" t="n"/>
@@ -2122,13 +2167,15 @@
       <c r="P24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="35" t="n">
+      <c r="Q24" s="31" t="n">
         <v>12</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S24" s="10" t="n"/>
+      <c r="S24" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T24" s="10" t="n"/>
       <c r="U24" s="9" t="n"/>
       <c r="V24" s="9" t="n"/>
@@ -2203,13 +2250,15 @@
       <c r="P25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="35" t="n">
+      <c r="Q25" s="31" t="n">
         <v>9</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S25" s="10" t="n"/>
+      <c r="S25" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="T25" s="10" t="n"/>
       <c r="U25" s="9" t="n"/>
       <c r="V25" s="9" t="n"/>
@@ -2284,13 +2333,15 @@
       <c r="P26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="35" t="n">
+      <c r="Q26" s="31" t="n">
         <v>1</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S26" s="10" t="n"/>
+      <c r="S26" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T26" s="10" t="n"/>
       <c r="U26" s="9" t="n"/>
       <c r="V26" s="9" t="n"/>
@@ -2363,13 +2414,15 @@
       <c r="P27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q27" s="35" t="n">
+      <c r="Q27" s="31" t="n">
         <v>1</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S27" s="10" t="n"/>
+      <c r="S27" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="9" t="n"/>
       <c r="V27" s="9" t="n"/>
@@ -2440,13 +2493,15 @@
         <v>4</v>
       </c>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="35" t="n">
+      <c r="Q28" s="31" t="n">
         <v>8</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S28" s="10" t="n"/>
+      <c r="S28" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="9" t="n"/>
       <c r="V28" s="9" t="n"/>
@@ -2521,13 +2576,15 @@
       <c r="P29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" s="35" t="n">
+      <c r="Q29" s="31" t="n">
         <v>9</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S29" s="10" t="n"/>
+      <c r="S29" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T29" s="10" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
@@ -2602,13 +2659,15 @@
       <c r="P30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="35" t="n">
+      <c r="Q30" s="31" t="n">
         <v>11</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S30" s="10" t="n"/>
+      <c r="S30" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T30" s="10" t="n"/>
       <c r="U30" s="9" t="n"/>
       <c r="V30" s="9" t="n"/>
@@ -2618,71 +2677,71 @@
       <c r="Z30" s="9" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>6710553051</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>นายธนทัต มุทธากาญจน์</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>Mr. Tanatud MUTTAKARN</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>tanatud.m@ku.th</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K31" s="34" t="inlineStr">
         <is>
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n"/>
+      <c r="L31" s="35" t="n"/>
+      <c r="M31" s="35" t="n"/>
+      <c r="N31" s="35" t="n"/>
+      <c r="O31" s="35" t="n"/>
+      <c r="P31" s="35" t="n"/>
       <c r="Q31" s="35" t="n"/>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="10" t="n"/>
-      <c r="T31" s="10" t="n"/>
-      <c r="U31" s="9" t="n"/>
-      <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
-      <c r="X31" s="9" t="n"/>
-      <c r="Y31" s="9" t="n"/>
-      <c r="Z31" s="9" t="n"/>
+      <c r="R31" s="35" t="n"/>
+      <c r="S31" s="35" t="n"/>
+      <c r="T31" s="35" t="n"/>
+      <c r="U31" s="36" t="n"/>
+      <c r="V31" s="36" t="n"/>
+      <c r="W31" s="36" t="n"/>
+      <c r="X31" s="36" t="n"/>
+      <c r="Y31" s="36" t="n"/>
+      <c r="Z31" s="36" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
@@ -2750,13 +2809,15 @@
       <c r="P32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="35" t="n">
+      <c r="Q32" s="31" t="n">
         <v>14</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S32" s="10" t="n"/>
+      <c r="S32" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="9" t="n"/>
       <c r="V32" s="9" t="n"/>
@@ -2829,13 +2890,15 @@
       <c r="P33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="35" t="n">
+      <c r="Q33" s="31" t="n">
         <v>3</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S33" s="10" t="n"/>
+      <c r="S33" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T33" s="10" t="n"/>
       <c r="U33" s="9" t="n"/>
       <c r="V33" s="9" t="n"/>
@@ -2845,52 +2908,52 @@
       <c r="Z33" s="9" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>6710553094</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>นายธรรมกร เจริญพร</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Mr. THAMMAKORN CHAROENPORN</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>thammakorn.c@ku.th</t>
         </is>
       </c>
-      <c r="K34" s="24" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>thammakorn.c@live.ku.th</t>
         </is>
@@ -2898,24 +2961,28 @@
       <c r="L34" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="M34" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="35" t="n">
+      <c r="M34" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="R34" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="S34" s="25" t="n"/>
-      <c r="T34" s="25" t="n"/>
+      <c r="R34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" s="10" t="n"/>
       <c r="U34" s="9" t="n"/>
       <c r="V34" s="9" t="n"/>
       <c r="W34" s="9" t="n"/>
@@ -2989,13 +3056,15 @@
       <c r="P35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="35" t="n">
+      <c r="Q35" s="31" t="n">
         <v>17</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="S35" s="10" t="n"/>
+      <c r="S35" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T35" s="10" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
@@ -3070,13 +3139,15 @@
       <c r="P36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="35" t="n">
+      <c r="Q36" s="31" t="n">
         <v>7</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S36" s="10" t="n"/>
+      <c r="S36" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T36" s="10" t="n"/>
       <c r="U36" s="9" t="n"/>
       <c r="V36" s="9" t="n"/>
@@ -3151,13 +3222,15 @@
       <c r="P37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" s="35" t="n">
+      <c r="Q37" s="31" t="n">
         <v>17</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S37" s="10" t="n"/>
+      <c r="S37" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
@@ -3230,13 +3303,15 @@
       <c r="P38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="35" t="n">
+      <c r="Q38" s="31" t="n">
         <v>16</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S38" s="10" t="n"/>
+      <c r="S38" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="9" t="n"/>
       <c r="V38" s="9" t="n"/>
@@ -3311,13 +3386,15 @@
       <c r="P39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="35" t="n">
+      <c r="Q39" s="31" t="n">
         <v>22</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S39" s="10" t="n"/>
+      <c r="S39" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T39" s="10" t="n"/>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
@@ -3392,13 +3469,15 @@
       <c r="P40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" s="35" t="n">
+      <c r="Q40" s="31" t="n">
         <v>15</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S40" s="10" t="n"/>
+      <c r="S40" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T40" s="10" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="9" t="n"/>
@@ -3473,13 +3552,15 @@
       <c r="P41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" s="35" t="n">
+      <c r="Q41" s="31" t="n">
         <v>6</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S41" s="10" t="n"/>
+      <c r="S41" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T41" s="10" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
@@ -3552,7 +3633,7 @@
         <v>10</v>
       </c>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="35" t="n">
+      <c r="Q42" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R42" s="10" t="n">
@@ -3633,13 +3714,15 @@
       <c r="P43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" s="35" t="n">
+      <c r="Q43" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="S43" s="10" t="n"/>
+      <c r="S43" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
@@ -3714,13 +3797,15 @@
       <c r="P44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" s="35" t="n">
+      <c r="Q44" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="S44" s="10" t="n"/>
+      <c r="S44" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="9" t="n"/>
@@ -3795,13 +3880,15 @@
       <c r="P45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" s="35" t="n">
+      <c r="Q45" s="31" t="n">
         <v>18</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S45" s="10" t="n"/>
+      <c r="S45" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T45" s="10" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
@@ -3876,13 +3963,15 @@
       <c r="P46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="35" t="n">
+      <c r="Q46" s="31" t="n">
         <v>3</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S46" s="10" t="n"/>
+      <c r="S46" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="9" t="n"/>
       <c r="V46" s="9" t="n"/>
@@ -3957,13 +4046,15 @@
       <c r="P47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="35" t="n">
+      <c r="Q47" s="31" t="n">
         <v>13</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="S47" s="10" t="n"/>
+      <c r="S47" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T47" s="10" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
@@ -4038,13 +4129,15 @@
       <c r="P48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" s="35" t="n">
+      <c r="Q48" s="31" t="n">
         <v>6</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S48" s="10" t="n"/>
+      <c r="S48" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T48" s="10" t="n"/>
       <c r="U48" s="9" t="n"/>
       <c r="V48" s="9" t="n"/>
@@ -4119,13 +4212,15 @@
       <c r="P49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" s="35" t="n">
+      <c r="Q49" s="31" t="n">
         <v>21</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="S49" s="10" t="n"/>
+      <c r="S49" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T49" s="10" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
@@ -4200,13 +4295,15 @@
       <c r="P50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" s="35" t="n">
+      <c r="Q50" s="31" t="n">
         <v>20</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S50" s="10" t="n"/>
+      <c r="S50" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T50" s="10" t="n"/>
       <c r="U50" s="9" t="n"/>
       <c r="V50" s="9" t="n"/>
@@ -4279,7 +4376,7 @@
         <v>10</v>
       </c>
       <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="35" t="n">
+      <c r="Q51" s="31" t="n">
         <v>4</v>
       </c>
       <c r="R51" s="10" t="n">
@@ -4360,13 +4457,15 @@
       <c r="P52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" s="35" t="n">
+      <c r="Q52" s="31" t="n">
         <v>22</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S52" s="10" t="n"/>
+      <c r="S52" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="9" t="n"/>
       <c r="V52" s="9" t="n"/>
@@ -4441,13 +4540,15 @@
       <c r="P53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="35" t="n">
+      <c r="Q53" s="31" t="n">
         <v>19</v>
       </c>
       <c r="R53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="S53" s="10" t="n"/>
+      <c r="S53" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="T53" s="10" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
@@ -4457,7 +4558,7 @@
       <c r="Z53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="Q54" s="27" t="inlineStr">
+      <c r="Q54" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4524,15 +4625,17 @@
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="41" t="n">
         <v>46258</v>
       </c>
-      <c r="H6" s="17" t="n"/>
+      <c r="H6" s="42" t="n">
+        <v>46265</v>
+      </c>
       <c r="I6" s="17" t="n"/>
       <c r="J6" s="17" t="n"/>
       <c r="K6" s="17" t="n"/>
@@ -4541,29 +4644,29 @@
       <c r="N6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29">
+      <c r="A7" s="25">
         <f>Exercise!B7</f>
         <v/>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="25">
         <f>Exercise!C7</f>
         <v/>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="25">
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="30" t="n"/>
-      <c r="I7" s="30" t="n"/>
-      <c r="J7" s="30" t="n"/>
-      <c r="K7" s="30" t="n"/>
-      <c r="L7" s="30" t="n"/>
-      <c r="M7" s="30" t="n"/>
-      <c r="N7" s="30" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="n"/>
+      <c r="N7" s="26" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -4586,7 +4689,9 @@
         <v>1</v>
       </c>
       <c r="G8" s="21" t="n"/>
-      <c r="H8" s="9" t="n"/>
+      <c r="H8" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="n"/>
@@ -4615,7 +4720,9 @@
       <c r="G9" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="9" t="n"/>
+      <c r="H9" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -4642,7 +4749,9 @@
       </c>
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="21" t="n"/>
-      <c r="H10" s="9" t="n"/>
+      <c r="H10" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="n"/>
@@ -4675,7 +4784,9 @@
       <c r="G11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
@@ -4708,7 +4819,9 @@
       <c r="G12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="n"/>
+      <c r="H12" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="9" t="n"/>
@@ -4737,7 +4850,9 @@
       <c r="G13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="9" t="n"/>
+      <c r="H13" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
@@ -4801,7 +4916,9 @@
       <c r="G15" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="9" t="n"/>
+      <c r="H15" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
@@ -4834,7 +4951,9 @@
       <c r="G16" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="9" t="n"/>
+      <c r="H16" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="9" t="n"/>
@@ -4867,7 +4986,9 @@
       <c r="G17" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="9" t="n"/>
+      <c r="H17" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
@@ -4898,7 +5019,9 @@
       <c r="G18" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="9" t="n"/>
+      <c r="H18" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="n"/>
@@ -4920,12 +5043,16 @@
         <v/>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="n"/>
+      <c r="H19" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
@@ -4954,7 +5081,9 @@
       <c r="G20" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="9" t="n"/>
+      <c r="H20" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="9" t="n"/>
@@ -5016,7 +5145,9 @@
       <c r="G22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="9" t="n"/>
+      <c r="H22" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="9" t="n"/>
@@ -5049,7 +5180,9 @@
       <c r="G23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="9" t="n"/>
+      <c r="H23" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
@@ -5082,7 +5215,9 @@
       <c r="G24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="9" t="n"/>
+      <c r="H24" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="n"/>
@@ -5115,7 +5250,9 @@
       <c r="G25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="9" t="n"/>
+      <c r="H25" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -5148,7 +5285,9 @@
       <c r="G26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="9" t="n"/>
+      <c r="H26" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="9" t="n"/>
@@ -5179,7 +5318,9 @@
       <c r="G27" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="9" t="n"/>
+      <c r="H27" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
@@ -5243,7 +5384,9 @@
       <c r="G29" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="9" t="n"/>
+      <c r="H29" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" s="9" t="n"/>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
@@ -5276,7 +5419,9 @@
       <c r="G30" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="9" t="n"/>
+      <c r="H30" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="9" t="n"/>
@@ -5334,7 +5479,9 @@
       <c r="G32" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n"/>
+      <c r="H32" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I32" s="9" t="n"/>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="9" t="n"/>
@@ -5365,7 +5512,9 @@
       <c r="G33" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="9" t="n"/>
+      <c r="H33" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="9" t="n"/>
@@ -5398,7 +5547,9 @@
       <c r="G34" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="9" t="n"/>
+      <c r="H34" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="9" t="n"/>
@@ -5431,7 +5582,9 @@
       <c r="G35" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="9" t="n"/>
+      <c r="H35" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="9" t="n"/>
@@ -5497,7 +5650,9 @@
       <c r="G37" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="9" t="n"/>
+      <c r="H37" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
@@ -5528,7 +5683,9 @@
       <c r="G38" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="9" t="n"/>
+      <c r="H38" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="9" t="n"/>
@@ -5561,7 +5718,9 @@
       <c r="G39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="9" t="n"/>
+      <c r="H39" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I39" s="9" t="n"/>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="9" t="n"/>
@@ -5594,7 +5753,9 @@
       <c r="G40" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="9" t="n"/>
+      <c r="H40" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="9" t="n"/>
@@ -5627,7 +5788,9 @@
       <c r="G41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="9" t="n"/>
+      <c r="H41" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="9" t="n"/>
@@ -5660,7 +5823,9 @@
       <c r="G42" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="9" t="n"/>
+      <c r="H42" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
@@ -5693,7 +5858,9 @@
       <c r="G43" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="9" t="n"/>
+      <c r="H43" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I43" s="9" t="n"/>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
@@ -5726,7 +5893,9 @@
       <c r="G44" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="9" t="n"/>
+      <c r="H44" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
@@ -5759,7 +5928,9 @@
       <c r="G45" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="9" t="n"/>
+      <c r="H45" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I45" s="9" t="n"/>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
@@ -5792,7 +5963,9 @@
       <c r="G46" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="9" t="n"/>
+      <c r="H46" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I46" s="9" t="n"/>
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="9" t="n"/>
@@ -5825,7 +5998,9 @@
       <c r="G47" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="9" t="n"/>
+      <c r="H47" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I47" s="9" t="n"/>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="9" t="n"/>
@@ -5858,7 +6033,9 @@
       <c r="G48" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="9" t="n"/>
+      <c r="H48" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="9" t="n"/>
@@ -5891,7 +6068,9 @@
       <c r="G49" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="9" t="n"/>
+      <c r="H49" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I49" s="9" t="n"/>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="9" t="n"/>
@@ -5924,7 +6103,9 @@
       <c r="G50" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="9" t="n"/>
+      <c r="H50" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I50" s="9" t="n"/>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="9" t="n"/>
@@ -5957,7 +6138,9 @@
       <c r="G51" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="9" t="n"/>
+      <c r="H51" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I51" s="9" t="n"/>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="9" t="n"/>
@@ -5990,7 +6173,9 @@
       <c r="G52" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="9" t="n"/>
+      <c r="H52" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="9" t="n"/>
@@ -6023,7 +6208,9 @@
       <c r="G53" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="9" t="n"/>
+      <c r="H53" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I53" s="9" t="n"/>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
@@ -6033,6 +6220,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
@@ -6059,2204 +6247,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="40" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="40" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="40" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="40" t="inlineStr">
+      <c r="F1" s="43" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="40" t="inlineStr">
+      <c r="G1" s="43" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="40" t="inlineStr">
+      <c r="H1" s="43" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="40" t="inlineStr">
+      <c r="I1" s="43" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="40" t="inlineStr">
+      <c r="J1" s="43" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="40" t="inlineStr">
+      <c r="K1" s="43" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="41" t="inlineStr">
+      <c r="A2" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
-        <is>
-          <t>23.00/88.00</t>
-        </is>
-      </c>
-      <c r="E2" s="43" t="n">
-        <v>26.13636363636364</v>
-      </c>
-      <c r="F2" s="43" t="n">
-        <v>18.29545454545454</v>
-      </c>
-      <c r="G2" s="41" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H2" s="43" t="n">
+      <c r="D2" s="44" t="inlineStr">
+        <is>
+          <t>31.00/98.00</t>
+        </is>
+      </c>
+      <c r="E2" s="46" t="n">
+        <v>31.63265306122449</v>
+      </c>
+      <c r="F2" s="46" t="n">
+        <v>22.14285714285715</v>
+      </c>
+      <c r="G2" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H2" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" s="46" t="n">
+        <v>40.14285714285715</v>
+      </c>
+      <c r="K2" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="inlineStr">
+        <is>
+          <t>6610553165</t>
+        </is>
+      </c>
+      <c r="C3" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>37.00/98.00</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="n">
+        <v>37.75510204081633</v>
+      </c>
+      <c r="F3" s="46" t="n">
+        <v>26.42857142857143</v>
+      </c>
+      <c r="G3" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H3" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J3" s="46" t="n">
+        <v>44.42857142857143</v>
+      </c>
+      <c r="K3" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>6610553173</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>30.00/98.00</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="n">
+        <v>30.61224489795918</v>
+      </c>
+      <c r="F4" s="46" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="G4" s="44" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="I4" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" s="46" t="n">
+        <v>33.42857142857143</v>
+      </c>
+      <c r="K4" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>6610553181</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>64.00/98.00</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="n">
+        <v>65.30612244897959</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>45.71428571428571</v>
+      </c>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="46" t="n">
+        <v>75.71428571428571</v>
+      </c>
+      <c r="K5" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>46.00/98.00</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>46.93877551020408</v>
+      </c>
+      <c r="F6" s="46" t="n">
+        <v>32.85714285714286</v>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>62.85714285714286</v>
+      </c>
+      <c r="K6" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>15.00/98.00</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>15.30612244897959</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>10.71428571428572</v>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J7" s="46" t="n">
+        <v>28.71428571428572</v>
+      </c>
+      <c r="K7" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>32.00/98.00</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>32.6530612244898</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>22.85714285714285</v>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J8" s="46" t="n">
+        <v>40.85714285714285</v>
+      </c>
+      <c r="K8" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>62.00/98.00</t>
+        </is>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>63.26530612244898</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>44.28571428571429</v>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="46" t="n">
+        <v>74.28571428571429</v>
+      </c>
+      <c r="K9" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>49.00/98.00</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="I2" s="43" t="n">
+      <c r="F10" s="46" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>65</v>
+      </c>
+      <c r="K10" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>67.00/98.00</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>68.36734693877551</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>47.85714285714285</v>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H11" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>77.85714285714286</v>
+      </c>
+      <c r="K11" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>41.00/98.00</t>
+        </is>
+      </c>
+      <c r="E12" s="46" t="n">
+        <v>41.83673469387755</v>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>29.28571428571429</v>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>53.28571428571429</v>
+      </c>
+      <c r="K12" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>20.00/98.00</t>
+        </is>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>20.40816326530612</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>32.28571428571428</v>
+      </c>
+      <c r="K13" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>50.00/98.00</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>51.02040816326531</v>
+      </c>
+      <c r="F14" s="46" t="n">
+        <v>35.71428571428572</v>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" s="46" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="K14" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>38.00/98.00</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="n">
+        <v>38.77551020408163</v>
+      </c>
+      <c r="F15" s="46" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="46" t="n">
+        <v>39.14285714285714</v>
+      </c>
+      <c r="K15" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="43" t="n">
-        <v>33.29545454545455</v>
-      </c>
-      <c r="K2" s="41" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>65.00/98.00</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="n">
+        <v>66.32653061224489</v>
+      </c>
+      <c r="F16" s="46" t="n">
+        <v>46.42857142857142</v>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H16" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="46" t="n">
+        <v>76.42857142857142</v>
+      </c>
+      <c r="K16" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>81.00/98.00</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>82.6530612244898</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>57.85714285714286</v>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H17" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="46" t="n">
+        <v>87.85714285714286</v>
+      </c>
+      <c r="K17" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>80.00/98.00</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>81.63265306122449</v>
+      </c>
+      <c r="F18" s="46" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>87.14285714285714</v>
+      </c>
+      <c r="K18" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>59.00/98.00</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>60.20408163265306</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>42.14285714285715</v>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="46" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="K19" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>68.00/98.00</t>
+        </is>
+      </c>
+      <c r="E20" s="46" t="n">
+        <v>69.38775510204081</v>
+      </c>
+      <c r="F20" s="46" t="n">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H20" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="K20" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>53.00/98.00</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="n">
+        <v>54.08163265306123</v>
+      </c>
+      <c r="F21" s="46" t="n">
+        <v>37.85714285714286</v>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H21" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I21" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" s="46" t="n">
+        <v>61.85714285714286</v>
+      </c>
+      <c r="K21" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>46.00/98.00</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>46.93877551020408</v>
+      </c>
+      <c r="F22" s="46" t="n">
+        <v>32.85714285714286</v>
+      </c>
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H22" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" s="46" t="n">
+        <v>50.85714285714286</v>
+      </c>
+      <c r="K22" s="44" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="41" t="inlineStr">
-        <is>
-          <t>6610553165</t>
-        </is>
-      </c>
-      <c r="C3" s="42" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="45" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
-        <is>
-          <t>27.00/88.00</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="n">
-        <v>30.68181818181818</v>
-      </c>
-      <c r="F3" s="43" t="n">
-        <v>21.47727272727273</v>
-      </c>
-      <c r="G3" s="41" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H3" s="43" t="n">
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>73.00/98.00</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>74.48979591836735</v>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>52.14285714285715</v>
+      </c>
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H23" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="46" t="n">
+        <v>82.14285714285714</v>
+      </c>
+      <c r="K23" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>83.00/98.00</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="n">
+        <v>84.69387755102041</v>
+      </c>
+      <c r="F24" s="46" t="n">
+        <v>59.28571428571429</v>
+      </c>
+      <c r="G24" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H24" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="46" t="n">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="K24" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>0.00/98.00</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="44" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>80.00/98.00</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>81.63265306122449</v>
+      </c>
+      <c r="F26" s="46" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H26" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>87.14285714285714</v>
+      </c>
+      <c r="K26" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>58.00/98.00</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="n">
+        <v>59.18367346938776</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>41.42857142857143</v>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H27" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I27" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J27" s="46" t="n">
+        <v>65.42857142857143</v>
+      </c>
+      <c r="K27" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>95.00/98.00</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="n">
+        <v>96.93877551020408</v>
+      </c>
+      <c r="F28" s="46" t="n">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="G28" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H28" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="46" t="n">
+        <v>97.85714285714286</v>
+      </c>
+      <c r="K28" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>82.00/98.00</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="n">
+        <v>83.67346938775511</v>
+      </c>
+      <c r="F29" s="46" t="n">
+        <v>58.57142857142858</v>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H29" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="46" t="n">
+        <v>88.57142857142858</v>
+      </c>
+      <c r="K29" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>74.00/98.00</t>
+        </is>
+      </c>
+      <c r="E30" s="46" t="n">
+        <v>75.51020408163265</v>
+      </c>
+      <c r="F30" s="46" t="n">
+        <v>52.85714285714285</v>
+      </c>
+      <c r="G30" s="44" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H30" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" s="46" t="n">
+        <v>76.85714285714286</v>
+      </c>
+      <c r="K30" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>85.00/98.00</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="n">
+        <v>86.73469387755102</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>60.71428571428571</v>
+      </c>
+      <c r="G31" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H31" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="46" t="n">
+        <v>90.71428571428571</v>
+      </c>
+      <c r="K31" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>61.00/98.00</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="n">
+        <v>62.24489795918367</v>
+      </c>
+      <c r="F32" s="46" t="n">
+        <v>43.57142857142858</v>
+      </c>
+      <c r="G32" s="44" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="I32" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J32" s="46" t="n">
+        <v>67.57142857142858</v>
+      </c>
+      <c r="K32" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="inlineStr">
+        <is>
+          <t>94.00/98.00</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="n">
+        <v>95.91836734693877</v>
+      </c>
+      <c r="F33" s="46" t="n">
+        <v>67.14285714285714</v>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H33" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="46" t="n">
+        <v>97.14285714285714</v>
+      </c>
+      <c r="K33" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>79.00/98.00</t>
+        </is>
+      </c>
+      <c r="E34" s="46" t="n">
+        <v>80.61224489795919</v>
+      </c>
+      <c r="F34" s="46" t="n">
+        <v>56.42857142857143</v>
+      </c>
+      <c r="G34" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H34" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="46" t="n">
+        <v>86.42857142857143</v>
+      </c>
+      <c r="K34" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>70.00/98.00</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="F35" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="I3" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="43" t="n">
-        <v>36.47727272727273</v>
-      </c>
-      <c r="K3" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="41" t="inlineStr">
-        <is>
-          <t>6610553173</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H35" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="K35" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
-        <is>
-          <t>20.00/88.00</t>
-        </is>
-      </c>
-      <c r="E4" s="43" t="n">
-        <v>22.72727272727273</v>
-      </c>
-      <c r="F4" s="43" t="n">
-        <v>15.90909090909091</v>
-      </c>
-      <c r="G4" s="41" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H4" s="43" t="n">
-        <v>25</v>
-      </c>
-      <c r="I4" s="43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J4" s="43" t="n">
-        <v>23.40909090909091</v>
-      </c>
-      <c r="K4" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>6610553181</t>
-        </is>
-      </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>48.00/98.00</t>
+        </is>
+      </c>
+      <c r="E36" s="46" t="n">
+        <v>48.97959183673469</v>
+      </c>
+      <c r="F36" s="46" t="n">
+        <v>34.28571428571428</v>
+      </c>
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H36" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="46" t="n">
+        <v>64.28571428571428</v>
+      </c>
+      <c r="K36" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="45" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>54.00/88.00</t>
-        </is>
-      </c>
-      <c r="E5" s="43" t="n">
-        <v>61.36363636363637</v>
-      </c>
-      <c r="F5" s="43" t="n">
-        <v>42.95454545454545</v>
-      </c>
-      <c r="G5" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H5" s="43" t="n">
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>54.00/98.00</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="n">
+        <v>55.10204081632652</v>
+      </c>
+      <c r="F37" s="46" t="n">
+        <v>38.57142857142857</v>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H37" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="43" t="n">
+      <c r="I37" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="43" t="n">
-        <v>72.95454545454545</v>
-      </c>
-      <c r="K5" s="41" t="inlineStr">
+      <c r="J37" s="46" t="n">
+        <v>68.57142857142857</v>
+      </c>
+      <c r="K37" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>58.00/98.00</t>
+        </is>
+      </c>
+      <c r="E38" s="46" t="n">
+        <v>59.18367346938776</v>
+      </c>
+      <c r="F38" s="46" t="n">
+        <v>41.42857142857143</v>
+      </c>
+      <c r="G38" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H38" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="46" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="K38" s="44" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="41" t="n">
+    <row r="39">
+      <c r="A39" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>85.00/98.00</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="n">
+        <v>86.73469387755102</v>
+      </c>
+      <c r="F39" s="46" t="n">
+        <v>60.71428571428571</v>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H39" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="46" t="n">
+        <v>90.71428571428571</v>
+      </c>
+      <c r="K39" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>66.00/98.00</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="n">
+        <v>67.3469387755102</v>
+      </c>
+      <c r="F40" s="46" t="n">
+        <v>47.14285714285714</v>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H40" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="46" t="n">
+        <v>77.14285714285714</v>
+      </c>
+      <c r="K40" s="44" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>77.00/98.00</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="n">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="F41" s="46" t="n">
+        <v>55</v>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H41" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="46" t="n">
+        <v>85</v>
+      </c>
+      <c r="K41" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>71.00/98.00</t>
+        </is>
+      </c>
+      <c r="E42" s="46" t="n">
+        <v>72.44897959183673</v>
+      </c>
+      <c r="F42" s="46" t="n">
+        <v>50.71428571428572</v>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H42" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="46" t="n">
+        <v>80.71428571428572</v>
+      </c>
+      <c r="K42" s="44" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>87.00/98.00</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="n">
+        <v>88.77551020408163</v>
+      </c>
+      <c r="F43" s="46" t="n">
+        <v>62.14285714285714</v>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H43" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="46" t="n">
+        <v>92.14285714285714</v>
+      </c>
+      <c r="K43" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>86.00/98.00</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="n">
+        <v>87.75510204081633</v>
+      </c>
+      <c r="F44" s="46" t="n">
+        <v>61.42857142857142</v>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H44" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="46" t="n">
+        <v>91.42857142857142</v>
+      </c>
+      <c r="K44" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>42.00/98.00</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="F45" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H45" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="K45" s="44" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>92.00/98.00</t>
+        </is>
+      </c>
+      <c r="E46" s="46" t="n">
+        <v>93.87755102040816</v>
+      </c>
+      <c r="F46" s="46" t="n">
+        <v>65.71428571428572</v>
+      </c>
+      <c r="G46" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H46" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="46" t="n">
+        <v>95.71428571428572</v>
+      </c>
+      <c r="K46" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="45" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>86.00/98.00</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="n">
+        <v>87.75510204081633</v>
+      </c>
+      <c r="F47" s="46" t="n">
+        <v>61.42857142857142</v>
+      </c>
+      <c r="G47" s="44" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H47" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="46" t="n">
+        <v>91.42857142857142</v>
+      </c>
+      <c r="K47" s="44" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="47" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="48" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="47" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="49" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="47" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="41" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D6" s="41" t="inlineStr">
-        <is>
-          <t>36.00/88.00</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="n">
-        <v>40.90909090909091</v>
-      </c>
-      <c r="F6" s="43" t="n">
-        <v>28.63636363636364</v>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H6" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="43" t="n">
-        <v>58.63636363636364</v>
-      </c>
-      <c r="K6" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>5.00/88.00</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>5.681818181818182</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>3.977272727272727</v>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>18.97727272727273</v>
-      </c>
-      <c r="K7" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>29.00/88.00</t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>32.95454545454545</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>23.06818181818182</v>
-      </c>
-      <c r="G8" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H8" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I8" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J8" s="43" t="n">
-        <v>45.56818181818181</v>
-      </c>
-      <c r="K8" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="41" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="41" t="inlineStr">
-        <is>
-          <t>54.00/88.00</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>61.36363636363637</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>42.95454545454545</v>
-      </c>
-      <c r="G9" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H9" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <v>72.95454545454545</v>
-      </c>
-      <c r="K9" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="41" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t>39.00/88.00</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>44.31818181818182</v>
-      </c>
-      <c r="F10" s="43" t="n">
-        <v>31.02272727272727</v>
-      </c>
-      <c r="G10" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H10" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="43" t="n">
-        <v>61.02272727272727</v>
-      </c>
-      <c r="K10" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="41" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>57.00/88.00</t>
-        </is>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>64.77272727272727</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>45.34090909090909</v>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H11" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>75.34090909090909</v>
-      </c>
-      <c r="K11" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="41" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="41" t="inlineStr">
-        <is>
-          <t>31.00/88.00</t>
-        </is>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>35.22727272727273</v>
-      </c>
-      <c r="F12" s="43" t="n">
-        <v>24.65909090909091</v>
-      </c>
-      <c r="G12" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H12" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I12" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J12" s="43" t="n">
-        <v>47.15909090909091</v>
-      </c>
-      <c r="K12" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="41" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="41" t="inlineStr">
-        <is>
-          <t>10.00/88.00</t>
-        </is>
-      </c>
-      <c r="E13" s="43" t="n">
-        <v>11.36363636363636</v>
-      </c>
-      <c r="F13" s="43" t="n">
-        <v>7.954545454545454</v>
-      </c>
-      <c r="G13" s="41" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H13" s="43" t="n">
-        <v>25</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>15.45454545454545</v>
-      </c>
-      <c r="K13" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="41" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
-        <is>
-          <t>50.00/88.00</t>
-        </is>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>56.81818181818182</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>39.77272727272727</v>
-      </c>
-      <c r="G14" s="41" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H14" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="I14" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="43" t="n">
-        <v>54.77272727272727</v>
-      </c>
-      <c r="K14" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="41" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="41" t="inlineStr">
-        <is>
-          <t>28.00/88.00</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>31.81818181818182</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>22.27272727272727</v>
-      </c>
-      <c r="G15" s="41" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="H15" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="I15" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="43" t="n">
-        <v>37.27272727272727</v>
-      </c>
-      <c r="K15" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="41" t="inlineStr">
-        <is>
-          <t>56.00/88.00</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="F16" s="43" t="n">
-        <v>44.54545454545455</v>
-      </c>
-      <c r="G16" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H16" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="43" t="n">
-        <v>74.54545454545455</v>
-      </c>
-      <c r="K16" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="41" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="41" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="41" t="inlineStr">
-        <is>
-          <t>71.00/88.00</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="n">
-        <v>80.68181818181817</v>
-      </c>
-      <c r="F17" s="43" t="n">
-        <v>56.47727272727273</v>
-      </c>
-      <c r="G17" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H17" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="43" t="n">
-        <v>86.47727272727272</v>
-      </c>
-      <c r="K17" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="41" t="inlineStr">
-        <is>
-          <t>70.00/88.00</t>
-        </is>
-      </c>
-      <c r="E18" s="43" t="n">
-        <v>79.54545454545455</v>
-      </c>
-      <c r="F18" s="43" t="n">
-        <v>55.68181818181818</v>
-      </c>
-      <c r="G18" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H18" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="43" t="n">
-        <v>85.68181818181819</v>
-      </c>
-      <c r="K18" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="41" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t>54.00/88.00</t>
-        </is>
-      </c>
-      <c r="E19" s="43" t="n">
-        <v>61.36363636363637</v>
-      </c>
-      <c r="F19" s="43" t="n">
-        <v>42.95454545454545</v>
-      </c>
-      <c r="G19" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="43" t="n">
-        <v>72.95454545454545</v>
-      </c>
-      <c r="K19" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="41" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="41" t="inlineStr">
-        <is>
-          <t>58.00/88.00</t>
-        </is>
-      </c>
-      <c r="E20" s="43" t="n">
-        <v>65.90909090909091</v>
-      </c>
-      <c r="F20" s="43" t="n">
-        <v>46.13636363636363</v>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H20" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="43" t="n">
-        <v>76.13636363636363</v>
-      </c>
-      <c r="K20" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="41" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="41" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="inlineStr">
-        <is>
-          <t>43.00/88.00</t>
-        </is>
-      </c>
-      <c r="E21" s="43" t="n">
-        <v>48.86363636363637</v>
-      </c>
-      <c r="F21" s="43" t="n">
-        <v>34.20454545454545</v>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H21" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I21" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J21" s="43" t="n">
-        <v>56.70454545454545</v>
-      </c>
-      <c r="K21" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="41" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="41" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="41" t="inlineStr">
-        <is>
-          <t>36.00/88.00</t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="n">
-        <v>40.90909090909091</v>
-      </c>
-      <c r="F22" s="43" t="n">
-        <v>28.63636363636364</v>
-      </c>
-      <c r="G22" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H22" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I22" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J22" s="43" t="n">
-        <v>51.13636363636364</v>
-      </c>
-      <c r="K22" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="41" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="41" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>63.00/88.00</t>
-        </is>
-      </c>
-      <c r="E23" s="43" t="n">
-        <v>71.59090909090909</v>
-      </c>
-      <c r="F23" s="43" t="n">
-        <v>50.11363636363637</v>
-      </c>
-      <c r="G23" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H23" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="43" t="n">
-        <v>80.11363636363637</v>
-      </c>
-      <c r="K23" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="41" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="41" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="41" t="inlineStr">
-        <is>
-          <t>73.00/88.00</t>
-        </is>
-      </c>
-      <c r="E24" s="43" t="n">
-        <v>82.95454545454545</v>
-      </c>
-      <c r="F24" s="43" t="n">
-        <v>58.06818181818182</v>
-      </c>
-      <c r="G24" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H24" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="43" t="n">
-        <v>88.06818181818181</v>
-      </c>
-      <c r="K24" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="41" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="41" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="inlineStr">
-        <is>
-          <t>0.00/88.00</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="41" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="41" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="41" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="41" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="41" t="inlineStr">
-        <is>
-          <t>70.00/88.00</t>
-        </is>
-      </c>
-      <c r="E26" s="43" t="n">
-        <v>79.54545454545455</v>
-      </c>
-      <c r="F26" s="43" t="n">
-        <v>55.68181818181818</v>
-      </c>
-      <c r="G26" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H26" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="43" t="n">
-        <v>85.68181818181819</v>
-      </c>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="41" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="41" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>48.00/88.00</t>
-        </is>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>54.54545454545454</v>
-      </c>
-      <c r="F27" s="43" t="n">
-        <v>38.18181818181818</v>
-      </c>
-      <c r="G27" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H27" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I27" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J27" s="43" t="n">
-        <v>60.68181818181818</v>
-      </c>
-      <c r="K27" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="41" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>71.00/88.00</t>
-        </is>
-      </c>
-      <c r="E28" s="43" t="n">
-        <v>80.68181818181817</v>
-      </c>
-      <c r="F28" s="43" t="n">
-        <v>56.47727272727273</v>
-      </c>
-      <c r="G28" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H28" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="43" t="n">
-        <v>86.47727272727272</v>
-      </c>
-      <c r="K28" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="41" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="41" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="41" t="inlineStr">
-        <is>
-          <t>72.00/88.00</t>
-        </is>
-      </c>
-      <c r="E29" s="43" t="n">
-        <v>81.81818181818183</v>
-      </c>
-      <c r="F29" s="43" t="n">
-        <v>57.27272727272727</v>
-      </c>
-      <c r="G29" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H29" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="43" t="n">
-        <v>87.27272727272728</v>
-      </c>
-      <c r="K29" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="41" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="41" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="41" t="inlineStr">
-        <is>
-          <t>64.00/88.00</t>
-        </is>
-      </c>
-      <c r="E30" s="43" t="n">
-        <v>72.72727272727273</v>
-      </c>
-      <c r="F30" s="43" t="n">
-        <v>50.90909090909091</v>
-      </c>
-      <c r="G30" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H30" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="43" t="n">
-        <v>80.90909090909091</v>
-      </c>
-      <c r="K30" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="41" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="41" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="inlineStr">
-        <is>
-          <t>75.00/88.00</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="n">
-        <v>85.22727272727273</v>
-      </c>
-      <c r="F31" s="43" t="n">
-        <v>59.65909090909091</v>
-      </c>
-      <c r="G31" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H31" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="43" t="n">
-        <v>89.65909090909091</v>
-      </c>
-      <c r="K31" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="41" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="41" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="41" t="inlineStr">
-        <is>
-          <t>51.00/88.00</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="n">
-        <v>57.95454545454546</v>
-      </c>
-      <c r="F32" s="43" t="n">
-        <v>40.56818181818182</v>
-      </c>
-      <c r="G32" s="41" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H32" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I32" s="43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J32" s="43" t="n">
-        <v>63.06818181818182</v>
-      </c>
-      <c r="K32" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="41" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="41" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="41" t="inlineStr">
-        <is>
-          <t>84.00/88.00</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>95.45454545454545</v>
-      </c>
-      <c r="F33" s="43" t="n">
-        <v>66.81818181818183</v>
-      </c>
-      <c r="G33" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H33" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="43" t="n">
-        <v>96.81818181818183</v>
-      </c>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="41" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="41" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="41" t="inlineStr">
-        <is>
-          <t>69.00/88.00</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="n">
-        <v>78.40909090909091</v>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>54.88636363636363</v>
-      </c>
-      <c r="G34" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H34" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="43" t="n">
-        <v>84.88636363636363</v>
-      </c>
-      <c r="K34" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="41" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="41" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="41" t="inlineStr">
-        <is>
-          <t>60.00/88.00</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>68.18181818181817</v>
-      </c>
-      <c r="F35" s="43" t="n">
-        <v>47.72727272727273</v>
-      </c>
-      <c r="G35" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H35" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="43" t="n">
-        <v>77.72727272727272</v>
-      </c>
-      <c r="K35" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="41" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="41" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="41" t="inlineStr">
-        <is>
-          <t>48.00/88.00</t>
-        </is>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>54.54545454545454</v>
-      </c>
-      <c r="F36" s="43" t="n">
-        <v>38.18181818181818</v>
-      </c>
-      <c r="G36" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H36" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="43" t="n">
-        <v>68.18181818181819</v>
-      </c>
-      <c r="K36" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="41" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="41" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="41" t="inlineStr">
-        <is>
-          <t>49.00/88.00</t>
-        </is>
-      </c>
-      <c r="E37" s="43" t="n">
-        <v>55.68181818181818</v>
-      </c>
-      <c r="F37" s="43" t="n">
-        <v>38.97727272727273</v>
-      </c>
-      <c r="G37" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H37" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="43" t="n">
-        <v>68.97727272727272</v>
-      </c>
-      <c r="K37" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="41" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="41" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="41" t="inlineStr">
-        <is>
-          <t>48.00/88.00</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>54.54545454545454</v>
-      </c>
-      <c r="F38" s="43" t="n">
-        <v>38.18181818181818</v>
-      </c>
-      <c r="G38" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H38" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="43" t="n">
-        <v>68.18181818181819</v>
-      </c>
-      <c r="K38" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="41" t="inlineStr">
-        <is>
-          <t>75.00/88.00</t>
-        </is>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>85.22727272727273</v>
-      </c>
-      <c r="F39" s="43" t="n">
-        <v>59.65909090909091</v>
-      </c>
-      <c r="G39" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H39" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="43" t="n">
-        <v>89.65909090909091</v>
-      </c>
-      <c r="K39" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="41" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="41" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="41" t="inlineStr">
-        <is>
-          <t>56.00/88.00</t>
-        </is>
-      </c>
-      <c r="E40" s="43" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="F40" s="43" t="n">
-        <v>44.54545454545455</v>
-      </c>
-      <c r="G40" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H40" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="43" t="n">
-        <v>74.54545454545455</v>
-      </c>
-      <c r="K40" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="41" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="41" t="inlineStr">
-        <is>
-          <t>67.00/88.00</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>76.13636363636364</v>
-      </c>
-      <c r="F41" s="43" t="n">
-        <v>53.29545454545455</v>
-      </c>
-      <c r="G41" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H41" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="43" t="n">
-        <v>83.29545454545455</v>
-      </c>
-      <c r="K41" s="41" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="41" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="41" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="41" t="inlineStr">
-        <is>
-          <t>61.00/88.00</t>
-        </is>
-      </c>
-      <c r="E42" s="43" t="n">
-        <v>69.31818181818183</v>
-      </c>
-      <c r="F42" s="43" t="n">
-        <v>48.52272727272727</v>
-      </c>
-      <c r="G42" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H42" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="43" t="n">
-        <v>78.52272727272728</v>
-      </c>
-      <c r="K42" s="41" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="41" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="41" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="41" t="inlineStr">
-        <is>
-          <t>77.00/88.00</t>
-        </is>
-      </c>
-      <c r="E43" s="43" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="F43" s="43" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="G43" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H43" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="43" t="n">
-        <v>91.25</v>
-      </c>
-      <c r="K43" s="41" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="41" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="41" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="41" t="inlineStr">
-        <is>
-          <t>76.00/88.00</t>
-        </is>
-      </c>
-      <c r="E44" s="43" t="n">
-        <v>86.36363636363636</v>
-      </c>
-      <c r="F44" s="43" t="n">
-        <v>60.45454545454545</v>
-      </c>
-      <c r="G44" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H44" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="43" t="n">
-        <v>90.45454545454545</v>
-      </c>
-      <c r="K44" s="41" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="41" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="41" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="41" t="inlineStr">
-        <is>
-          <t>42.00/88.00</t>
-        </is>
-      </c>
-      <c r="E45" s="43" t="n">
-        <v>47.72727272727273</v>
-      </c>
-      <c r="F45" s="43" t="n">
-        <v>33.40909090909091</v>
-      </c>
-      <c r="G45" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H45" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="43" t="n">
-        <v>63.40909090909091</v>
-      </c>
-      <c r="K45" s="41" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="41" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="41" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="inlineStr">
-        <is>
-          <t>82.00/88.00</t>
-        </is>
-      </c>
-      <c r="E46" s="43" t="n">
-        <v>93.18181818181817</v>
-      </c>
-      <c r="F46" s="43" t="n">
-        <v>65.22727272727272</v>
-      </c>
-      <c r="G46" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H46" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="43" t="n">
-        <v>95.22727272727272</v>
-      </c>
-      <c r="K46" s="41" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="41" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="47" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="49" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="47" t="n"/>
+      <c r="B54" s="48" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="47" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="42" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="inlineStr">
-        <is>
-          <t>76.00/88.00</t>
-        </is>
-      </c>
-      <c r="E47" s="43" t="n">
-        <v>86.36363636363636</v>
-      </c>
-      <c r="F47" s="43" t="n">
-        <v>60.45454545454545</v>
-      </c>
-      <c r="G47" s="41" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H47" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="43" t="n">
-        <v>90.45454545454545</v>
-      </c>
-      <c r="K47" s="41" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="44" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="45" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="44" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="46" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="44" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="45" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="44" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="46" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="44" t="n"/>
-      <c r="B54" s="45" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="44" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="45" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="47" t="n">
-        <v>67.40118577075098</v>
+      <c r="B56" s="50" t="n">
+        <v>69.87577639751552</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="44" t="inlineStr">
+      <c r="A57" s="47" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="47" t="n">
-        <v>22.89945411126535</v>
+      <c r="B57" s="50" t="n">
+        <v>21.45721912582595</v>
       </c>
     </row>
   </sheetData>
